--- a/artfynd/A 51504-2025 artfynd.xlsx
+++ b/artfynd/A 51504-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY125"/>
+  <dimension ref="A1:AY198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16018,6 +16018,8292 @@
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>134161617</v>
+      </c>
+      <c r="B126" t="n">
+        <v>79358</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>460738</v>
+      </c>
+      <c r="R126" t="n">
+        <v>7051903</v>
+      </c>
+      <c r="S126" t="n">
+        <v>4</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>Fördelat på 2 gamla granar</t>
+        </is>
+      </c>
+      <c r="AD126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>134159342</v>
+      </c>
+      <c r="B127" t="n">
+        <v>79358</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>460672</v>
+      </c>
+      <c r="R127" t="n">
+        <v>7051847</v>
+      </c>
+      <c r="S127" t="n">
+        <v>10</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AD127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT127" t="inlineStr"/>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>134171971</v>
+      </c>
+      <c r="B128" t="n">
+        <v>96396</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>460688</v>
+      </c>
+      <c r="R128" t="n">
+        <v>7051821</v>
+      </c>
+      <c r="S128" t="n">
+        <v>3</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>09:04</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>09:04</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>På marken i gammal fuktig granskog</t>
+        </is>
+      </c>
+      <c r="AD128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT128" t="inlineStr"/>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>134166248</v>
+      </c>
+      <c r="B129" t="n">
+        <v>79358</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Lortåsen, Lortåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q129" t="n">
+        <v>460708</v>
+      </c>
+      <c r="R129" t="n">
+        <v>7052503</v>
+      </c>
+      <c r="S129" t="n">
+        <v>10</v>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT129" t="inlineStr"/>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>134161325</v>
+      </c>
+      <c r="B130" t="n">
+        <v>99200</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q130" t="n">
+        <v>460664</v>
+      </c>
+      <c r="R130" t="n">
+        <v>7051927</v>
+      </c>
+      <c r="S130" t="n">
+        <v>5</v>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AD130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT130" t="inlineStr"/>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>134159098</v>
+      </c>
+      <c r="B131" t="n">
+        <v>80429</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>229748</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Protopannaria pezizoides</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q131" t="n">
+        <v>460718</v>
+      </c>
+      <c r="R131" t="n">
+        <v>7051777</v>
+      </c>
+      <c r="S131" t="n">
+        <v>5</v>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>09:08</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>09:08</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>På död, klen rönn</t>
+        </is>
+      </c>
+      <c r="AD131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT131" t="inlineStr"/>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>134165576</v>
+      </c>
+      <c r="B132" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>Lortåsen, Lortåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q132" t="n">
+        <v>460650</v>
+      </c>
+      <c r="R132" t="n">
+        <v>7052431</v>
+      </c>
+      <c r="S132" t="n">
+        <v>10</v>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AD132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT132" t="inlineStr"/>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>134165432</v>
+      </c>
+      <c r="B133" t="n">
+        <v>79790</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>1778</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Fjällig knopplav</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Biatora fallax</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Hepp</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>Lortåsen, Lortåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q133" t="n">
+        <v>460673</v>
+      </c>
+      <c r="R133" t="n">
+        <v>7052450</v>
+      </c>
+      <c r="S133" t="n">
+        <v>10</v>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>På bark vid basen av gammal levande grov gran i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT133" t="inlineStr"/>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>134165125</v>
+      </c>
+      <c r="B134" t="n">
+        <v>99200</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>Lortåsen, Lortåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q134" t="n">
+        <v>460690</v>
+      </c>
+      <c r="R134" t="n">
+        <v>7052375</v>
+      </c>
+      <c r="S134" t="n">
+        <v>5</v>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AD134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT134" t="inlineStr"/>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>134162895</v>
+      </c>
+      <c r="B135" t="n">
+        <v>79358</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q135" t="n">
+        <v>460789</v>
+      </c>
+      <c r="R135" t="n">
+        <v>7051975</v>
+      </c>
+      <c r="S135" t="n">
+        <v>6</v>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT135" t="inlineStr"/>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX135" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>134158960</v>
+      </c>
+      <c r="B136" t="n">
+        <v>80477</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q136" t="n">
+        <v>460718</v>
+      </c>
+      <c r="R136" t="n">
+        <v>7051777</v>
+      </c>
+      <c r="S136" t="n">
+        <v>5</v>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AD136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT136" t="inlineStr"/>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX136" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>134165214</v>
+      </c>
+      <c r="B137" t="n">
+        <v>80478</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>Lortåsen, Lortåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q137" t="n">
+        <v>460690</v>
+      </c>
+      <c r="R137" t="n">
+        <v>7052375</v>
+      </c>
+      <c r="S137" t="n">
+        <v>4</v>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>På rönn</t>
+        </is>
+      </c>
+      <c r="AD137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT137" t="inlineStr"/>
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX137" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>134159178</v>
+      </c>
+      <c r="B138" t="n">
+        <v>80478</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q138" t="n">
+        <v>460683</v>
+      </c>
+      <c r="R138" t="n">
+        <v>7051835</v>
+      </c>
+      <c r="S138" t="n">
+        <v>6</v>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB138" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>På död, klen rönn</t>
+        </is>
+      </c>
+      <c r="AD138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT138" t="inlineStr"/>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX138" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>134171947</v>
+      </c>
+      <c r="B139" t="n">
+        <v>80485</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q139" t="n">
+        <v>460715</v>
+      </c>
+      <c r="R139" t="n">
+        <v>7052448</v>
+      </c>
+      <c r="S139" t="n">
+        <v>4</v>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>På rönnlåga i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT139" t="inlineStr"/>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>134171951</v>
+      </c>
+      <c r="B140" t="n">
+        <v>79358</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q140" t="n">
+        <v>460689</v>
+      </c>
+      <c r="R140" t="n">
+        <v>7052417</v>
+      </c>
+      <c r="S140" t="n">
+        <v>3</v>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AD140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT140" t="inlineStr"/>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>134166744</v>
+      </c>
+      <c r="B141" t="n">
+        <v>79358</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>Lortåsen, Lortåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q141" t="n">
+        <v>460779</v>
+      </c>
+      <c r="R141" t="n">
+        <v>7052179</v>
+      </c>
+      <c r="S141" t="n">
+        <v>10</v>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>Rikligt på gammal levande gran i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT141" t="inlineStr"/>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX141" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>134165139</v>
+      </c>
+      <c r="B142" t="n">
+        <v>79358</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>Lortåsen, Lortåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q142" t="n">
+        <v>460690</v>
+      </c>
+      <c r="R142" t="n">
+        <v>7052375</v>
+      </c>
+      <c r="S142" t="n">
+        <v>10</v>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AD142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT142" t="inlineStr"/>
+      <c r="AW142" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX142" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>134162493</v>
+      </c>
+      <c r="B143" t="n">
+        <v>80477</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q143" t="n">
+        <v>460804</v>
+      </c>
+      <c r="R143" t="n">
+        <v>7052009</v>
+      </c>
+      <c r="S143" t="n">
+        <v>4</v>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AD143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT143" t="inlineStr"/>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>134163868</v>
+      </c>
+      <c r="B144" t="n">
+        <v>79358</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>Lortåsen, Lortåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q144" t="n">
+        <v>460752</v>
+      </c>
+      <c r="R144" t="n">
+        <v>7052276</v>
+      </c>
+      <c r="S144" t="n">
+        <v>10</v>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>Rikligt på gammal levande grov gran (45 cm dbh) i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT144" t="inlineStr"/>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>134165713</v>
+      </c>
+      <c r="B145" t="n">
+        <v>80478</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>Lortåsen, Lortåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q145" t="n">
+        <v>460711</v>
+      </c>
+      <c r="R145" t="n">
+        <v>7052457</v>
+      </c>
+      <c r="S145" t="n">
+        <v>8</v>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB145" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>På gammal rönn i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT145" t="inlineStr"/>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX145" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>134171966</v>
+      </c>
+      <c r="B146" t="n">
+        <v>80429</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>229748</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Protopannaria pezizoides</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q146" t="n">
+        <v>460676</v>
+      </c>
+      <c r="R146" t="n">
+        <v>7051857</v>
+      </c>
+      <c r="S146" t="n">
+        <v>3</v>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z146" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB146" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>På rönn i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT146" t="inlineStr"/>
+      <c r="AW146" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX146" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>134171965</v>
+      </c>
+      <c r="B147" t="n">
+        <v>106291</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q147" t="n">
+        <v>460691</v>
+      </c>
+      <c r="R147" t="n">
+        <v>7051813</v>
+      </c>
+      <c r="S147" t="n">
+        <v>8</v>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB147" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT147" t="inlineStr"/>
+      <c r="AW147" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX147" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>134166104</v>
+      </c>
+      <c r="B148" t="n">
+        <v>99200</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>Lortåsen, Lortåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q148" t="n">
+        <v>460692</v>
+      </c>
+      <c r="R148" t="n">
+        <v>7052457</v>
+      </c>
+      <c r="S148" t="n">
+        <v>4</v>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB148" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AD148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT148" t="inlineStr"/>
+      <c r="AW148" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX148" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>134171976</v>
+      </c>
+      <c r="B149" t="n">
+        <v>99200</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q149" t="n">
+        <v>460751</v>
+      </c>
+      <c r="R149" t="n">
+        <v>7051437</v>
+      </c>
+      <c r="S149" t="n">
+        <v>3</v>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>På marken i äldre granskog</t>
+        </is>
+      </c>
+      <c r="AD149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT149" t="inlineStr"/>
+      <c r="AW149" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX149" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>134158853</v>
+      </c>
+      <c r="B150" t="n">
+        <v>99200</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q150" t="n">
+        <v>460723</v>
+      </c>
+      <c r="R150" t="n">
+        <v>7051736</v>
+      </c>
+      <c r="S150" t="n">
+        <v>3</v>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z150" t="inlineStr">
+        <is>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB150" t="inlineStr">
+        <is>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="AD150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT150" t="inlineStr"/>
+      <c r="AW150" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX150" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>134171956</v>
+      </c>
+      <c r="B151" t="n">
+        <v>79358</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q151" t="n">
+        <v>460688</v>
+      </c>
+      <c r="R151" t="n">
+        <v>7052421</v>
+      </c>
+      <c r="S151" t="n">
+        <v>3</v>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AD151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT151" t="inlineStr"/>
+      <c r="AW151" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX151" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>134171946</v>
+      </c>
+      <c r="B152" t="n">
+        <v>80478</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr"/>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q152" t="n">
+        <v>460716</v>
+      </c>
+      <c r="R152" t="n">
+        <v>7052447</v>
+      </c>
+      <c r="S152" t="n">
+        <v>3</v>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z152" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB152" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>På rönnlåga i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT152" t="inlineStr"/>
+      <c r="AW152" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX152" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>134171970</v>
+      </c>
+      <c r="B153" t="n">
+        <v>101386</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q153" t="n">
+        <v>460688</v>
+      </c>
+      <c r="R153" t="n">
+        <v>7051821</v>
+      </c>
+      <c r="S153" t="n">
+        <v>3</v>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>På marken i gammal fuktig granskog</t>
+        </is>
+      </c>
+      <c r="AD153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT153" t="inlineStr"/>
+      <c r="AW153" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX153" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>134161529</v>
+      </c>
+      <c r="B154" t="n">
+        <v>79358</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q154" t="n">
+        <v>460757</v>
+      </c>
+      <c r="R154" t="n">
+        <v>7051937</v>
+      </c>
+      <c r="S154" t="n">
+        <v>8</v>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W154" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z154" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB154" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>Fördelat på 3 gamla granar</t>
+        </is>
+      </c>
+      <c r="AD154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT154" t="inlineStr"/>
+      <c r="AW154" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX154" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>134161209</v>
+      </c>
+      <c r="B155" t="n">
+        <v>91920</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q155" t="n">
+        <v>460668</v>
+      </c>
+      <c r="R155" t="n">
+        <v>7051920</v>
+      </c>
+      <c r="S155" t="n">
+        <v>5</v>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AD155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT155" t="inlineStr"/>
+      <c r="AW155" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX155" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>134163277</v>
+      </c>
+      <c r="B156" t="n">
+        <v>79358</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>Lortåsen, Lortåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q156" t="n">
+        <v>460726</v>
+      </c>
+      <c r="R156" t="n">
+        <v>7052196</v>
+      </c>
+      <c r="S156" t="n">
+        <v>10</v>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W156" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>Fördelat på 3 gamla granar</t>
+        </is>
+      </c>
+      <c r="AD156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT156" t="inlineStr"/>
+      <c r="AW156" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX156" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>134162816</v>
+      </c>
+      <c r="B157" t="n">
+        <v>79358</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>Kampen, Kampen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q157" t="n">
+        <v>460812</v>
+      </c>
+      <c r="R157" t="n">
+        <v>7052078</v>
+      </c>
+      <c r="S157" t="n">
+        <v>10</v>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>Gammal död gran (ca 23 cm dbh) draperad med garnlav i gammal gles granskog</t>
+        </is>
+      </c>
+      <c r="AD157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT157" t="inlineStr"/>
+      <c r="AW157" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX157" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>134166640</v>
+      </c>
+      <c r="B158" t="n">
+        <v>79358</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>Lortåsen, Lortåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q158" t="n">
+        <v>460776</v>
+      </c>
+      <c r="R158" t="n">
+        <v>7052247</v>
+      </c>
+      <c r="S158" t="n">
+        <v>8</v>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W158" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB158" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AD158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT158" t="inlineStr"/>
+      <c r="AW158" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX158" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>134163338</v>
+      </c>
+      <c r="B159" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>Lortåsen, Lortåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q159" t="n">
+        <v>460744</v>
+      </c>
+      <c r="R159" t="n">
+        <v>7052204</v>
+      </c>
+      <c r="S159" t="n">
+        <v>10</v>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>Ca 5 äldre rader med ringhack på gammal grov levande gran i gammal garnlavsrik granskog</t>
+        </is>
+      </c>
+      <c r="AD159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT159" t="inlineStr"/>
+      <c r="AW159" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX159" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>134171949</v>
+      </c>
+      <c r="B160" t="n">
+        <v>79358</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q160" t="n">
+        <v>460691</v>
+      </c>
+      <c r="R160" t="n">
+        <v>7052421</v>
+      </c>
+      <c r="S160" t="n">
+        <v>3</v>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W160" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB160" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AD160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT160" t="inlineStr"/>
+      <c r="AW160" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX160" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>134171952</v>
+      </c>
+      <c r="B161" t="n">
+        <v>79358</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q161" t="n">
+        <v>460688</v>
+      </c>
+      <c r="R161" t="n">
+        <v>7052420</v>
+      </c>
+      <c r="S161" t="n">
+        <v>3</v>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W161" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y161" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z161" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB161" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AD161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT161" t="inlineStr"/>
+      <c r="AW161" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX161" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>134171954</v>
+      </c>
+      <c r="B162" t="n">
+        <v>79358</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr"/>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q162" t="n">
+        <v>460686</v>
+      </c>
+      <c r="R162" t="n">
+        <v>7052421</v>
+      </c>
+      <c r="S162" t="n">
+        <v>3</v>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W162" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y162" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AD162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT162" t="inlineStr"/>
+      <c r="AW162" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX162" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>134160980</v>
+      </c>
+      <c r="B163" t="n">
+        <v>83343</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr"/>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q163" t="n">
+        <v>460672</v>
+      </c>
+      <c r="R163" t="n">
+        <v>7051901</v>
+      </c>
+      <c r="S163" t="n">
+        <v>4</v>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W163" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y163" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z163" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB163" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC163" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
+        </is>
+      </c>
+      <c r="AD163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT163" t="inlineStr"/>
+      <c r="AW163" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX163" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>134165091</v>
+      </c>
+      <c r="B164" t="n">
+        <v>91920</v>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr"/>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>Lortåsen, Lortåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q164" t="n">
+        <v>460690</v>
+      </c>
+      <c r="R164" t="n">
+        <v>7052375</v>
+      </c>
+      <c r="S164" t="n">
+        <v>6</v>
+      </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V164" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W164" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y164" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z164" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB164" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AD164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT164" t="inlineStr"/>
+      <c r="AW164" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX164" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>134158548</v>
+      </c>
+      <c r="B165" t="n">
+        <v>99178</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q165" t="n">
+        <v>460863</v>
+      </c>
+      <c r="R165" t="n">
+        <v>7051485</v>
+      </c>
+      <c r="S165" t="n">
+        <v>3</v>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W165" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>08:37</t>
+        </is>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB165" t="inlineStr">
+        <is>
+          <t>08:37</t>
+        </is>
+      </c>
+      <c r="AD165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT165" t="inlineStr"/>
+      <c r="AW165" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX165" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>134171957</v>
+      </c>
+      <c r="B166" t="n">
+        <v>79358</v>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr"/>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q166" t="n">
+        <v>460698</v>
+      </c>
+      <c r="R166" t="n">
+        <v>7052420</v>
+      </c>
+      <c r="S166" t="n">
+        <v>4</v>
+      </c>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V166" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W166" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y166" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z166" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB166" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AD166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT166" t="inlineStr"/>
+      <c r="AW166" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX166" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>134171967</v>
+      </c>
+      <c r="B167" t="n">
+        <v>80478</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr"/>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q167" t="n">
+        <v>460677</v>
+      </c>
+      <c r="R167" t="n">
+        <v>7051857</v>
+      </c>
+      <c r="S167" t="n">
+        <v>15</v>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>09:16</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB167" t="inlineStr">
+        <is>
+          <t>09:16</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>På gammal levande rönn i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT167" t="inlineStr"/>
+      <c r="AW167" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX167" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>134158911</v>
+      </c>
+      <c r="B168" t="n">
+        <v>99200</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr"/>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q168" t="n">
+        <v>460718</v>
+      </c>
+      <c r="R168" t="n">
+        <v>7051777</v>
+      </c>
+      <c r="S168" t="n">
+        <v>8</v>
+      </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V168" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W168" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y168" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z168" t="inlineStr">
+        <is>
+          <t>08:58</t>
+        </is>
+      </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB168" t="inlineStr">
+        <is>
+          <t>08:58</t>
+        </is>
+      </c>
+      <c r="AD168" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE168" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG168" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT168" t="inlineStr"/>
+      <c r="AW168" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX168" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>134163852</v>
+      </c>
+      <c r="B169" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr"/>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>Lortåsen, Lortåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q169" t="n">
+        <v>460763</v>
+      </c>
+      <c r="R169" t="n">
+        <v>7052266</v>
+      </c>
+      <c r="S169" t="n">
+        <v>9</v>
+      </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W169" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y169" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z169" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB169" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AC169" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT169" t="inlineStr"/>
+      <c r="AW169" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX169" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>134159322</v>
+      </c>
+      <c r="B170" t="n">
+        <v>99200</v>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr"/>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q170" t="n">
+        <v>460672</v>
+      </c>
+      <c r="R170" t="n">
+        <v>7051847</v>
+      </c>
+      <c r="S170" t="n">
+        <v>3</v>
+      </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V170" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W170" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y170" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB170" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="AD170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT170" t="inlineStr"/>
+      <c r="AW170" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX170" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>134171955</v>
+      </c>
+      <c r="B171" t="n">
+        <v>79358</v>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr"/>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q171" t="n">
+        <v>460685</v>
+      </c>
+      <c r="R171" t="n">
+        <v>7052421</v>
+      </c>
+      <c r="S171" t="n">
+        <v>3</v>
+      </c>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W171" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y171" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z171" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB171" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AD171" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE171" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG171" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT171" t="inlineStr"/>
+      <c r="AW171" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX171" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>134171974</v>
+      </c>
+      <c r="B172" t="n">
+        <v>79977</v>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr"/>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q172" t="n">
+        <v>460722</v>
+      </c>
+      <c r="R172" t="n">
+        <v>7051751</v>
+      </c>
+      <c r="S172" t="n">
+        <v>3</v>
+      </c>
+      <c r="T172" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V172" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W172" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y172" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z172" t="inlineStr">
+        <is>
+          <t>08:56</t>
+        </is>
+      </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB172" t="inlineStr">
+        <is>
+          <t>08:56</t>
+        </is>
+      </c>
+      <c r="AC172" t="inlineStr">
+        <is>
+          <t>På dimensionsavverkningsstubbe av tall i gammal garnlavsrik granskog</t>
+        </is>
+      </c>
+      <c r="AD172" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE172" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG172" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT172" t="inlineStr"/>
+      <c r="AW172" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX172" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>134164951</v>
+      </c>
+      <c r="B173" t="n">
+        <v>96406</v>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr"/>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>Lortåsen, Lortåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q173" t="n">
+        <v>460763</v>
+      </c>
+      <c r="R173" t="n">
+        <v>7052266</v>
+      </c>
+      <c r="S173" t="n">
+        <v>5</v>
+      </c>
+      <c r="T173" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V173" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W173" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y173" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z173" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB173" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AC173" t="inlineStr">
+        <is>
+          <t>På block i kanten av lok</t>
+        </is>
+      </c>
+      <c r="AD173" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE173" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG173" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT173" t="inlineStr"/>
+      <c r="AW173" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX173" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>134171973</v>
+      </c>
+      <c r="B174" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" t="inlineStr"/>
+      <c r="N174" t="inlineStr"/>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q174" t="n">
+        <v>460716</v>
+      </c>
+      <c r="R174" t="n">
+        <v>7051811</v>
+      </c>
+      <c r="S174" t="n">
+        <v>3</v>
+      </c>
+      <c r="T174" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V174" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W174" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y174" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z174" t="inlineStr">
+        <is>
+          <t>08:59</t>
+        </is>
+      </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB174" t="inlineStr">
+        <is>
+          <t>08:59</t>
+        </is>
+      </c>
+      <c r="AC174" t="inlineStr">
+        <is>
+          <t>1 ex uppflog</t>
+        </is>
+      </c>
+      <c r="AD174" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE174" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG174" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT174" t="inlineStr"/>
+      <c r="AW174" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX174" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>134161522</v>
+      </c>
+      <c r="B175" t="n">
+        <v>79358</v>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q175" t="n">
+        <v>460702</v>
+      </c>
+      <c r="R175" t="n">
+        <v>7051854</v>
+      </c>
+      <c r="S175" t="n">
+        <v>6</v>
+      </c>
+      <c r="T175" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V175" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W175" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y175" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z175" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB175" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AC175" t="inlineStr">
+        <is>
+          <t>Rikligt, draperat, på de flesta granar i gammal flerskiktad granskog</t>
+        </is>
+      </c>
+      <c r="AD175" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE175" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG175" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT175" t="inlineStr"/>
+      <c r="AW175" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX175" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>134165583</v>
+      </c>
+      <c r="B176" t="n">
+        <v>58079</v>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E176" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>Lortåsen, Lortåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q176" t="n">
+        <v>460650</v>
+      </c>
+      <c r="R176" t="n">
+        <v>7052431</v>
+      </c>
+      <c r="S176" t="n">
+        <v>10</v>
+      </c>
+      <c r="T176" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V176" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W176" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y176" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z176" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB176" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AD176" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE176" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG176" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT176" t="inlineStr"/>
+      <c r="AW176" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX176" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>134160600</v>
+      </c>
+      <c r="B177" t="n">
+        <v>79358</v>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q177" t="n">
+        <v>460703</v>
+      </c>
+      <c r="R177" t="n">
+        <v>7051878</v>
+      </c>
+      <c r="S177" t="n">
+        <v>4</v>
+      </c>
+      <c r="T177" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V177" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W177" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y177" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z177" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB177" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AC177" t="inlineStr">
+        <is>
+          <t>På grov gammal gran</t>
+        </is>
+      </c>
+      <c r="AD177" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE177" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG177" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT177" t="inlineStr"/>
+      <c r="AW177" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX177" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>134163087</v>
+      </c>
+      <c r="B178" t="n">
+        <v>89338</v>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E178" t="n">
+        <v>510</v>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr"/>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q178" t="n">
+        <v>460736</v>
+      </c>
+      <c r="R178" t="n">
+        <v>7052124</v>
+      </c>
+      <c r="S178" t="n">
+        <v>3</v>
+      </c>
+      <c r="T178" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V178" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W178" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y178" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z178" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB178" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AC178" t="inlineStr">
+        <is>
+          <t>På gammal granlåga</t>
+        </is>
+      </c>
+      <c r="AD178" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE178" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG178" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT178" t="inlineStr"/>
+      <c r="AW178" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX178" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>134171960</v>
+      </c>
+      <c r="B179" t="n">
+        <v>79358</v>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr"/>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q179" t="n">
+        <v>460692</v>
+      </c>
+      <c r="R179" t="n">
+        <v>7052417</v>
+      </c>
+      <c r="S179" t="n">
+        <v>3</v>
+      </c>
+      <c r="T179" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V179" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W179" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y179" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z179" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB179" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AD179" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE179" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG179" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT179" t="inlineStr"/>
+      <c r="AW179" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX179" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>134161245</v>
+      </c>
+      <c r="B180" t="n">
+        <v>83207</v>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E180" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr"/>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q180" t="n">
+        <v>460664</v>
+      </c>
+      <c r="R180" t="n">
+        <v>7051927</v>
+      </c>
+      <c r="S180" t="n">
+        <v>6</v>
+      </c>
+      <c r="T180" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V180" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W180" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y180" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z180" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB180" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AC180" t="inlineStr">
+        <is>
+          <t>På död gammal gran</t>
+        </is>
+      </c>
+      <c r="AD180" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE180" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG180" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT180" t="inlineStr"/>
+      <c r="AW180" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX180" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>134162652</v>
+      </c>
+      <c r="B181" t="n">
+        <v>79358</v>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>Kampen, Kampen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q181" t="n">
+        <v>460812</v>
+      </c>
+      <c r="R181" t="n">
+        <v>7052075</v>
+      </c>
+      <c r="S181" t="n">
+        <v>10</v>
+      </c>
+      <c r="T181" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V181" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W181" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y181" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z181" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB181" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AC181" t="inlineStr">
+        <is>
+          <t>Gammal gran draperad med garnlav, i gammal gles granskog</t>
+        </is>
+      </c>
+      <c r="AD181" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE181" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG181" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT181" t="inlineStr"/>
+      <c r="AW181" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX181" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>134165861</v>
+      </c>
+      <c r="B182" t="n">
+        <v>79358</v>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E182" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr"/>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>Lortåsen, Lortåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q182" t="n">
+        <v>460714</v>
+      </c>
+      <c r="R182" t="n">
+        <v>7052420</v>
+      </c>
+      <c r="S182" t="n">
+        <v>10</v>
+      </c>
+      <c r="T182" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V182" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W182" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y182" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z182" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB182" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AC182" t="inlineStr">
+        <is>
+          <t>På gammal grov gran, 70 cm i diameter, i gammal bördig granskog</t>
+        </is>
+      </c>
+      <c r="AD182" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE182" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG182" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT182" t="inlineStr"/>
+      <c r="AW182" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX182" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>134165723</v>
+      </c>
+      <c r="B183" t="n">
+        <v>80429</v>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E183" t="n">
+        <v>229748</v>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Protopannaria pezizoides</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr"/>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>Lortåsen, Lortåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q183" t="n">
+        <v>460711</v>
+      </c>
+      <c r="R183" t="n">
+        <v>7052457</v>
+      </c>
+      <c r="S183" t="n">
+        <v>10</v>
+      </c>
+      <c r="T183" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V183" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W183" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y183" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z183" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB183" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AC183" t="inlineStr">
+        <is>
+          <t>På gammal rönn i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD183" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE183" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG183" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT183" t="inlineStr"/>
+      <c r="AW183" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX183" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>134161669</v>
+      </c>
+      <c r="B184" t="n">
+        <v>79358</v>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q184" t="n">
+        <v>460693</v>
+      </c>
+      <c r="R184" t="n">
+        <v>7051901</v>
+      </c>
+      <c r="S184" t="n">
+        <v>10</v>
+      </c>
+      <c r="T184" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V184" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W184" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y184" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z184" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB184" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AC184" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD184" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE184" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG184" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT184" t="inlineStr"/>
+      <c r="AW184" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX184" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>134165966</v>
+      </c>
+      <c r="B185" t="n">
+        <v>79790</v>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E185" t="n">
+        <v>1778</v>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Fjällig knopplav</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Biatora fallax</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Hepp</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr"/>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>Lortåsen, Lortåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q185" t="n">
+        <v>460694</v>
+      </c>
+      <c r="R185" t="n">
+        <v>7052451</v>
+      </c>
+      <c r="S185" t="n">
+        <v>10</v>
+      </c>
+      <c r="T185" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V185" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W185" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y185" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z185" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB185" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AC185" t="inlineStr">
+        <is>
+          <t>På bark på rotben på gammal levande grov gran (55 cm dbh) i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD185" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE185" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG185" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT185" t="inlineStr"/>
+      <c r="AW185" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX185" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>134163114</v>
+      </c>
+      <c r="B186" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E186" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr"/>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q186" t="n">
+        <v>460736</v>
+      </c>
+      <c r="R186" t="n">
+        <v>7052124</v>
+      </c>
+      <c r="S186" t="n">
+        <v>4</v>
+      </c>
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V186" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W186" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y186" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z186" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB186" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AC186" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD186" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE186" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG186" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT186" t="inlineStr"/>
+      <c r="AW186" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX186" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>134161962</v>
+      </c>
+      <c r="B187" t="n">
+        <v>83207</v>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E187" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr"/>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q187" t="n">
+        <v>460653</v>
+      </c>
+      <c r="R187" t="n">
+        <v>7051927</v>
+      </c>
+      <c r="S187" t="n">
+        <v>4</v>
+      </c>
+      <c r="T187" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V187" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W187" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y187" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z187" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB187" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AC187" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
+        </is>
+      </c>
+      <c r="AD187" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE187" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG187" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT187" t="inlineStr"/>
+      <c r="AW187" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX187" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>134171972</v>
+      </c>
+      <c r="B188" t="n">
+        <v>79358</v>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E188" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr"/>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q188" t="n">
+        <v>460714</v>
+      </c>
+      <c r="R188" t="n">
+        <v>7051804</v>
+      </c>
+      <c r="S188" t="n">
+        <v>3</v>
+      </c>
+      <c r="T188" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U188" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V188" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W188" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y188" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z188" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB188" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="AC188" t="inlineStr">
+        <is>
+          <t>1000 ex fördelat på 10 granar i gammal garnlavsrik granskog</t>
+        </is>
+      </c>
+      <c r="AD188" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE188" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG188" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT188" t="inlineStr"/>
+      <c r="AW188" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX188" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>134164962</v>
+      </c>
+      <c r="B189" t="n">
+        <v>96396</v>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E189" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr"/>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>Lortåsen, Lortåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q189" t="n">
+        <v>460763</v>
+      </c>
+      <c r="R189" t="n">
+        <v>7052266</v>
+      </c>
+      <c r="S189" t="n">
+        <v>5</v>
+      </c>
+      <c r="T189" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U189" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V189" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W189" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y189" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z189" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB189" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AC189" t="inlineStr">
+        <is>
+          <t>På block i kanten av lok</t>
+        </is>
+      </c>
+      <c r="AD189" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE189" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG189" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT189" t="inlineStr"/>
+      <c r="AW189" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX189" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>134161368</v>
+      </c>
+      <c r="B190" t="n">
+        <v>79358</v>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E190" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q190" t="n">
+        <v>460664</v>
+      </c>
+      <c r="R190" t="n">
+        <v>7051927</v>
+      </c>
+      <c r="S190" t="n">
+        <v>7</v>
+      </c>
+      <c r="T190" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V190" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W190" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y190" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z190" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB190" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AC190" t="inlineStr">
+        <is>
+          <t>På grov gammal gran</t>
+        </is>
+      </c>
+      <c r="AD190" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE190" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG190" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT190" t="inlineStr"/>
+      <c r="AW190" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX190" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>134162490</v>
+      </c>
+      <c r="B191" t="n">
+        <v>91957</v>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E191" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr"/>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q191" t="n">
+        <v>460806</v>
+      </c>
+      <c r="R191" t="n">
+        <v>7052008</v>
+      </c>
+      <c r="S191" t="n">
+        <v>5</v>
+      </c>
+      <c r="T191" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U191" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V191" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W191" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y191" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z191" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB191" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AC191" t="inlineStr">
+        <is>
+          <t>På gammal granlåga</t>
+        </is>
+      </c>
+      <c r="AD191" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE191" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG191" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT191" t="inlineStr"/>
+      <c r="AW191" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX191" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>134162546</v>
+      </c>
+      <c r="B192" t="n">
+        <v>79358</v>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E192" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q192" t="n">
+        <v>460804</v>
+      </c>
+      <c r="R192" t="n">
+        <v>7052009</v>
+      </c>
+      <c r="S192" t="n">
+        <v>9</v>
+      </c>
+      <c r="T192" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U192" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V192" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W192" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y192" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z192" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB192" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AC192" t="inlineStr">
+        <is>
+          <t>Fördelat på 5 gamla granar</t>
+        </is>
+      </c>
+      <c r="AD192" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE192" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG192" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT192" t="inlineStr"/>
+      <c r="AW192" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX192" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>134171958</v>
+      </c>
+      <c r="B193" t="n">
+        <v>79358</v>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E193" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr"/>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q193" t="n">
+        <v>460696</v>
+      </c>
+      <c r="R193" t="n">
+        <v>7052420</v>
+      </c>
+      <c r="S193" t="n">
+        <v>3</v>
+      </c>
+      <c r="T193" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U193" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V193" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W193" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y193" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z193" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB193" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AD193" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE193" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG193" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT193" t="inlineStr"/>
+      <c r="AW193" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX193" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>134162379</v>
+      </c>
+      <c r="B194" t="n">
+        <v>79358</v>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E194" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>Kampen, Kampen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q194" t="n">
+        <v>460792</v>
+      </c>
+      <c r="R194" t="n">
+        <v>7052051</v>
+      </c>
+      <c r="S194" t="n">
+        <v>10</v>
+      </c>
+      <c r="T194" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V194" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W194" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y194" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z194" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB194" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AC194" t="inlineStr">
+        <is>
+          <t>På gammal död gran (25 cm dbh) i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD194" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE194" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG194" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT194" t="inlineStr"/>
+      <c r="AW194" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX194" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>134166396</v>
+      </c>
+      <c r="B195" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E195" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr"/>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>Lortåsen, Lortåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q195" t="n">
+        <v>460693</v>
+      </c>
+      <c r="R195" t="n">
+        <v>7052473</v>
+      </c>
+      <c r="S195" t="n">
+        <v>10</v>
+      </c>
+      <c r="T195" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V195" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W195" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y195" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z195" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB195" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AC195" t="inlineStr">
+        <is>
+          <t>Ringhack på gammal levande gran i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD195" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE195" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG195" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT195" t="inlineStr"/>
+      <c r="AW195" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX195" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>134162445</v>
+      </c>
+      <c r="B196" t="n">
+        <v>79358</v>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E196" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>Kampen, Kampen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q196" t="n">
+        <v>460801</v>
+      </c>
+      <c r="R196" t="n">
+        <v>7052041</v>
+      </c>
+      <c r="S196" t="n">
+        <v>10</v>
+      </c>
+      <c r="T196" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V196" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W196" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y196" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z196" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB196" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AC196" t="inlineStr">
+        <is>
+          <t>På gammal, döende gran i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD196" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE196" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG196" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT196" t="inlineStr"/>
+      <c r="AW196" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX196" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>134160932</v>
+      </c>
+      <c r="B197" t="n">
+        <v>79358</v>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E197" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q197" t="n">
+        <v>460672</v>
+      </c>
+      <c r="R197" t="n">
+        <v>7051901</v>
+      </c>
+      <c r="S197" t="n">
+        <v>5</v>
+      </c>
+      <c r="T197" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V197" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W197" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y197" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z197" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB197" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AD197" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE197" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG197" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT197" t="inlineStr"/>
+      <c r="AW197" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX197" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>134171968</v>
+      </c>
+      <c r="B198" t="n">
+        <v>80484</v>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E198" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr"/>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q198" t="n">
+        <v>460675</v>
+      </c>
+      <c r="R198" t="n">
+        <v>7051857</v>
+      </c>
+      <c r="S198" t="n">
+        <v>4</v>
+      </c>
+      <c r="T198" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V198" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W198" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y198" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z198" t="inlineStr">
+        <is>
+          <t>09:16</t>
+        </is>
+      </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB198" t="inlineStr">
+        <is>
+          <t>09:16</t>
+        </is>
+      </c>
+      <c r="AC198" t="inlineStr">
+        <is>
+          <t>På gammal levande rönn i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD198" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE198" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG198" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT198" t="inlineStr"/>
+      <c r="AW198" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX198" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY198" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51504-2025 artfynd.xlsx
+++ b/artfynd/A 51504-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY198"/>
+  <dimension ref="A1:AY221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16374,57 +16374,48 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>134166248</v>
+        <v>134159098</v>
       </c>
       <c r="B129" t="n">
-        <v>79358</v>
+        <v>80429</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>229748</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>460708</v>
+        <v>460718</v>
       </c>
       <c r="R129" t="n">
-        <v>7052503</v>
+        <v>7051777</v>
       </c>
       <c r="S129" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -16453,7 +16444,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -16463,12 +16454,12 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På död, klen rönn</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -16483,60 +16474,74 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>134161325</v>
+        <v>134165576</v>
       </c>
       <c r="B130" t="n">
-        <v>99200</v>
+        <v>57975</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>460664</v>
+        <v>460650</v>
       </c>
       <c r="R130" t="n">
-        <v>7051927</v>
+        <v>7052431</v>
       </c>
       <c r="S130" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -16565,7 +16570,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -16575,7 +16580,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -16595,17 +16600,17 @@
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>134159098</v>
+        <v>134161325</v>
       </c>
       <c r="B131" t="n">
-        <v>80429</v>
+        <v>99200</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16613,21 +16618,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>229748</v>
+        <v>221952</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -16637,10 +16642,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>460718</v>
+        <v>460664</v>
       </c>
       <c r="R131" t="n">
-        <v>7051777</v>
+        <v>7051927</v>
       </c>
       <c r="S131" t="n">
         <v>5</v>
@@ -16672,7 +16677,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -16682,12 +16687,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>09:08</t>
-        </is>
-      </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>På död, klen rönn</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -16707,69 +16707,55 @@
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>134165576</v>
+        <v>134165125</v>
       </c>
       <c r="B132" t="n">
-        <v>57975</v>
+        <v>99200</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L132" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>460650</v>
+        <v>460690</v>
       </c>
       <c r="R132" t="n">
-        <v>7052431</v>
+        <v>7052375</v>
       </c>
       <c r="S132" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -16798,7 +16784,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -16808,7 +16794,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -16835,53 +16821,57 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>134165432</v>
+        <v>134162895</v>
       </c>
       <c r="B133" t="n">
-        <v>79790</v>
+        <v>79358</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1778</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Fjällig knopplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Biatora fallax</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Hepp</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr"/>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>460673</v>
+        <v>460789</v>
       </c>
       <c r="R133" t="n">
-        <v>7052450</v>
+        <v>7051975</v>
       </c>
       <c r="S133" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -16910,7 +16900,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -16920,12 +16910,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>12:42</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>På bark vid basen av gammal levande grov gran i gammal granskog</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -16940,60 +16925,65 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>134165125</v>
+        <v>134165432</v>
       </c>
       <c r="B134" t="n">
-        <v>99200</v>
+        <v>79790</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>221952</v>
+        <v>1778</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fjällig knopplav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Biatora fallax</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Hepp</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>460690</v>
+        <v>460673</v>
       </c>
       <c r="R134" t="n">
-        <v>7052375</v>
+        <v>7052450</v>
       </c>
       <c r="S134" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -17022,7 +17012,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -17032,7 +17022,12 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>På bark vid basen av gammal levande grov gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -17047,19 +17042,19 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>134162895</v>
+        <v>134166248</v>
       </c>
       <c r="B135" t="n">
         <v>79358</v>
@@ -17089,7 +17084,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -17099,17 +17094,17 @@
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>460789</v>
+        <v>460708</v>
       </c>
       <c r="R135" t="n">
-        <v>7051975</v>
+        <v>7052503</v>
       </c>
       <c r="S135" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -17138,7 +17133,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -17148,7 +17143,12 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -17163,22 +17163,22 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>134158960</v>
+        <v>134159178</v>
       </c>
       <c r="B136" t="n">
-        <v>80477</v>
+        <v>80478</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -17186,21 +17186,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6461</v>
+        <v>6462</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -17210,13 +17210,13 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>460718</v>
+        <v>460683</v>
       </c>
       <c r="R136" t="n">
-        <v>7051777</v>
+        <v>7051835</v>
       </c>
       <c r="S136" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -17245,7 +17245,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -17255,7 +17255,12 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>På död, klen rönn</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -17282,10 +17287,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>134165214</v>
+        <v>134158960</v>
       </c>
       <c r="B137" t="n">
-        <v>80478</v>
+        <v>80477</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -17293,37 +17298,37 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6462</v>
+        <v>6461</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>460690</v>
+        <v>460718</v>
       </c>
       <c r="R137" t="n">
-        <v>7052375</v>
+        <v>7051777</v>
       </c>
       <c r="S137" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -17352,7 +17357,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -17362,12 +17367,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>12:33</t>
-        </is>
-      </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>På rönn</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -17394,7 +17394,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>134159178</v>
+        <v>134165214</v>
       </c>
       <c r="B138" t="n">
         <v>80478</v>
@@ -17425,17 +17425,17 @@
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>460683</v>
+        <v>460690</v>
       </c>
       <c r="R138" t="n">
-        <v>7051835</v>
+        <v>7052375</v>
       </c>
       <c r="S138" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -17464,7 +17464,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -17474,12 +17474,12 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AC138" t="inlineStr">
         <is>
-          <t>På död, klen rönn</t>
+          <t>På rönn</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -17725,7 +17725,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>134166744</v>
+        <v>134165139</v>
       </c>
       <c r="B141" t="n">
         <v>79358</v>
@@ -17755,7 +17755,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>700</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -17769,10 +17769,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>460779</v>
+        <v>460690</v>
       </c>
       <c r="R141" t="n">
-        <v>7052179</v>
+        <v>7052375</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -17804,7 +17804,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -17814,12 +17814,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>13:39</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>Rikligt på gammal levande gran i gammal granskog</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -17834,19 +17829,19 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>134165139</v>
+        <v>134166744</v>
       </c>
       <c r="B142" t="n">
         <v>79358</v>
@@ -17876,7 +17871,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -17890,10 +17885,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>460690</v>
+        <v>460779</v>
       </c>
       <c r="R142" t="n">
-        <v>7052375</v>
+        <v>7052179</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -17925,7 +17920,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -17935,7 +17930,12 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>Rikligt på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -17950,12 +17950,12 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
@@ -18069,57 +18069,48 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>134163868</v>
+        <v>134165713</v>
       </c>
       <c r="B144" t="n">
-        <v>79358</v>
+        <v>80478</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>460752</v>
+        <v>460711</v>
       </c>
       <c r="R144" t="n">
-        <v>7052276</v>
+        <v>7052457</v>
       </c>
       <c r="S144" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -18148,7 +18139,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -18158,12 +18149,12 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>Rikligt på gammal levande grov gran (45 cm dbh) i gammal granskog</t>
+          <t>På gammal rönn i gammal granskog</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -18190,10 +18181,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>134165713</v>
+        <v>134171966</v>
       </c>
       <c r="B145" t="n">
-        <v>80478</v>
+        <v>80429</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -18201,37 +18192,37 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6462</v>
+        <v>229748</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>460711</v>
+        <v>460676</v>
       </c>
       <c r="R145" t="n">
-        <v>7052457</v>
+        <v>7051857</v>
       </c>
       <c r="S145" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -18260,7 +18251,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -18270,12 +18261,12 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>På gammal rönn i gammal granskog</t>
+          <t>På rönn i gammal granskog</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -18302,48 +18293,57 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>134171966</v>
+        <v>134163868</v>
       </c>
       <c r="B146" t="n">
-        <v>80429</v>
+        <v>79358</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>229748</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>460676</v>
+        <v>460752</v>
       </c>
       <c r="R146" t="n">
-        <v>7051857</v>
+        <v>7052276</v>
       </c>
       <c r="S146" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -18372,7 +18372,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -18382,12 +18382,12 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>På rönn i gammal granskog</t>
+          <t>Rikligt på gammal levande grov gran (45 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -18414,10 +18414,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>134171965</v>
+        <v>134171976</v>
       </c>
       <c r="B147" t="n">
-        <v>106291</v>
+        <v>99200</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -18425,21 +18425,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>221725</v>
+        <v>221952</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -18449,13 +18449,13 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>460691</v>
+        <v>460751</v>
       </c>
       <c r="R147" t="n">
-        <v>7051813</v>
+        <v>7051437</v>
       </c>
       <c r="S147" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -18484,7 +18484,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -18494,12 +18494,12 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På marken i äldre granskog</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -18526,10 +18526,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>134166104</v>
+        <v>134171965</v>
       </c>
       <c r="B148" t="n">
-        <v>99200</v>
+        <v>106291</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -18537,37 +18537,37 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>221952</v>
+        <v>221725</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>460692</v>
+        <v>460691</v>
       </c>
       <c r="R148" t="n">
-        <v>7052457</v>
+        <v>7051813</v>
       </c>
       <c r="S148" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -18596,7 +18596,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -18606,7 +18606,12 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -18621,19 +18626,19 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>134171976</v>
+        <v>134158853</v>
       </c>
       <c r="B149" t="n">
         <v>99200</v>
@@ -18664,14 +18669,14 @@
       <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>460751</v>
+        <v>460723</v>
       </c>
       <c r="R149" t="n">
-        <v>7051437</v>
+        <v>7051736</v>
       </c>
       <c r="S149" t="n">
         <v>3</v>
@@ -18703,7 +18708,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -18713,12 +18718,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="AC149" t="inlineStr">
-        <is>
-          <t>På marken i äldre granskog</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -18733,19 +18733,19 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>134158853</v>
+        <v>134166104</v>
       </c>
       <c r="B150" t="n">
         <v>99200</v>
@@ -18776,17 +18776,17 @@
       <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>460723</v>
+        <v>460692</v>
       </c>
       <c r="R150" t="n">
-        <v>7051736</v>
+        <v>7052457</v>
       </c>
       <c r="S150" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -18815,7 +18815,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -18825,7 +18825,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -18852,48 +18852,48 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>134171956</v>
+        <v>134161209</v>
       </c>
       <c r="B151" t="n">
-        <v>79358</v>
+        <v>91920</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>460688</v>
+        <v>460668</v>
       </c>
       <c r="R151" t="n">
-        <v>7052421</v>
+        <v>7051920</v>
       </c>
       <c r="S151" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -18922,7 +18922,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -18932,7 +18932,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -18947,44 +18947,44 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>134171946</v>
+        <v>134171956</v>
       </c>
       <c r="B152" t="n">
-        <v>80478</v>
+        <v>79358</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -18994,10 +18994,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>460716</v>
+        <v>460688</v>
       </c>
       <c r="R152" t="n">
-        <v>7052447</v>
+        <v>7052421</v>
       </c>
       <c r="S152" t="n">
         <v>3</v>
@@ -19029,7 +19029,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -19039,12 +19039,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC152" t="inlineStr">
-        <is>
-          <t>På rönnlåga i gammal granskog</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -19071,10 +19066,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>134171970</v>
+        <v>134171946</v>
       </c>
       <c r="B153" t="n">
-        <v>101386</v>
+        <v>80478</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -19082,21 +19077,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>222498</v>
+        <v>6462</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -19106,10 +19101,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>460688</v>
+        <v>460716</v>
       </c>
       <c r="R153" t="n">
-        <v>7051821</v>
+        <v>7052447</v>
       </c>
       <c r="S153" t="n">
         <v>3</v>
@@ -19141,7 +19136,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -19151,12 +19146,12 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>På marken i gammal fuktig granskog</t>
+          <t>På rönnlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -19183,7 +19178,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>134161529</v>
+        <v>134162816</v>
       </c>
       <c r="B154" t="n">
         <v>79358</v>
@@ -19223,17 +19218,17 @@
       </c>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>460757</v>
+        <v>460812</v>
       </c>
       <c r="R154" t="n">
-        <v>7051937</v>
+        <v>7052078</v>
       </c>
       <c r="S154" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -19262,7 +19257,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -19272,12 +19267,12 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AC154" t="inlineStr">
         <is>
-          <t>Fördelat på 3 gamla granar</t>
+          <t>Gammal död gran (ca 23 cm dbh) draperad med garnlav i gammal gles granskog</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -19292,22 +19287,22 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>134161209</v>
+        <v>134171970</v>
       </c>
       <c r="B155" t="n">
-        <v>91920</v>
+        <v>101386</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -19315,37 +19310,37 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>460668</v>
+        <v>460688</v>
       </c>
       <c r="R155" t="n">
-        <v>7051920</v>
+        <v>7051821</v>
       </c>
       <c r="S155" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -19374,7 +19369,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -19384,7 +19379,12 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>På marken i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -19399,12 +19399,12 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
@@ -19532,7 +19532,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>134162816</v>
+        <v>134161529</v>
       </c>
       <c r="B157" t="n">
         <v>79358</v>
@@ -19572,17 +19572,17 @@
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>460812</v>
+        <v>460757</v>
       </c>
       <c r="R157" t="n">
-        <v>7052078</v>
+        <v>7051937</v>
       </c>
       <c r="S157" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -19611,7 +19611,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -19621,12 +19621,12 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AC157" t="inlineStr">
         <is>
-          <t>Gammal död gran (ca 23 cm dbh) draperad med garnlav i gammal gles granskog</t>
+          <t>Fördelat på 3 gamla granar</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -19641,12 +19641,12 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
@@ -19993,10 +19993,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>134171952</v>
+        <v>134160980</v>
       </c>
       <c r="B161" t="n">
-        <v>79358</v>
+        <v>83343</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -20004,37 +20004,37 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>460688</v>
+        <v>460672</v>
       </c>
       <c r="R161" t="n">
-        <v>7052420</v>
+        <v>7051901</v>
       </c>
       <c r="S161" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -20063,7 +20063,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -20073,7 +20073,12 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -20088,60 +20093,60 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>134171954</v>
+        <v>134165091</v>
       </c>
       <c r="B162" t="n">
-        <v>79358</v>
+        <v>91920</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>460686</v>
+        <v>460690</v>
       </c>
       <c r="R162" t="n">
-        <v>7052421</v>
+        <v>7052375</v>
       </c>
       <c r="S162" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -20170,7 +20175,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -20180,7 +20185,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -20195,22 +20200,22 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>134160980</v>
+        <v>134171952</v>
       </c>
       <c r="B163" t="n">
-        <v>83343</v>
+        <v>79358</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -20218,37 +20223,37 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>460672</v>
+        <v>460688</v>
       </c>
       <c r="R163" t="n">
-        <v>7051901</v>
+        <v>7052420</v>
       </c>
       <c r="S163" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -20277,7 +20282,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -20287,12 +20292,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC163" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -20307,60 +20307,60 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>134165091</v>
+        <v>134171954</v>
       </c>
       <c r="B164" t="n">
-        <v>91920</v>
+        <v>79358</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>460690</v>
+        <v>460686</v>
       </c>
       <c r="R164" t="n">
-        <v>7052375</v>
+        <v>7052421</v>
       </c>
       <c r="S164" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -20389,7 +20389,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -20399,7 +20399,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -20414,12 +20414,12 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
@@ -20542,32 +20542,32 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>134171957</v>
+        <v>134171967</v>
       </c>
       <c r="B166" t="n">
-        <v>79358</v>
+        <v>80478</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -20577,13 +20577,13 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>460698</v>
+        <v>460677</v>
       </c>
       <c r="R166" t="n">
-        <v>7052420</v>
+        <v>7051857</v>
       </c>
       <c r="S166" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -20612,7 +20612,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -20622,7 +20622,12 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>09:16</t>
+        </is>
+      </c>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t>På gammal levande rönn i gammal granskog</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -20649,32 +20654,32 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>134171967</v>
+        <v>134171957</v>
       </c>
       <c r="B167" t="n">
-        <v>80478</v>
+        <v>79358</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -20684,13 +20689,13 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>460677</v>
+        <v>460698</v>
       </c>
       <c r="R167" t="n">
-        <v>7051857</v>
+        <v>7052420</v>
       </c>
       <c r="S167" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -20719,7 +20724,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -20729,12 +20734,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>09:16</t>
-        </is>
-      </c>
-      <c r="AC167" t="inlineStr">
-        <is>
-          <t>På gammal levande rönn i gammal granskog</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -20868,10 +20868,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>134163852</v>
+        <v>134171955</v>
       </c>
       <c r="B169" t="n">
-        <v>57975</v>
+        <v>79358</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -20879,42 +20879,37 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
-      <c r="M169" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>460763</v>
+        <v>460685</v>
       </c>
       <c r="R169" t="n">
-        <v>7052266</v>
+        <v>7052421</v>
       </c>
       <c r="S169" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -20943,7 +20938,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -20953,12 +20948,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>11:49</t>
-        </is>
-      </c>
-      <c r="AC169" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -20973,12 +20963,12 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
@@ -21092,10 +21082,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>134171955</v>
+        <v>134163852</v>
       </c>
       <c r="B171" t="n">
-        <v>79358</v>
+        <v>57975</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -21103,37 +21093,42 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>460685</v>
+        <v>460763</v>
       </c>
       <c r="R171" t="n">
-        <v>7052421</v>
+        <v>7052266</v>
       </c>
       <c r="S171" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -21162,7 +21157,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -21172,7 +21167,12 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AC171" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -21187,60 +21187,60 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>134171974</v>
+        <v>134164951</v>
       </c>
       <c r="B172" t="n">
-        <v>79977</v>
+        <v>96406</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6453</v>
+        <v>2810</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>460722</v>
+        <v>460763</v>
       </c>
       <c r="R172" t="n">
-        <v>7051751</v>
+        <v>7052266</v>
       </c>
       <c r="S172" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -21269,7 +21269,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -21279,12 +21279,12 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AC172" t="inlineStr">
         <is>
-          <t>På dimensionsavverkningsstubbe av tall i gammal garnlavsrik granskog</t>
+          <t>På block i kanten av lok</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -21299,60 +21299,60 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>134164951</v>
+        <v>134171974</v>
       </c>
       <c r="B173" t="n">
-        <v>96406</v>
+        <v>79977</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>2810</v>
+        <v>6453</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>460763</v>
+        <v>460722</v>
       </c>
       <c r="R173" t="n">
-        <v>7052266</v>
+        <v>7051751</v>
       </c>
       <c r="S173" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -21381,7 +21381,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -21391,12 +21391,12 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AC173" t="inlineStr">
         <is>
-          <t>På block i kanten av lok</t>
+          <t>På dimensionsavverkningsstubbe av tall i gammal garnlavsrik granskog</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -21411,65 +21411,57 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>134171973</v>
+        <v>134163087</v>
       </c>
       <c r="B174" t="n">
-        <v>57162</v>
+        <v>89338</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>100138</v>
+        <v>510</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K174" t="inlineStr"/>
-      <c r="L174" t="inlineStr"/>
-      <c r="M174" t="inlineStr"/>
-      <c r="N174" t="inlineStr"/>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>460716</v>
+        <v>460736</v>
       </c>
       <c r="R174" t="n">
-        <v>7051811</v>
+        <v>7052124</v>
       </c>
       <c r="S174" t="n">
         <v>3</v>
@@ -21501,7 +21493,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -21511,12 +21503,12 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AC174" t="inlineStr">
         <is>
-          <t>1 ex uppflog</t>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -21531,19 +21523,19 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>134161522</v>
+        <v>134160600</v>
       </c>
       <c r="B175" t="n">
         <v>79358</v>
@@ -21573,7 +21565,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>400</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -21587,13 +21579,13 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>460702</v>
+        <v>460703</v>
       </c>
       <c r="R175" t="n">
-        <v>7051854</v>
+        <v>7051878</v>
       </c>
       <c r="S175" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T175" t="inlineStr">
         <is>
@@ -21622,7 +21614,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -21632,12 +21624,12 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AC175" t="inlineStr">
         <is>
-          <t>Rikligt, draperat, på de flesta granar i gammal flerskiktad granskog</t>
+          <t>På grov gammal gran</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -21652,12 +21644,12 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
@@ -21775,57 +21767,56 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>134160600</v>
+        <v>134171973</v>
       </c>
       <c r="B177" t="n">
-        <v>79358</v>
+        <v>57162</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="J177" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr"/>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" t="inlineStr"/>
+      <c r="N177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>460703</v>
+        <v>460716</v>
       </c>
       <c r="R177" t="n">
-        <v>7051878</v>
+        <v>7051811</v>
       </c>
       <c r="S177" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -21854,7 +21845,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -21864,12 +21855,12 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AC177" t="inlineStr">
         <is>
-          <t>På grov gammal gran</t>
+          <t>1 ex uppflog</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -21884,22 +21875,22 @@
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>134163087</v>
+        <v>134161522</v>
       </c>
       <c r="B178" t="n">
-        <v>89338</v>
+        <v>79358</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -21907,37 +21898,46 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P178" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>460736</v>
+        <v>460702</v>
       </c>
       <c r="R178" t="n">
-        <v>7052124</v>
+        <v>7051854</v>
       </c>
       <c r="S178" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
@@ -21966,7 +21966,7 @@
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -21976,12 +21976,12 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AC178" t="inlineStr">
         <is>
-          <t>På gammal granlåga</t>
+          <t>Rikligt, draperat, på de flesta granar i gammal flerskiktad granskog</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -21996,12 +21996,12 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
@@ -22805,10 +22805,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>134163114</v>
+        <v>134161962</v>
       </c>
       <c r="B186" t="n">
-        <v>57975</v>
+        <v>83207</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -22816,39 +22816,34 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
-      <c r="M186" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P186" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>460736</v>
+        <v>460653</v>
       </c>
       <c r="R186" t="n">
-        <v>7052124</v>
+        <v>7051927</v>
       </c>
       <c r="S186" t="n">
         <v>4</v>
@@ -22880,7 +22875,7 @@
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
@@ -22890,12 +22885,12 @@
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AC186" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -22922,10 +22917,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>134161962</v>
+        <v>134163114</v>
       </c>
       <c r="B187" t="n">
-        <v>83207</v>
+        <v>57975</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -22933,34 +22928,39 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P187" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>460653</v>
+        <v>460736</v>
       </c>
       <c r="R187" t="n">
-        <v>7051927</v>
+        <v>7052124</v>
       </c>
       <c r="S187" t="n">
         <v>4</v>
@@ -22992,7 +22992,7 @@
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
@@ -23002,12 +23002,12 @@
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AC187" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -23034,48 +23034,48 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>134171972</v>
+        <v>134164962</v>
       </c>
       <c r="B188" t="n">
-        <v>79358</v>
+        <v>96396</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>460714</v>
+        <v>460763</v>
       </c>
       <c r="R188" t="n">
-        <v>7051804</v>
+        <v>7052266</v>
       </c>
       <c r="S188" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -23104,7 +23104,7 @@
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
@@ -23114,12 +23114,12 @@
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AC188" t="inlineStr">
         <is>
-          <t>1000 ex fördelat på 10 granar i gammal garnlavsrik granskog</t>
+          <t>På block i kanten av lok</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -23134,60 +23134,60 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>134164962</v>
+        <v>134171972</v>
       </c>
       <c r="B189" t="n">
-        <v>96396</v>
+        <v>79358</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>460763</v>
+        <v>460714</v>
       </c>
       <c r="R189" t="n">
-        <v>7052266</v>
+        <v>7051804</v>
       </c>
       <c r="S189" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -23216,7 +23216,7 @@
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
@@ -23226,12 +23226,12 @@
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AC189" t="inlineStr">
         <is>
-          <t>På block i kanten av lok</t>
+          <t>1000 ex fördelat på 10 granar i gammal garnlavsrik granskog</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -23246,19 +23246,19 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>134161368</v>
+        <v>134171958</v>
       </c>
       <c r="B190" t="n">
         <v>79358</v>
@@ -23286,29 +23286,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J190" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>460664</v>
+        <v>460696</v>
       </c>
       <c r="R190" t="n">
-        <v>7051927</v>
+        <v>7052420</v>
       </c>
       <c r="S190" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -23337,7 +23328,7 @@
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
@@ -23347,12 +23338,7 @@
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>10:19</t>
-        </is>
-      </c>
-      <c r="AC190" t="inlineStr">
-        <is>
-          <t>På grov gammal gran</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -23367,12 +23353,12 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
@@ -23491,7 +23477,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>134162546</v>
+        <v>134161368</v>
       </c>
       <c r="B192" t="n">
         <v>79358</v>
@@ -23521,7 +23507,7 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -23535,13 +23521,13 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>460804</v>
+        <v>460664</v>
       </c>
       <c r="R192" t="n">
-        <v>7052009</v>
+        <v>7051927</v>
       </c>
       <c r="S192" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -23570,7 +23556,7 @@
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -23580,12 +23566,12 @@
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AC192" t="inlineStr">
         <is>
-          <t>Fördelat på 5 gamla granar</t>
+          <t>På grov gammal gran</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -23605,14 +23591,14 @@
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>134171958</v>
+        <v>134162546</v>
       </c>
       <c r="B193" t="n">
         <v>79358</v>
@@ -23640,20 +23626,29 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I193" t="inlineStr"/>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>460696</v>
+        <v>460804</v>
       </c>
       <c r="R193" t="n">
-        <v>7052420</v>
+        <v>7052009</v>
       </c>
       <c r="S193" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -23682,7 +23677,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -23692,7 +23687,12 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AC193" t="inlineStr">
+        <is>
+          <t>Fördelat på 5 gamla granar</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -23707,19 +23707,19 @@
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>134162379</v>
+        <v>134160932</v>
       </c>
       <c r="B194" t="n">
         <v>79358</v>
@@ -23749,7 +23749,7 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>400</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -23759,17 +23759,17 @@
       </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>460792</v>
+        <v>460672</v>
       </c>
       <c r="R194" t="n">
-        <v>7052051</v>
+        <v>7051901</v>
       </c>
       <c r="S194" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -23798,7 +23798,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -23808,12 +23808,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>10:58</t>
-        </is>
-      </c>
-      <c r="AC194" t="inlineStr">
-        <is>
-          <t>På gammal död gran (25 cm dbh) i gammal granskog</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -23828,22 +23823,22 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>134166396</v>
+        <v>134162379</v>
       </c>
       <c r="B195" t="n">
-        <v>57975</v>
+        <v>79358</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -23851,39 +23846,43 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I195" t="inlineStr"/>
-      <c r="M195" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>460693</v>
+        <v>460792</v>
       </c>
       <c r="R195" t="n">
-        <v>7052473</v>
+        <v>7052051</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -23915,7 +23914,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -23925,12 +23924,12 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AC195" t="inlineStr">
         <is>
-          <t>Ringhack på gammal levande gran i gammal granskog</t>
+          <t>På gammal död gran (25 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -24078,10 +24077,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>134160932</v>
+        <v>134166396</v>
       </c>
       <c r="B197" t="n">
-        <v>79358</v>
+        <v>57975</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -24089,46 +24088,42 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="J197" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr"/>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>460672</v>
+        <v>460693</v>
       </c>
       <c r="R197" t="n">
-        <v>7051901</v>
+        <v>7052473</v>
       </c>
       <c r="S197" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T197" t="inlineStr">
         <is>
@@ -24157,7 +24152,7 @@
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -24167,7 +24162,12 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AC197" t="inlineStr">
+        <is>
+          <t>Ringhack på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -24182,12 +24182,12 @@
       <c r="AT197" t="inlineStr"/>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
@@ -24304,6 +24304,2589 @@
       </c>
       <c r="AY198" t="inlineStr"/>
     </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>134187980</v>
+      </c>
+      <c r="B199" t="n">
+        <v>79358</v>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E199" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr"/>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q199" t="n">
+        <v>460749</v>
+      </c>
+      <c r="R199" t="n">
+        <v>7052313</v>
+      </c>
+      <c r="S199" t="n">
+        <v>10</v>
+      </c>
+      <c r="T199" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V199" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W199" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y199" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z199" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB199" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AD199" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE199" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG199" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT199" t="inlineStr"/>
+      <c r="AW199" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX199" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>134188076</v>
+      </c>
+      <c r="B200" t="n">
+        <v>79358</v>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E200" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr"/>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q200" t="n">
+        <v>460747</v>
+      </c>
+      <c r="R200" t="n">
+        <v>7052190</v>
+      </c>
+      <c r="S200" t="n">
+        <v>10</v>
+      </c>
+      <c r="T200" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V200" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W200" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y200" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z200" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB200" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AD200" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE200" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG200" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT200" t="inlineStr"/>
+      <c r="AW200" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX200" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>134190545</v>
+      </c>
+      <c r="B201" t="n">
+        <v>79358</v>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E201" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q201" t="n">
+        <v>460801</v>
+      </c>
+      <c r="R201" t="n">
+        <v>7052035</v>
+      </c>
+      <c r="S201" t="n">
+        <v>10</v>
+      </c>
+      <c r="T201" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V201" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W201" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y201" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z201" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB201" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AC201" t="inlineStr">
+        <is>
+          <t>På gammal gran i garnlavsrik granskog</t>
+        </is>
+      </c>
+      <c r="AD201" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE201" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG201" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT201" t="inlineStr"/>
+      <c r="AW201" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX201" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>134188832</v>
+      </c>
+      <c r="B202" t="n">
+        <v>79358</v>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E202" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q202" t="n">
+        <v>460787</v>
+      </c>
+      <c r="R202" t="n">
+        <v>7052035</v>
+      </c>
+      <c r="S202" t="n">
+        <v>10</v>
+      </c>
+      <c r="T202" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V202" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W202" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y202" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z202" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB202" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AD202" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE202" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG202" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT202" t="inlineStr"/>
+      <c r="AW202" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX202" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>134187405</v>
+      </c>
+      <c r="B203" t="n">
+        <v>79358</v>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E203" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q203" t="n">
+        <v>460801</v>
+      </c>
+      <c r="R203" t="n">
+        <v>7052065</v>
+      </c>
+      <c r="S203" t="n">
+        <v>10</v>
+      </c>
+      <c r="T203" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V203" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W203" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y203" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z203" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB203" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AC203" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD203" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE203" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG203" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT203" t="inlineStr"/>
+      <c r="AW203" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX203" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>134187568</v>
+      </c>
+      <c r="B204" t="n">
+        <v>79358</v>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E204" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q204" t="n">
+        <v>460775</v>
+      </c>
+      <c r="R204" t="n">
+        <v>7052220</v>
+      </c>
+      <c r="S204" t="n">
+        <v>10</v>
+      </c>
+      <c r="T204" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V204" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W204" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y204" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z204" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB204" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AC204" t="inlineStr">
+        <is>
+          <t>Rikligt, draperar granarna</t>
+        </is>
+      </c>
+      <c r="AD204" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE204" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG204" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT204" t="inlineStr"/>
+      <c r="AW204" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX204" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>134187643</v>
+      </c>
+      <c r="B205" t="n">
+        <v>79358</v>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E205" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr"/>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q205" t="n">
+        <v>460736</v>
+      </c>
+      <c r="R205" t="n">
+        <v>7052375</v>
+      </c>
+      <c r="S205" t="n">
+        <v>10</v>
+      </c>
+      <c r="T205" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V205" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W205" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y205" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z205" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB205" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AC205" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
+        </is>
+      </c>
+      <c r="AD205" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE205" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG205" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT205" t="inlineStr"/>
+      <c r="AW205" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX205" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>134190856</v>
+      </c>
+      <c r="B206" t="n">
+        <v>79358</v>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E206" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr"/>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q206" t="n">
+        <v>460702</v>
+      </c>
+      <c r="R206" t="n">
+        <v>7051850</v>
+      </c>
+      <c r="S206" t="n">
+        <v>10</v>
+      </c>
+      <c r="T206" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V206" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W206" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y206" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z206" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB206" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AD206" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE206" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG206" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT206" t="inlineStr"/>
+      <c r="AW206" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX206" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>134187781</v>
+      </c>
+      <c r="B207" t="n">
+        <v>79358</v>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E207" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr"/>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q207" t="n">
+        <v>460723</v>
+      </c>
+      <c r="R207" t="n">
+        <v>7052438</v>
+      </c>
+      <c r="S207" t="n">
+        <v>10</v>
+      </c>
+      <c r="T207" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V207" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W207" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y207" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z207" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB207" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC207" t="inlineStr">
+        <is>
+          <t>På grov gammal gran</t>
+        </is>
+      </c>
+      <c r="AD207" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE207" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG207" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT207" t="inlineStr"/>
+      <c r="AW207" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX207" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>134187721</v>
+      </c>
+      <c r="B208" t="n">
+        <v>79358</v>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E208" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr"/>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q208" t="n">
+        <v>460681</v>
+      </c>
+      <c r="R208" t="n">
+        <v>7052407</v>
+      </c>
+      <c r="S208" t="n">
+        <v>10</v>
+      </c>
+      <c r="T208" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V208" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W208" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y208" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z208" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB208" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AC208" t="inlineStr">
+        <is>
+          <t>På grov gammal gran</t>
+        </is>
+      </c>
+      <c r="AD208" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE208" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG208" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT208" t="inlineStr"/>
+      <c r="AW208" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX208" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>134187880</v>
+      </c>
+      <c r="B209" t="n">
+        <v>79358</v>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E209" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr"/>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q209" t="n">
+        <v>460681</v>
+      </c>
+      <c r="R209" t="n">
+        <v>7052376</v>
+      </c>
+      <c r="S209" t="n">
+        <v>10</v>
+      </c>
+      <c r="T209" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V209" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W209" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y209" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z209" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB209" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AD209" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE209" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG209" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT209" t="inlineStr"/>
+      <c r="AW209" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX209" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>134187536</v>
+      </c>
+      <c r="B210" t="n">
+        <v>79358</v>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E210" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr"/>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q210" t="n">
+        <v>460775</v>
+      </c>
+      <c r="R210" t="n">
+        <v>7052159</v>
+      </c>
+      <c r="S210" t="n">
+        <v>10</v>
+      </c>
+      <c r="T210" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U210" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V210" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W210" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y210" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z210" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB210" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC210" t="inlineStr">
+        <is>
+          <t>På gammal gran, 170-200 år, i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD210" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE210" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG210" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT210" t="inlineStr"/>
+      <c r="AW210" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX210" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>134190717</v>
+      </c>
+      <c r="B211" t="n">
+        <v>79358</v>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E211" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr"/>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q211" t="n">
+        <v>460688</v>
+      </c>
+      <c r="R211" t="n">
+        <v>7051819</v>
+      </c>
+      <c r="S211" t="n">
+        <v>10</v>
+      </c>
+      <c r="T211" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V211" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W211" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y211" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z211" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB211" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AD211" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE211" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG211" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT211" t="inlineStr"/>
+      <c r="AW211" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX211" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>134190455</v>
+      </c>
+      <c r="B212" t="n">
+        <v>79358</v>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E212" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q212" t="n">
+        <v>460787</v>
+      </c>
+      <c r="R212" t="n">
+        <v>7052065</v>
+      </c>
+      <c r="S212" t="n">
+        <v>20</v>
+      </c>
+      <c r="T212" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V212" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W212" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y212" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z212" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB212" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AC212" t="inlineStr">
+        <is>
+          <t>Rikligt på gamla granar</t>
+        </is>
+      </c>
+      <c r="AD212" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE212" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG212" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT212" t="inlineStr"/>
+      <c r="AW212" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX212" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>134190579</v>
+      </c>
+      <c r="B213" t="n">
+        <v>79358</v>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E213" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr"/>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q213" t="n">
+        <v>460635</v>
+      </c>
+      <c r="R213" t="n">
+        <v>7052005</v>
+      </c>
+      <c r="S213" t="n">
+        <v>10</v>
+      </c>
+      <c r="T213" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V213" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W213" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y213" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z213" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB213" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AD213" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE213" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG213" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT213" t="inlineStr"/>
+      <c r="AW213" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX213" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>134190569</v>
+      </c>
+      <c r="B214" t="n">
+        <v>79358</v>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E214" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q214" t="n">
+        <v>460773</v>
+      </c>
+      <c r="R214" t="n">
+        <v>7052035</v>
+      </c>
+      <c r="S214" t="n">
+        <v>10</v>
+      </c>
+      <c r="T214" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U214" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V214" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W214" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y214" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z214" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB214" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AD214" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE214" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG214" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT214" t="inlineStr"/>
+      <c r="AW214" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX214" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>134190741</v>
+      </c>
+      <c r="B215" t="n">
+        <v>79358</v>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E215" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q215" t="n">
+        <v>460702</v>
+      </c>
+      <c r="R215" t="n">
+        <v>7051819</v>
+      </c>
+      <c r="S215" t="n">
+        <v>10</v>
+      </c>
+      <c r="T215" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U215" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V215" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W215" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y215" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z215" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB215" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AD215" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE215" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG215" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT215" t="inlineStr"/>
+      <c r="AW215" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX215" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>134188004</v>
+      </c>
+      <c r="B216" t="n">
+        <v>79358</v>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E216" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr"/>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q216" t="n">
+        <v>460734</v>
+      </c>
+      <c r="R216" t="n">
+        <v>7052252</v>
+      </c>
+      <c r="S216" t="n">
+        <v>10</v>
+      </c>
+      <c r="T216" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U216" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V216" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W216" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y216" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z216" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB216" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AD216" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE216" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG216" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT216" t="inlineStr"/>
+      <c r="AW216" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX216" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>134188053</v>
+      </c>
+      <c r="B217" t="n">
+        <v>79358</v>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E217" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr"/>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q217" t="n">
+        <v>460762</v>
+      </c>
+      <c r="R217" t="n">
+        <v>7052283</v>
+      </c>
+      <c r="S217" t="n">
+        <v>10</v>
+      </c>
+      <c r="T217" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U217" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V217" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W217" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y217" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z217" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB217" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AD217" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE217" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG217" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT217" t="inlineStr"/>
+      <c r="AW217" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX217" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY217" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>134187660</v>
+      </c>
+      <c r="B218" t="n">
+        <v>79358</v>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E218" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr"/>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q218" t="n">
+        <v>460682</v>
+      </c>
+      <c r="R218" t="n">
+        <v>7052469</v>
+      </c>
+      <c r="S218" t="n">
+        <v>10</v>
+      </c>
+      <c r="T218" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U218" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V218" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W218" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y218" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z218" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB218" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AC218" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD218" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE218" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG218" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT218" t="inlineStr"/>
+      <c r="AW218" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX218" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY218" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>134188655</v>
+      </c>
+      <c r="B219" t="n">
+        <v>79358</v>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E219" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q219" t="n">
+        <v>460788</v>
+      </c>
+      <c r="R219" t="n">
+        <v>7052097</v>
+      </c>
+      <c r="S219" t="n">
+        <v>10</v>
+      </c>
+      <c r="T219" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U219" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V219" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W219" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y219" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z219" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AA219" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB219" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AC219" t="inlineStr">
+        <is>
+          <t>Rikligt på gammal gran</t>
+        </is>
+      </c>
+      <c r="AD219" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE219" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG219" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT219" t="inlineStr"/>
+      <c r="AW219" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX219" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>134189045</v>
+      </c>
+      <c r="B220" t="n">
+        <v>79358</v>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E220" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr"/>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q220" t="n">
+        <v>460760</v>
+      </c>
+      <c r="R220" t="n">
+        <v>7052066</v>
+      </c>
+      <c r="S220" t="n">
+        <v>10</v>
+      </c>
+      <c r="T220" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V220" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W220" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y220" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z220" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB220" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AD220" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE220" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG220" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT220" t="inlineStr"/>
+      <c r="AW220" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX220" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>134187869</v>
+      </c>
+      <c r="B221" t="n">
+        <v>79358</v>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E221" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr"/>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q221" t="n">
+        <v>460627</v>
+      </c>
+      <c r="R221" t="n">
+        <v>7052439</v>
+      </c>
+      <c r="S221" t="n">
+        <v>20</v>
+      </c>
+      <c r="T221" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V221" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W221" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y221" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z221" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB221" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AD221" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE221" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG221" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT221" t="inlineStr"/>
+      <c r="AW221" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX221" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY221" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51504-2025 artfynd.xlsx
+++ b/artfynd/A 51504-2025 artfynd.xlsx
@@ -16020,7 +16020,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>134161617</v>
+        <v>134159342</v>
       </c>
       <c r="B126" t="n">
         <v>79358</v>
@@ -16050,7 +16050,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -16058,24 +16058,19 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>460738</v>
+        <v>460672</v>
       </c>
       <c r="R126" t="n">
-        <v>7051903</v>
+        <v>7051847</v>
       </c>
       <c r="S126" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -16104,7 +16099,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -16114,12 +16109,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>10:35</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>Fördelat på 2 gamla granar</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -16139,64 +16129,55 @@
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>134159342</v>
+        <v>134171971</v>
       </c>
       <c r="B127" t="n">
-        <v>79358</v>
+        <v>96396</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>460672</v>
+        <v>460688</v>
       </c>
       <c r="R127" t="n">
-        <v>7051847</v>
+        <v>7051821</v>
       </c>
       <c r="S127" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -16225,7 +16206,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -16235,7 +16216,12 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:04</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>På marken i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -16250,60 +16236,74 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>134171971</v>
+        <v>134161617</v>
       </c>
       <c r="B128" t="n">
-        <v>96396</v>
+        <v>79358</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>460688</v>
+        <v>460738</v>
       </c>
       <c r="R128" t="n">
-        <v>7051821</v>
+        <v>7051903</v>
       </c>
       <c r="S128" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -16332,7 +16332,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -16342,12 +16342,12 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>På marken i gammal fuktig granskog</t>
+          <t>Fördelat på 2 gamla granar</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -16362,22 +16362,22 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>134159098</v>
+        <v>134161325</v>
       </c>
       <c r="B129" t="n">
-        <v>80429</v>
+        <v>99200</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -16385,21 +16385,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>229748</v>
+        <v>221952</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -16409,10 +16409,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>460718</v>
+        <v>460664</v>
       </c>
       <c r="R129" t="n">
-        <v>7051777</v>
+        <v>7051927</v>
       </c>
       <c r="S129" t="n">
         <v>5</v>
@@ -16444,7 +16444,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -16454,12 +16454,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>09:08</t>
-        </is>
-      </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>På död, klen rönn</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -16479,69 +16474,55 @@
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>134165576</v>
+        <v>134165125</v>
       </c>
       <c r="B130" t="n">
-        <v>57975</v>
+        <v>99200</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L130" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>460650</v>
+        <v>460690</v>
       </c>
       <c r="R130" t="n">
-        <v>7052431</v>
+        <v>7052375</v>
       </c>
       <c r="S130" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -16570,7 +16551,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -16580,7 +16561,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -16607,48 +16588,62 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>134161325</v>
+        <v>134165576</v>
       </c>
       <c r="B131" t="n">
-        <v>99200</v>
+        <v>57975</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>460664</v>
+        <v>460650</v>
       </c>
       <c r="R131" t="n">
-        <v>7051927</v>
+        <v>7052431</v>
       </c>
       <c r="S131" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -16677,7 +16672,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -16687,7 +16682,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -16707,55 +16702,64 @@
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>134165125</v>
+        <v>134162895</v>
       </c>
       <c r="B132" t="n">
-        <v>99200</v>
+        <v>79358</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>460690</v>
+        <v>460789</v>
       </c>
       <c r="R132" t="n">
-        <v>7052375</v>
+        <v>7051975</v>
       </c>
       <c r="S132" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -16784,7 +16788,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -16794,7 +16798,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -16821,57 +16825,53 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>134162895</v>
+        <v>134165432</v>
       </c>
       <c r="B133" t="n">
-        <v>79358</v>
+        <v>79790</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>1778</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällig knopplav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Biatora fallax</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>Hepp</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>460789</v>
+        <v>460673</v>
       </c>
       <c r="R133" t="n">
-        <v>7051975</v>
+        <v>7052450</v>
       </c>
       <c r="S133" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -16900,7 +16900,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -16910,7 +16910,12 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>På bark vid basen av gammal levande grov gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -16925,50 +16930,54 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>134165432</v>
+        <v>134166248</v>
       </c>
       <c r="B134" t="n">
-        <v>79790</v>
+        <v>79358</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1778</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Fjällig knopplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Biatora fallax</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Hepp</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr"/>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
@@ -16977,10 +16986,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>460673</v>
+        <v>460708</v>
       </c>
       <c r="R134" t="n">
-        <v>7052450</v>
+        <v>7052503</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -17012,7 +17021,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -17022,12 +17031,12 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>På bark vid basen av gammal levande grov gran i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -17054,57 +17063,48 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>134166248</v>
+        <v>134159098</v>
       </c>
       <c r="B135" t="n">
-        <v>79358</v>
+        <v>80429</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>229748</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>460708</v>
+        <v>460718</v>
       </c>
       <c r="R135" t="n">
-        <v>7052503</v>
+        <v>7051777</v>
       </c>
       <c r="S135" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -17133,7 +17133,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -17143,12 +17143,12 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AC135" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På död, klen rönn</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -17163,22 +17163,22 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>134159178</v>
+        <v>134158960</v>
       </c>
       <c r="B136" t="n">
-        <v>80478</v>
+        <v>80477</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -17186,21 +17186,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6462</v>
+        <v>6461</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -17210,13 +17210,13 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>460683</v>
+        <v>460718</v>
       </c>
       <c r="R136" t="n">
-        <v>7051835</v>
+        <v>7051777</v>
       </c>
       <c r="S136" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -17245,7 +17245,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -17255,12 +17255,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>09:09</t>
-        </is>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>På död, klen rönn</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -17287,10 +17282,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>134158960</v>
+        <v>134159178</v>
       </c>
       <c r="B137" t="n">
-        <v>80477</v>
+        <v>80478</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -17298,21 +17293,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6461</v>
+        <v>6462</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -17322,13 +17317,13 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>460718</v>
+        <v>460683</v>
       </c>
       <c r="R137" t="n">
-        <v>7051777</v>
+        <v>7051835</v>
       </c>
       <c r="S137" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -17357,7 +17352,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -17367,7 +17362,12 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>På död, klen rönn</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -18414,7 +18414,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>134171976</v>
+        <v>134158853</v>
       </c>
       <c r="B147" t="n">
         <v>99200</v>
@@ -18445,14 +18445,14 @@
       <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>460751</v>
+        <v>460723</v>
       </c>
       <c r="R147" t="n">
-        <v>7051437</v>
+        <v>7051736</v>
       </c>
       <c r="S147" t="n">
         <v>3</v>
@@ -18484,7 +18484,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -18494,12 +18494,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="AC147" t="inlineStr">
-        <is>
-          <t>På marken i äldre granskog</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -18514,22 +18509,22 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>134171965</v>
+        <v>134166104</v>
       </c>
       <c r="B148" t="n">
-        <v>106291</v>
+        <v>99200</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -18537,37 +18532,37 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>221725</v>
+        <v>221952</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>460691</v>
+        <v>460692</v>
       </c>
       <c r="R148" t="n">
-        <v>7051813</v>
+        <v>7052457</v>
       </c>
       <c r="S148" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -18596,7 +18591,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -18606,12 +18601,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>10:21</t>
-        </is>
-      </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>På marken i gammal granskog</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -18626,19 +18616,19 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>134158853</v>
+        <v>134171976</v>
       </c>
       <c r="B149" t="n">
         <v>99200</v>
@@ -18669,14 +18659,14 @@
       <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>460723</v>
+        <v>460751</v>
       </c>
       <c r="R149" t="n">
-        <v>7051736</v>
+        <v>7051437</v>
       </c>
       <c r="S149" t="n">
         <v>3</v>
@@ -18708,7 +18698,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -18718,7 +18708,12 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>På marken i äldre granskog</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -18733,22 +18728,22 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>134166104</v>
+        <v>134171965</v>
       </c>
       <c r="B150" t="n">
-        <v>99200</v>
+        <v>106292</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18756,37 +18751,37 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>221952</v>
+        <v>221725</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>460692</v>
+        <v>460691</v>
       </c>
       <c r="R150" t="n">
-        <v>7052457</v>
+        <v>7051813</v>
       </c>
       <c r="S150" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -18815,7 +18810,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -18825,7 +18820,12 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -18840,12 +18840,12 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
@@ -20868,45 +20868,45 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>134171955</v>
+        <v>134159322</v>
       </c>
       <c r="B169" t="n">
-        <v>79358</v>
+        <v>99200</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>460685</v>
+        <v>460672</v>
       </c>
       <c r="R169" t="n">
-        <v>7052421</v>
+        <v>7051847</v>
       </c>
       <c r="S169" t="n">
         <v>3</v>
@@ -20938,7 +20938,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -20948,7 +20948,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -20963,60 +20963,65 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>134159322</v>
+        <v>134163852</v>
       </c>
       <c r="B170" t="n">
-        <v>99200</v>
+        <v>57975</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>460672</v>
+        <v>460763</v>
       </c>
       <c r="R170" t="n">
-        <v>7051847</v>
+        <v>7052266</v>
       </c>
       <c r="S170" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -21045,7 +21050,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -21055,7 +21060,12 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -21082,10 +21092,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>134163852</v>
+        <v>134171955</v>
       </c>
       <c r="B171" t="n">
-        <v>57975</v>
+        <v>79358</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -21093,42 +21103,37 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>460763</v>
+        <v>460685</v>
       </c>
       <c r="R171" t="n">
-        <v>7052266</v>
+        <v>7052421</v>
       </c>
       <c r="S171" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -21157,7 +21162,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -21167,12 +21172,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>11:49</t>
-        </is>
-      </c>
-      <c r="AC171" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -21187,60 +21187,60 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>134164951</v>
+        <v>134171974</v>
       </c>
       <c r="B172" t="n">
-        <v>96406</v>
+        <v>79977</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>2810</v>
+        <v>6453</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>460763</v>
+        <v>460722</v>
       </c>
       <c r="R172" t="n">
-        <v>7052266</v>
+        <v>7051751</v>
       </c>
       <c r="S172" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -21269,7 +21269,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -21279,12 +21279,12 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AC172" t="inlineStr">
         <is>
-          <t>På block i kanten av lok</t>
+          <t>På dimensionsavverkningsstubbe av tall i gammal garnlavsrik granskog</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -21299,60 +21299,60 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>134171974</v>
+        <v>134164951</v>
       </c>
       <c r="B173" t="n">
-        <v>79977</v>
+        <v>96406</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6453</v>
+        <v>2810</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>460722</v>
+        <v>460763</v>
       </c>
       <c r="R173" t="n">
-        <v>7051751</v>
+        <v>7052266</v>
       </c>
       <c r="S173" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -21381,7 +21381,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -21391,12 +21391,12 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AC173" t="inlineStr">
         <is>
-          <t>På dimensionsavverkningsstubbe av tall i gammal garnlavsrik granskog</t>
+          <t>På block i kanten av lok</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -21411,57 +21411,65 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>134163087</v>
+        <v>134171973</v>
       </c>
       <c r="B174" t="n">
-        <v>89338</v>
+        <v>57162</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>510</v>
+        <v>100138</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" t="inlineStr"/>
+      <c r="N174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>460736</v>
+        <v>460716</v>
       </c>
       <c r="R174" t="n">
-        <v>7052124</v>
+        <v>7051811</v>
       </c>
       <c r="S174" t="n">
         <v>3</v>
@@ -21493,7 +21501,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -21503,12 +21511,12 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AC174" t="inlineStr">
         <is>
-          <t>På gammal granlåga</t>
+          <t>1 ex uppflog</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -21523,19 +21531,19 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>134160600</v>
+        <v>134161522</v>
       </c>
       <c r="B175" t="n">
         <v>79358</v>
@@ -21565,7 +21573,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -21579,13 +21587,13 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>460703</v>
+        <v>460702</v>
       </c>
       <c r="R175" t="n">
-        <v>7051878</v>
+        <v>7051854</v>
       </c>
       <c r="S175" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T175" t="inlineStr">
         <is>
@@ -21614,7 +21622,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -21624,12 +21632,12 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AC175" t="inlineStr">
         <is>
-          <t>På grov gammal gran</t>
+          <t>Rikligt, draperat, på de flesta granar i gammal flerskiktad granskog</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -21644,64 +21652,60 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>134165583</v>
+        <v>134171960</v>
       </c>
       <c r="B176" t="n">
-        <v>58079</v>
+        <v>79358</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>460650</v>
+        <v>460692</v>
       </c>
       <c r="R176" t="n">
-        <v>7052431</v>
+        <v>7052417</v>
       </c>
       <c r="S176" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -21730,7 +21734,7 @@
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -21740,7 +21744,7 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -21755,65 +21759,57 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>134171973</v>
+        <v>134163087</v>
       </c>
       <c r="B177" t="n">
-        <v>57162</v>
+        <v>89338</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>100138</v>
+        <v>510</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K177" t="inlineStr"/>
-      <c r="L177" t="inlineStr"/>
-      <c r="M177" t="inlineStr"/>
-      <c r="N177" t="inlineStr"/>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>460716</v>
+        <v>460736</v>
       </c>
       <c r="R177" t="n">
-        <v>7051811</v>
+        <v>7052124</v>
       </c>
       <c r="S177" t="n">
         <v>3</v>
@@ -21845,7 +21841,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -21855,12 +21851,12 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AC177" t="inlineStr">
         <is>
-          <t>1 ex uppflog</t>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -21875,19 +21871,19 @@
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>134161522</v>
+        <v>134160600</v>
       </c>
       <c r="B178" t="n">
         <v>79358</v>
@@ -21917,7 +21913,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>400</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -21931,13 +21927,13 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>460702</v>
+        <v>460703</v>
       </c>
       <c r="R178" t="n">
-        <v>7051854</v>
+        <v>7051878</v>
       </c>
       <c r="S178" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
@@ -21966,7 +21962,7 @@
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -21976,12 +21972,12 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AC178" t="inlineStr">
         <is>
-          <t>Rikligt, draperat, på de flesta granar i gammal flerskiktad granskog</t>
+          <t>På grov gammal gran</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -21996,60 +21992,64 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>134171960</v>
+        <v>134165583</v>
       </c>
       <c r="B179" t="n">
-        <v>79358</v>
+        <v>58079</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I179" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>460692</v>
+        <v>460650</v>
       </c>
       <c r="R179" t="n">
-        <v>7052417</v>
+        <v>7052431</v>
       </c>
       <c r="S179" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -22078,7 +22078,7 @@
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
@@ -22088,7 +22088,7 @@
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -22103,12 +22103,12 @@
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
@@ -22805,10 +22805,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>134161962</v>
+        <v>134171972</v>
       </c>
       <c r="B186" t="n">
-        <v>83207</v>
+        <v>79358</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -22816,37 +22816,37 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>460653</v>
+        <v>460714</v>
       </c>
       <c r="R186" t="n">
-        <v>7051927</v>
+        <v>7051804</v>
       </c>
       <c r="S186" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -22875,7 +22875,7 @@
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
@@ -22885,12 +22885,12 @@
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AC186" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>1000 ex fördelat på 10 granar i gammal garnlavsrik granskog</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -22905,22 +22905,22 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>134163114</v>
+        <v>134161962</v>
       </c>
       <c r="B187" t="n">
-        <v>57975</v>
+        <v>83207</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -22928,39 +22928,34 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
-      <c r="M187" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P187" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>460736</v>
+        <v>460653</v>
       </c>
       <c r="R187" t="n">
-        <v>7052124</v>
+        <v>7051927</v>
       </c>
       <c r="S187" t="n">
         <v>4</v>
@@ -22992,7 +22987,7 @@
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
@@ -23002,12 +22997,12 @@
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AC187" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -23146,10 +23141,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>134171972</v>
+        <v>134163114</v>
       </c>
       <c r="B189" t="n">
-        <v>79358</v>
+        <v>57975</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -23157,37 +23152,42 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>460714</v>
+        <v>460736</v>
       </c>
       <c r="R189" t="n">
-        <v>7051804</v>
+        <v>7052124</v>
       </c>
       <c r="S189" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -23216,7 +23216,7 @@
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
@@ -23226,12 +23226,12 @@
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AC189" t="inlineStr">
         <is>
-          <t>1000 ex fördelat på 10 granar i gammal garnlavsrik granskog</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -23246,22 +23246,22 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>134171958</v>
+        <v>134162490</v>
       </c>
       <c r="B190" t="n">
-        <v>79358</v>
+        <v>91957</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -23269,37 +23269,37 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>460696</v>
+        <v>460806</v>
       </c>
       <c r="R190" t="n">
-        <v>7052420</v>
+        <v>7052008</v>
       </c>
       <c r="S190" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -23328,7 +23328,7 @@
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
@@ -23338,7 +23338,12 @@
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AC190" t="inlineStr">
+        <is>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -23353,22 +23358,22 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>134162490</v>
+        <v>134161368</v>
       </c>
       <c r="B191" t="n">
-        <v>91957</v>
+        <v>79358</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -23376,37 +23381,46 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P191" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>460806</v>
+        <v>460664</v>
       </c>
       <c r="R191" t="n">
-        <v>7052008</v>
+        <v>7051927</v>
       </c>
       <c r="S191" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -23435,7 +23449,7 @@
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
@@ -23445,12 +23459,12 @@
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AC191" t="inlineStr">
         <is>
-          <t>På gammal granlåga</t>
+          <t>På grov gammal gran</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -23470,14 +23484,14 @@
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>134161368</v>
+        <v>134162546</v>
       </c>
       <c r="B192" t="n">
         <v>79358</v>
@@ -23507,7 +23521,7 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -23521,13 +23535,13 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>460664</v>
+        <v>460804</v>
       </c>
       <c r="R192" t="n">
-        <v>7051927</v>
+        <v>7052009</v>
       </c>
       <c r="S192" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -23556,7 +23570,7 @@
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -23566,12 +23580,12 @@
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AC192" t="inlineStr">
         <is>
-          <t>På grov gammal gran</t>
+          <t>Fördelat på 5 gamla granar</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -23591,14 +23605,14 @@
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>134162546</v>
+        <v>134171958</v>
       </c>
       <c r="B193" t="n">
         <v>79358</v>
@@ -23626,29 +23640,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I193" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J193" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>460804</v>
+        <v>460696</v>
       </c>
       <c r="R193" t="n">
-        <v>7052009</v>
+        <v>7052420</v>
       </c>
       <c r="S193" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -23677,7 +23682,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -23687,12 +23692,7 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>11:06</t>
-        </is>
-      </c>
-      <c r="AC193" t="inlineStr">
-        <is>
-          <t>Fördelat på 5 gamla granar</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -23707,19 +23707,19 @@
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>134160932</v>
+        <v>134162379</v>
       </c>
       <c r="B194" t="n">
         <v>79358</v>
@@ -23749,7 +23749,7 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -23759,17 +23759,17 @@
       </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>460672</v>
+        <v>460792</v>
       </c>
       <c r="R194" t="n">
-        <v>7051901</v>
+        <v>7052051</v>
       </c>
       <c r="S194" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -23798,7 +23798,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -23808,7 +23808,12 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AC194" t="inlineStr">
+        <is>
+          <t>På gammal död gran (25 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -23823,19 +23828,19 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>134162379</v>
+        <v>134162445</v>
       </c>
       <c r="B195" t="n">
         <v>79358</v>
@@ -23879,10 +23884,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>460792</v>
+        <v>460801</v>
       </c>
       <c r="R195" t="n">
-        <v>7052051</v>
+        <v>7052041</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -23914,7 +23919,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -23924,12 +23929,12 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AC195" t="inlineStr">
         <is>
-          <t>På gammal död gran (25 cm dbh) i gammal granskog</t>
+          <t>På gammal, döende gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -23956,10 +23961,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>134162445</v>
+        <v>134166396</v>
       </c>
       <c r="B196" t="n">
-        <v>79358</v>
+        <v>57975</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -23967,43 +23972,39 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I196" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J196" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr"/>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>460801</v>
+        <v>460693</v>
       </c>
       <c r="R196" t="n">
-        <v>7052041</v>
+        <v>7052473</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -24035,7 +24036,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -24045,12 +24046,12 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AC196" t="inlineStr">
         <is>
-          <t>På gammal, döende gran i gammal granskog</t>
+          <t>Ringhack på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -24077,53 +24078,48 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>134166396</v>
+        <v>134171968</v>
       </c>
       <c r="B197" t="n">
-        <v>57975</v>
+        <v>80484</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
-      <c r="M197" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>460693</v>
+        <v>460675</v>
       </c>
       <c r="R197" t="n">
-        <v>7052473</v>
+        <v>7051857</v>
       </c>
       <c r="S197" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T197" t="inlineStr">
         <is>
@@ -24152,7 +24148,7 @@
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -24162,12 +24158,12 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AC197" t="inlineStr">
         <is>
-          <t>Ringhack på gammal levande gran i gammal granskog</t>
+          <t>På gammal levande rönn i gammal granskog</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -24194,27 +24190,27 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>134171968</v>
+        <v>134160932</v>
       </c>
       <c r="B198" t="n">
-        <v>80484</v>
+        <v>79358</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -24222,20 +24218,29 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I198" t="inlineStr"/>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>460675</v>
+        <v>460672</v>
       </c>
       <c r="R198" t="n">
-        <v>7051857</v>
+        <v>7051901</v>
       </c>
       <c r="S198" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
@@ -24264,7 +24269,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -24274,12 +24279,7 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>09:16</t>
-        </is>
-      </c>
-      <c r="AC198" t="inlineStr">
-        <is>
-          <t>På gammal levande rönn i gammal granskog</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -24294,19 +24294,19 @@
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>134187980</v>
+        <v>134188076</v>
       </c>
       <c r="B199" t="n">
         <v>79358</v>
@@ -24341,10 +24341,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>460749</v>
+        <v>460747</v>
       </c>
       <c r="R199" t="n">
-        <v>7052313</v>
+        <v>7052190</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -24376,7 +24376,7 @@
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -24386,7 +24386,7 @@
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -24413,7 +24413,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>134188076</v>
+        <v>134187980</v>
       </c>
       <c r="B200" t="n">
         <v>79358</v>
@@ -24448,10 +24448,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>460747</v>
+        <v>460749</v>
       </c>
       <c r="R200" t="n">
-        <v>7052190</v>
+        <v>7052313</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -24483,7 +24483,7 @@
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
@@ -24493,7 +24493,7 @@
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -25442,7 +25442,7 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>134187880</v>
+        <v>134187536</v>
       </c>
       <c r="B209" t="n">
         <v>79358</v>
@@ -25477,10 +25477,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>460681</v>
+        <v>460775</v>
       </c>
       <c r="R209" t="n">
-        <v>7052376</v>
+        <v>7052159</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -25512,7 +25512,7 @@
       </c>
       <c r="Z209" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
@@ -25522,7 +25522,12 @@
       </c>
       <c r="AB209" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC209" t="inlineStr">
+        <is>
+          <t>På gammal gran, 170-200 år, i gammal granskog</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -25549,7 +25554,7 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>134187536</v>
+        <v>134187880</v>
       </c>
       <c r="B210" t="n">
         <v>79358</v>
@@ -25584,10 +25589,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>460775</v>
+        <v>460681</v>
       </c>
       <c r="R210" t="n">
-        <v>7052159</v>
+        <v>7052376</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -25619,7 +25624,7 @@
       </c>
       <c r="Z210" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
@@ -25629,12 +25634,7 @@
       </c>
       <c r="AB210" t="inlineStr">
         <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC210" t="inlineStr">
-        <is>
-          <t>På gammal gran, 170-200 år, i gammal granskog</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -25889,7 +25889,7 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>134190579</v>
+        <v>134188004</v>
       </c>
       <c r="B213" t="n">
         <v>79358</v>
@@ -25924,10 +25924,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>460635</v>
+        <v>460734</v>
       </c>
       <c r="R213" t="n">
-        <v>7052005</v>
+        <v>7052252</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -25959,7 +25959,7 @@
       </c>
       <c r="Z213" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="AB213" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -25996,7 +25996,7 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>134190569</v>
+        <v>134190741</v>
       </c>
       <c r="B214" t="n">
         <v>79358</v>
@@ -26040,10 +26040,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>460773</v>
+        <v>460702</v>
       </c>
       <c r="R214" t="n">
-        <v>7052035</v>
+        <v>7051819</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -26075,7 +26075,7 @@
       </c>
       <c r="Z214" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
@@ -26085,7 +26085,7 @@
       </c>
       <c r="AB214" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -26112,7 +26112,7 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>134190741</v>
+        <v>134188053</v>
       </c>
       <c r="B215" t="n">
         <v>79358</v>
@@ -26140,26 +26140,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I215" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J215" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I215" t="inlineStr"/>
       <c r="P215" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>460702</v>
+        <v>460762</v>
       </c>
       <c r="R215" t="n">
-        <v>7051819</v>
+        <v>7052283</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -26191,7 +26182,7 @@
       </c>
       <c r="Z215" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
@@ -26201,7 +26192,7 @@
       </c>
       <c r="AB215" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -26228,7 +26219,7 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>134188004</v>
+        <v>134190569</v>
       </c>
       <c r="B216" t="n">
         <v>79358</v>
@@ -26256,17 +26247,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I216" t="inlineStr"/>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P216" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>460734</v>
+        <v>460773</v>
       </c>
       <c r="R216" t="n">
-        <v>7052252</v>
+        <v>7052035</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -26298,7 +26298,7 @@
       </c>
       <c r="Z216" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
@@ -26308,7 +26308,7 @@
       </c>
       <c r="AB216" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -26335,7 +26335,7 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>134188053</v>
+        <v>134190579</v>
       </c>
       <c r="B217" t="n">
         <v>79358</v>
@@ -26370,10 +26370,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>460762</v>
+        <v>460635</v>
       </c>
       <c r="R217" t="n">
-        <v>7052283</v>
+        <v>7052005</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -26405,7 +26405,7 @@
       </c>
       <c r="Z217" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
@@ -26415,7 +26415,7 @@
       </c>
       <c r="AB217" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD217" t="b">

--- a/artfynd/A 51504-2025 artfynd.xlsx
+++ b/artfynd/A 51504-2025 artfynd.xlsx
@@ -16020,57 +16020,48 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>134159342</v>
+        <v>134171971</v>
       </c>
       <c r="B126" t="n">
-        <v>79358</v>
+        <v>96396</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>460672</v>
+        <v>460688</v>
       </c>
       <c r="R126" t="n">
-        <v>7051847</v>
+        <v>7051821</v>
       </c>
       <c r="S126" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -16099,7 +16090,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -16109,7 +16100,12 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:04</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>På marken i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -16124,60 +16120,69 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>134171971</v>
+        <v>134159342</v>
       </c>
       <c r="B127" t="n">
-        <v>96396</v>
+        <v>79358</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>460688</v>
+        <v>460672</v>
       </c>
       <c r="R127" t="n">
-        <v>7051821</v>
+        <v>7051847</v>
       </c>
       <c r="S127" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -16206,7 +16211,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -16216,12 +16221,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>09:04</t>
-        </is>
-      </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>På marken i gammal fuktig granskog</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -16236,12 +16236,12 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
@@ -16374,48 +16374,53 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>134161325</v>
+        <v>134165432</v>
       </c>
       <c r="B129" t="n">
-        <v>99200</v>
+        <v>79790</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>221952</v>
+        <v>1778</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fjällig knopplav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Biatora fallax</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Hepp</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>460664</v>
+        <v>460673</v>
       </c>
       <c r="R129" t="n">
-        <v>7051927</v>
+        <v>7052450</v>
       </c>
       <c r="S129" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -16444,7 +16449,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -16454,7 +16459,12 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>På bark vid basen av gammal levande grov gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -16469,60 +16479,69 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>134165125</v>
+        <v>134166248</v>
       </c>
       <c r="B130" t="n">
-        <v>99200</v>
+        <v>79358</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>460690</v>
+        <v>460708</v>
       </c>
       <c r="R130" t="n">
-        <v>7052375</v>
+        <v>7052503</v>
       </c>
       <c r="S130" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -16551,7 +16570,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -16561,7 +16580,12 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -16576,74 +16600,60 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>134165576</v>
+        <v>134159098</v>
       </c>
       <c r="B131" t="n">
-        <v>57975</v>
+        <v>80429</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100109</v>
+        <v>229748</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L131" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>460650</v>
+        <v>460718</v>
       </c>
       <c r="R131" t="n">
-        <v>7052431</v>
+        <v>7051777</v>
       </c>
       <c r="S131" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -16672,7 +16682,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -16682,7 +16692,12 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>09:08</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>På död, klen rönn</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -16709,57 +16724,48 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>134162895</v>
+        <v>134161325</v>
       </c>
       <c r="B132" t="n">
-        <v>79358</v>
+        <v>99200</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>460789</v>
+        <v>460664</v>
       </c>
       <c r="R132" t="n">
-        <v>7051975</v>
+        <v>7051927</v>
       </c>
       <c r="S132" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -16788,7 +16794,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -16798,7 +16804,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -16818,60 +16824,55 @@
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>134165432</v>
+        <v>134165125</v>
       </c>
       <c r="B133" t="n">
-        <v>79790</v>
+        <v>99200</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1778</v>
+        <v>221952</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Fjällig knopplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Biatora fallax</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Hepp</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>460673</v>
+        <v>460690</v>
       </c>
       <c r="R133" t="n">
-        <v>7052450</v>
+        <v>7052375</v>
       </c>
       <c r="S133" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -16900,7 +16901,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -16910,12 +16911,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>12:42</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>På bark vid basen av gammal levande grov gran i gammal granskog</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -16930,22 +16926,22 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>134166248</v>
+        <v>134165576</v>
       </c>
       <c r="B134" t="n">
-        <v>79358</v>
+        <v>57975</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16953,31 +16949,36 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
@@ -16986,10 +16987,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>460708</v>
+        <v>460650</v>
       </c>
       <c r="R134" t="n">
-        <v>7052503</v>
+        <v>7052431</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -17021,7 +17022,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -17031,12 +17032,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>13:18</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -17051,60 +17047,69 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>134159098</v>
+        <v>134162895</v>
       </c>
       <c r="B135" t="n">
-        <v>80429</v>
+        <v>79358</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>229748</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>460718</v>
+        <v>460789</v>
       </c>
       <c r="R135" t="n">
-        <v>7051777</v>
+        <v>7051975</v>
       </c>
       <c r="S135" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -17133,7 +17138,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -17143,12 +17148,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>09:08</t>
-        </is>
-      </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>På död, klen rönn</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -17962,10 +17962,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>134162493</v>
+        <v>134165713</v>
       </c>
       <c r="B143" t="n">
-        <v>80477</v>
+        <v>80478</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17973,37 +17973,37 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6461</v>
+        <v>6462</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>460804</v>
+        <v>460711</v>
       </c>
       <c r="R143" t="n">
-        <v>7052009</v>
+        <v>7052457</v>
       </c>
       <c r="S143" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -18032,7 +18032,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -18042,7 +18042,12 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>På gammal rönn i gammal granskog</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -18057,22 +18062,22 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>134165713</v>
+        <v>134171966</v>
       </c>
       <c r="B144" t="n">
-        <v>80478</v>
+        <v>80429</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -18080,37 +18085,37 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6462</v>
+        <v>229748</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>460711</v>
+        <v>460676</v>
       </c>
       <c r="R144" t="n">
-        <v>7052457</v>
+        <v>7051857</v>
       </c>
       <c r="S144" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -18139,7 +18144,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -18149,12 +18154,12 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>På gammal rönn i gammal granskog</t>
+          <t>På rönn i gammal granskog</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -18181,48 +18186,57 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>134171966</v>
+        <v>134163868</v>
       </c>
       <c r="B145" t="n">
-        <v>80429</v>
+        <v>79358</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>229748</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>460676</v>
+        <v>460752</v>
       </c>
       <c r="R145" t="n">
-        <v>7051857</v>
+        <v>7052276</v>
       </c>
       <c r="S145" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -18251,7 +18265,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -18261,12 +18275,12 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>På rönn i gammal granskog</t>
+          <t>Rikligt på gammal levande grov gran (45 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -18293,57 +18307,48 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>134163868</v>
+        <v>134162493</v>
       </c>
       <c r="B146" t="n">
-        <v>79358</v>
+        <v>80477</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J146" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>460752</v>
+        <v>460804</v>
       </c>
       <c r="R146" t="n">
-        <v>7052276</v>
+        <v>7052009</v>
       </c>
       <c r="S146" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -18372,7 +18377,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -18382,12 +18387,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>11:44</t>
-        </is>
-      </c>
-      <c r="AC146" t="inlineStr">
-        <is>
-          <t>Rikligt på gammal levande grov gran (45 cm dbh) i gammal granskog</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -18402,12 +18402,12 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
@@ -20975,10 +20975,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>134163852</v>
+        <v>134171955</v>
       </c>
       <c r="B170" t="n">
-        <v>57975</v>
+        <v>79358</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -20986,42 +20986,37 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
-      <c r="M170" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>460763</v>
+        <v>460685</v>
       </c>
       <c r="R170" t="n">
-        <v>7052266</v>
+        <v>7052421</v>
       </c>
       <c r="S170" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -21050,7 +21045,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -21060,12 +21055,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>11:49</t>
-        </is>
-      </c>
-      <c r="AC170" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -21080,22 +21070,22 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>134171955</v>
+        <v>134163852</v>
       </c>
       <c r="B171" t="n">
-        <v>79358</v>
+        <v>57975</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -21103,37 +21093,42 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>460685</v>
+        <v>460763</v>
       </c>
       <c r="R171" t="n">
-        <v>7052421</v>
+        <v>7052266</v>
       </c>
       <c r="S171" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -21162,7 +21157,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -21172,7 +21167,12 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AC171" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -21187,12 +21187,12 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
@@ -23258,10 +23258,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>134162490</v>
+        <v>134171958</v>
       </c>
       <c r="B190" t="n">
-        <v>91957</v>
+        <v>79358</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -23269,37 +23269,37 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>460806</v>
+        <v>460696</v>
       </c>
       <c r="R190" t="n">
-        <v>7052008</v>
+        <v>7052420</v>
       </c>
       <c r="S190" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -23328,7 +23328,7 @@
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
@@ -23338,12 +23338,7 @@
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>11:04</t>
-        </is>
-      </c>
-      <c r="AC190" t="inlineStr">
-        <is>
-          <t>På gammal granlåga</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -23358,22 +23353,22 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>134161368</v>
+        <v>134162490</v>
       </c>
       <c r="B191" t="n">
-        <v>79358</v>
+        <v>91957</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -23381,46 +23376,37 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J191" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>460664</v>
+        <v>460806</v>
       </c>
       <c r="R191" t="n">
-        <v>7051927</v>
+        <v>7052008</v>
       </c>
       <c r="S191" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -23449,7 +23435,7 @@
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
@@ -23459,12 +23445,12 @@
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AC191" t="inlineStr">
         <is>
-          <t>På grov gammal gran</t>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -23484,14 +23470,14 @@
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>134162546</v>
+        <v>134161368</v>
       </c>
       <c r="B192" t="n">
         <v>79358</v>
@@ -23521,7 +23507,7 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -23535,13 +23521,13 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>460804</v>
+        <v>460664</v>
       </c>
       <c r="R192" t="n">
-        <v>7052009</v>
+        <v>7051927</v>
       </c>
       <c r="S192" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -23570,7 +23556,7 @@
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -23580,12 +23566,12 @@
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AC192" t="inlineStr">
         <is>
-          <t>Fördelat på 5 gamla granar</t>
+          <t>På grov gammal gran</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -23605,14 +23591,14 @@
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>134171958</v>
+        <v>134162546</v>
       </c>
       <c r="B193" t="n">
         <v>79358</v>
@@ -23640,20 +23626,29 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I193" t="inlineStr"/>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>460696</v>
+        <v>460804</v>
       </c>
       <c r="R193" t="n">
-        <v>7052420</v>
+        <v>7052009</v>
       </c>
       <c r="S193" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -23682,7 +23677,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -23692,7 +23687,12 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AC193" t="inlineStr">
+        <is>
+          <t>Fördelat på 5 gamla granar</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -23707,19 +23707,19 @@
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>134162379</v>
+        <v>134160932</v>
       </c>
       <c r="B194" t="n">
         <v>79358</v>
@@ -23749,7 +23749,7 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>400</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -23759,17 +23759,17 @@
       </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>460792</v>
+        <v>460672</v>
       </c>
       <c r="R194" t="n">
-        <v>7052051</v>
+        <v>7051901</v>
       </c>
       <c r="S194" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -23798,7 +23798,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -23808,12 +23808,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>10:58</t>
-        </is>
-      </c>
-      <c r="AC194" t="inlineStr">
-        <is>
-          <t>På gammal död gran (25 cm dbh) i gammal granskog</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -23828,19 +23823,19 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>134162445</v>
+        <v>134162379</v>
       </c>
       <c r="B195" t="n">
         <v>79358</v>
@@ -23884,10 +23879,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>460801</v>
+        <v>460792</v>
       </c>
       <c r="R195" t="n">
-        <v>7052041</v>
+        <v>7052051</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -23919,7 +23914,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -23929,12 +23924,12 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AC195" t="inlineStr">
         <is>
-          <t>På gammal, döende gran i gammal granskog</t>
+          <t>På gammal död gran (25 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -23961,10 +23956,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>134166396</v>
+        <v>134162445</v>
       </c>
       <c r="B196" t="n">
-        <v>57975</v>
+        <v>79358</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -23972,39 +23967,43 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I196" t="inlineStr"/>
-      <c r="M196" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>460693</v>
+        <v>460801</v>
       </c>
       <c r="R196" t="n">
-        <v>7052473</v>
+        <v>7052041</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -24036,7 +24035,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -24046,12 +24045,12 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AC196" t="inlineStr">
         <is>
-          <t>Ringhack på gammal levande gran i gammal granskog</t>
+          <t>På gammal, döende gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -24078,48 +24077,53 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>134171968</v>
+        <v>134166396</v>
       </c>
       <c r="B197" t="n">
-        <v>80484</v>
+        <v>57975</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>460675</v>
+        <v>460693</v>
       </c>
       <c r="R197" t="n">
-        <v>7051857</v>
+        <v>7052473</v>
       </c>
       <c r="S197" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T197" t="inlineStr">
         <is>
@@ -24148,7 +24152,7 @@
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -24158,12 +24162,12 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AC197" t="inlineStr">
         <is>
-          <t>På gammal levande rönn i gammal granskog</t>
+          <t>Ringhack på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -24190,27 +24194,27 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>134160932</v>
+        <v>134171968</v>
       </c>
       <c r="B198" t="n">
-        <v>79358</v>
+        <v>80484</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -24218,29 +24222,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I198" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="J198" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>460672</v>
+        <v>460675</v>
       </c>
       <c r="R198" t="n">
-        <v>7051901</v>
+        <v>7051857</v>
       </c>
       <c r="S198" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
@@ -24269,7 +24264,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -24279,7 +24274,12 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:16</t>
+        </is>
+      </c>
+      <c r="AC198" t="inlineStr">
+        <is>
+          <t>På gammal levande rönn i gammal granskog</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -24294,12 +24294,12 @@
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>

--- a/artfynd/A 51504-2025 artfynd.xlsx
+++ b/artfynd/A 51504-2025 artfynd.xlsx
@@ -17962,10 +17962,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>134165713</v>
+        <v>134162493</v>
       </c>
       <c r="B143" t="n">
-        <v>80478</v>
+        <v>80477</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17973,37 +17973,37 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6462</v>
+        <v>6461</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>460711</v>
+        <v>460804</v>
       </c>
       <c r="R143" t="n">
-        <v>7052457</v>
+        <v>7052009</v>
       </c>
       <c r="S143" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -18032,7 +18032,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -18042,12 +18042,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>12:58</t>
-        </is>
-      </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>På gammal rönn i gammal granskog</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -18062,22 +18057,22 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>134171966</v>
+        <v>134165713</v>
       </c>
       <c r="B144" t="n">
-        <v>80429</v>
+        <v>80478</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -18085,37 +18080,37 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>229748</v>
+        <v>6462</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>460676</v>
+        <v>460711</v>
       </c>
       <c r="R144" t="n">
-        <v>7051857</v>
+        <v>7052457</v>
       </c>
       <c r="S144" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -18144,7 +18139,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -18154,12 +18149,12 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>På rönn i gammal granskog</t>
+          <t>På gammal rönn i gammal granskog</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -18186,57 +18181,48 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>134163868</v>
+        <v>134171966</v>
       </c>
       <c r="B145" t="n">
-        <v>79358</v>
+        <v>80429</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>229748</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>460752</v>
+        <v>460676</v>
       </c>
       <c r="R145" t="n">
-        <v>7052276</v>
+        <v>7051857</v>
       </c>
       <c r="S145" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -18265,7 +18251,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -18275,12 +18261,12 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>Rikligt på gammal levande grov gran (45 cm dbh) i gammal granskog</t>
+          <t>På rönn i gammal granskog</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -18307,48 +18293,57 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>134162493</v>
+        <v>134163868</v>
       </c>
       <c r="B146" t="n">
-        <v>80477</v>
+        <v>79358</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>460804</v>
+        <v>460752</v>
       </c>
       <c r="R146" t="n">
-        <v>7052009</v>
+        <v>7052276</v>
       </c>
       <c r="S146" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -18377,7 +18372,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -18387,7 +18382,12 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>Rikligt på gammal levande grov gran (45 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -18402,12 +18402,12 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
@@ -21423,10 +21423,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>134171973</v>
+        <v>134165583</v>
       </c>
       <c r="B174" t="n">
-        <v>57162</v>
+        <v>58079</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -21434,45 +21434,41 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>100138</v>
+        <v>103031</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K174" t="inlineStr"/>
-      <c r="L174" t="inlineStr"/>
-      <c r="M174" t="inlineStr"/>
-      <c r="N174" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>460716</v>
+        <v>460650</v>
       </c>
       <c r="R174" t="n">
-        <v>7051811</v>
+        <v>7052431</v>
       </c>
       <c r="S174" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>
@@ -21501,7 +21497,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -21511,12 +21507,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>08:59</t>
-        </is>
-      </c>
-      <c r="AC174" t="inlineStr">
-        <is>
-          <t>1 ex uppflog</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -21531,69 +21522,68 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>134161522</v>
+        <v>134171973</v>
       </c>
       <c r="B175" t="n">
-        <v>79358</v>
+        <v>57162</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J175" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr"/>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" t="inlineStr"/>
+      <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>460702</v>
+        <v>460716</v>
       </c>
       <c r="R175" t="n">
-        <v>7051854</v>
+        <v>7051811</v>
       </c>
       <c r="S175" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T175" t="inlineStr">
         <is>
@@ -21622,7 +21612,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -21632,12 +21622,12 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AC175" t="inlineStr">
         <is>
-          <t>Rikligt, draperat, på de flesta granar i gammal flerskiktad granskog</t>
+          <t>1 ex uppflog</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -21664,7 +21654,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>134171960</v>
+        <v>134161522</v>
       </c>
       <c r="B176" t="n">
         <v>79358</v>
@@ -21692,20 +21682,29 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I176" t="inlineStr"/>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>460692</v>
+        <v>460702</v>
       </c>
       <c r="R176" t="n">
-        <v>7052417</v>
+        <v>7051854</v>
       </c>
       <c r="S176" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -21734,7 +21733,7 @@
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -21744,7 +21743,12 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AC176" t="inlineStr">
+        <is>
+          <t>Rikligt, draperat, på de flesta granar i gammal flerskiktad granskog</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -21771,10 +21775,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>134163087</v>
+        <v>134171960</v>
       </c>
       <c r="B177" t="n">
-        <v>89338</v>
+        <v>79358</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -21782,34 +21786,34 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>460736</v>
+        <v>460692</v>
       </c>
       <c r="R177" t="n">
-        <v>7052124</v>
+        <v>7052417</v>
       </c>
       <c r="S177" t="n">
         <v>3</v>
@@ -21841,7 +21845,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -21851,12 +21855,7 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>11:21</t>
-        </is>
-      </c>
-      <c r="AC177" t="inlineStr">
-        <is>
-          <t>På gammal granlåga</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -21871,22 +21870,22 @@
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>134160600</v>
+        <v>134163087</v>
       </c>
       <c r="B178" t="n">
-        <v>79358</v>
+        <v>89338</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -21894,46 +21893,37 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="J178" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>460703</v>
+        <v>460736</v>
       </c>
       <c r="R178" t="n">
-        <v>7051878</v>
+        <v>7052124</v>
       </c>
       <c r="S178" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
@@ -21962,7 +21952,7 @@
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -21972,12 +21962,12 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AC178" t="inlineStr">
         <is>
-          <t>På grov gammal gran</t>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -22004,52 +21994,57 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>134165583</v>
+        <v>134160600</v>
       </c>
       <c r="B179" t="n">
-        <v>58079</v>
+        <v>79358</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>460650</v>
+        <v>460703</v>
       </c>
       <c r="R179" t="n">
-        <v>7052431</v>
+        <v>7051878</v>
       </c>
       <c r="S179" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -22078,7 +22073,7 @@
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
@@ -22088,7 +22083,12 @@
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AC179" t="inlineStr">
+        <is>
+          <t>På grov gammal gran</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -23719,7 +23719,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>134160932</v>
+        <v>134162379</v>
       </c>
       <c r="B194" t="n">
         <v>79358</v>
@@ -23749,7 +23749,7 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -23759,17 +23759,17 @@
       </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>460672</v>
+        <v>460792</v>
       </c>
       <c r="R194" t="n">
-        <v>7051901</v>
+        <v>7052051</v>
       </c>
       <c r="S194" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -23798,7 +23798,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -23808,7 +23808,12 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AC194" t="inlineStr">
+        <is>
+          <t>På gammal död gran (25 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -23823,19 +23828,19 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>134162379</v>
+        <v>134162445</v>
       </c>
       <c r="B195" t="n">
         <v>79358</v>
@@ -23879,10 +23884,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>460792</v>
+        <v>460801</v>
       </c>
       <c r="R195" t="n">
-        <v>7052051</v>
+        <v>7052041</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -23914,7 +23919,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -23924,12 +23929,12 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AC195" t="inlineStr">
         <is>
-          <t>På gammal död gran (25 cm dbh) i gammal granskog</t>
+          <t>På gammal, döende gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -23956,10 +23961,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>134162445</v>
+        <v>134166396</v>
       </c>
       <c r="B196" t="n">
-        <v>79358</v>
+        <v>57975</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -23967,43 +23972,39 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I196" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J196" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr"/>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>460801</v>
+        <v>460693</v>
       </c>
       <c r="R196" t="n">
-        <v>7052041</v>
+        <v>7052473</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -24035,7 +24036,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -24045,12 +24046,12 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AC196" t="inlineStr">
         <is>
-          <t>På gammal, döende gran i gammal granskog</t>
+          <t>Ringhack på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -24077,53 +24078,48 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>134166396</v>
+        <v>134171968</v>
       </c>
       <c r="B197" t="n">
-        <v>57975</v>
+        <v>80484</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
-      <c r="M197" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>460693</v>
+        <v>460675</v>
       </c>
       <c r="R197" t="n">
-        <v>7052473</v>
+        <v>7051857</v>
       </c>
       <c r="S197" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T197" t="inlineStr">
         <is>
@@ -24152,7 +24148,7 @@
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -24162,12 +24158,12 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AC197" t="inlineStr">
         <is>
-          <t>Ringhack på gammal levande gran i gammal granskog</t>
+          <t>På gammal levande rönn i gammal granskog</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -24194,27 +24190,27 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>134171968</v>
+        <v>134160932</v>
       </c>
       <c r="B198" t="n">
-        <v>80484</v>
+        <v>79358</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -24222,20 +24218,29 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I198" t="inlineStr"/>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>460675</v>
+        <v>460672</v>
       </c>
       <c r="R198" t="n">
-        <v>7051857</v>
+        <v>7051901</v>
       </c>
       <c r="S198" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
@@ -24264,7 +24269,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -24274,12 +24279,7 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>09:16</t>
-        </is>
-      </c>
-      <c r="AC198" t="inlineStr">
-        <is>
-          <t>På gammal levande rönn i gammal granskog</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -24294,12 +24294,12 @@
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>

--- a/artfynd/A 51504-2025 artfynd.xlsx
+++ b/artfynd/A 51504-2025 artfynd.xlsx
@@ -20868,45 +20868,45 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>134159322</v>
+        <v>134171955</v>
       </c>
       <c r="B169" t="n">
-        <v>99200</v>
+        <v>79358</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>460672</v>
+        <v>460685</v>
       </c>
       <c r="R169" t="n">
-        <v>7051847</v>
+        <v>7052421</v>
       </c>
       <c r="S169" t="n">
         <v>3</v>
@@ -20938,7 +20938,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -20948,7 +20948,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -20963,57 +20963,57 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>134171955</v>
+        <v>134159322</v>
       </c>
       <c r="B170" t="n">
-        <v>79358</v>
+        <v>99200</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>460685</v>
+        <v>460672</v>
       </c>
       <c r="R170" t="n">
-        <v>7052421</v>
+        <v>7051847</v>
       </c>
       <c r="S170" t="n">
         <v>3</v>
@@ -21045,7 +21045,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -21055,7 +21055,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -21070,12 +21070,12 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
@@ -23719,7 +23719,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>134162379</v>
+        <v>134160932</v>
       </c>
       <c r="B194" t="n">
         <v>79358</v>
@@ -23749,7 +23749,7 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>400</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -23759,17 +23759,17 @@
       </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>460792</v>
+        <v>460672</v>
       </c>
       <c r="R194" t="n">
-        <v>7052051</v>
+        <v>7051901</v>
       </c>
       <c r="S194" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -23798,7 +23798,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -23808,12 +23808,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>10:58</t>
-        </is>
-      </c>
-      <c r="AC194" t="inlineStr">
-        <is>
-          <t>På gammal död gran (25 cm dbh) i gammal granskog</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -23828,19 +23823,19 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>134162445</v>
+        <v>134162379</v>
       </c>
       <c r="B195" t="n">
         <v>79358</v>
@@ -23884,10 +23879,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>460801</v>
+        <v>460792</v>
       </c>
       <c r="R195" t="n">
-        <v>7052041</v>
+        <v>7052051</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -23919,7 +23914,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -23929,12 +23924,12 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AC195" t="inlineStr">
         <is>
-          <t>På gammal, döende gran i gammal granskog</t>
+          <t>På gammal död gran (25 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -23961,10 +23956,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>134166396</v>
+        <v>134162445</v>
       </c>
       <c r="B196" t="n">
-        <v>57975</v>
+        <v>79358</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -23972,39 +23967,43 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I196" t="inlineStr"/>
-      <c r="M196" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>460693</v>
+        <v>460801</v>
       </c>
       <c r="R196" t="n">
-        <v>7052473</v>
+        <v>7052041</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -24036,7 +24035,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -24046,12 +24045,12 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AC196" t="inlineStr">
         <is>
-          <t>Ringhack på gammal levande gran i gammal granskog</t>
+          <t>På gammal, döende gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -24078,48 +24077,53 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>134171968</v>
+        <v>134166396</v>
       </c>
       <c r="B197" t="n">
-        <v>80484</v>
+        <v>57975</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>460675</v>
+        <v>460693</v>
       </c>
       <c r="R197" t="n">
-        <v>7051857</v>
+        <v>7052473</v>
       </c>
       <c r="S197" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T197" t="inlineStr">
         <is>
@@ -24148,7 +24152,7 @@
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -24158,12 +24162,12 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AC197" t="inlineStr">
         <is>
-          <t>På gammal levande rönn i gammal granskog</t>
+          <t>Ringhack på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -24190,27 +24194,27 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>134160932</v>
+        <v>134171968</v>
       </c>
       <c r="B198" t="n">
-        <v>79358</v>
+        <v>80484</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -24218,29 +24222,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I198" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="J198" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>460672</v>
+        <v>460675</v>
       </c>
       <c r="R198" t="n">
-        <v>7051901</v>
+        <v>7051857</v>
       </c>
       <c r="S198" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
@@ -24269,7 +24264,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -24279,7 +24274,12 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:16</t>
+        </is>
+      </c>
+      <c r="AC198" t="inlineStr">
+        <is>
+          <t>På gammal levande rönn i gammal granskog</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -24294,12 +24294,12 @@
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>

--- a/artfynd/A 51504-2025 artfynd.xlsx
+++ b/artfynd/A 51504-2025 artfynd.xlsx
@@ -16020,48 +16020,62 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>134171971</v>
+        <v>134161617</v>
       </c>
       <c r="B126" t="n">
-        <v>96396</v>
+        <v>79359</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>460688</v>
+        <v>460738</v>
       </c>
       <c r="R126" t="n">
-        <v>7051821</v>
+        <v>7051903</v>
       </c>
       <c r="S126" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -16090,7 +16104,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -16100,12 +16114,12 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>På marken i gammal fuktig granskog</t>
+          <t>Fördelat på 2 gamla granar</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -16120,12 +16134,12 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
@@ -16135,7 +16149,7 @@
         <v>134159342</v>
       </c>
       <c r="B127" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -16248,62 +16262,48 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>134161617</v>
+        <v>134171971</v>
       </c>
       <c r="B128" t="n">
-        <v>79358</v>
+        <v>96398</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>460738</v>
+        <v>460688</v>
       </c>
       <c r="R128" t="n">
-        <v>7051903</v>
+        <v>7051821</v>
       </c>
       <c r="S128" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -16332,7 +16332,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -16342,12 +16342,12 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>Fördelat på 2 gamla granar</t>
+          <t>På marken i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -16362,12 +16362,12 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
@@ -16377,7 +16377,7 @@
         <v>134165432</v>
       </c>
       <c r="B129" t="n">
-        <v>79790</v>
+        <v>79791</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -16494,7 +16494,7 @@
         <v>134166248</v>
       </c>
       <c r="B130" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16612,10 +16612,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>134159098</v>
+        <v>134161325</v>
       </c>
       <c r="B131" t="n">
-        <v>80429</v>
+        <v>99202</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16623,21 +16623,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>229748</v>
+        <v>221952</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -16647,10 +16647,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>460718</v>
+        <v>460664</v>
       </c>
       <c r="R131" t="n">
-        <v>7051777</v>
+        <v>7051927</v>
       </c>
       <c r="S131" t="n">
         <v>5</v>
@@ -16682,7 +16682,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -16692,12 +16692,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>09:08</t>
-        </is>
-      </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>På död, klen rönn</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -16717,17 +16712,17 @@
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>134161325</v>
+        <v>134165125</v>
       </c>
       <c r="B132" t="n">
-        <v>99200</v>
+        <v>99202</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16755,14 +16750,14 @@
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>460664</v>
+        <v>460690</v>
       </c>
       <c r="R132" t="n">
-        <v>7051927</v>
+        <v>7052375</v>
       </c>
       <c r="S132" t="n">
         <v>5</v>
@@ -16794,7 +16789,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -16804,7 +16799,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -16824,55 +16819,69 @@
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>134165125</v>
+        <v>134165576</v>
       </c>
       <c r="B133" t="n">
-        <v>99200</v>
+        <v>57975</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>460690</v>
+        <v>460650</v>
       </c>
       <c r="R133" t="n">
-        <v>7052375</v>
+        <v>7052431</v>
       </c>
       <c r="S133" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -16901,7 +16910,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -16911,7 +16920,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -16938,62 +16947,48 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>134165576</v>
+        <v>134159098</v>
       </c>
       <c r="B134" t="n">
-        <v>57975</v>
+        <v>80430</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>100109</v>
+        <v>229748</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L134" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>460650</v>
+        <v>460718</v>
       </c>
       <c r="R134" t="n">
-        <v>7052431</v>
+        <v>7051777</v>
       </c>
       <c r="S134" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -17022,7 +17017,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -17032,7 +17027,12 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>09:08</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>På död, klen rönn</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -17062,7 +17062,7 @@
         <v>134162895</v>
       </c>
       <c r="B135" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -17178,7 +17178,7 @@
         <v>134158960</v>
       </c>
       <c r="B136" t="n">
-        <v>80477</v>
+        <v>80478</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -17285,7 +17285,7 @@
         <v>134159178</v>
       </c>
       <c r="B137" t="n">
-        <v>80478</v>
+        <v>80479</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -17397,7 +17397,7 @@
         <v>134165214</v>
       </c>
       <c r="B138" t="n">
-        <v>80478</v>
+        <v>80479</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -17509,7 +17509,7 @@
         <v>134171947</v>
       </c>
       <c r="B139" t="n">
-        <v>80485</v>
+        <v>80486</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17621,7 +17621,7 @@
         <v>134171951</v>
       </c>
       <c r="B140" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17728,7 +17728,7 @@
         <v>134165139</v>
       </c>
       <c r="B141" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17844,7 +17844,7 @@
         <v>134166744</v>
       </c>
       <c r="B142" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17962,10 +17962,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>134162493</v>
+        <v>134171966</v>
       </c>
       <c r="B143" t="n">
-        <v>80477</v>
+        <v>80430</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17973,37 +17973,37 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6461</v>
+        <v>229748</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>460804</v>
+        <v>460676</v>
       </c>
       <c r="R143" t="n">
-        <v>7052009</v>
+        <v>7051857</v>
       </c>
       <c r="S143" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -18032,7 +18032,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -18042,7 +18042,12 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>På rönn i gammal granskog</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -18057,60 +18062,69 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>134165713</v>
+        <v>134163868</v>
       </c>
       <c r="B144" t="n">
-        <v>80478</v>
+        <v>79359</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P144" t="inlineStr">
         <is>
           <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>460711</v>
+        <v>460752</v>
       </c>
       <c r="R144" t="n">
-        <v>7052457</v>
+        <v>7052276</v>
       </c>
       <c r="S144" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -18139,7 +18153,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -18149,12 +18163,12 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>På gammal rönn i gammal granskog</t>
+          <t>Rikligt på gammal levande grov gran (45 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -18181,10 +18195,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>134171966</v>
+        <v>134165713</v>
       </c>
       <c r="B145" t="n">
-        <v>80429</v>
+        <v>80479</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -18192,37 +18206,37 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>229748</v>
+        <v>6462</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>460676</v>
+        <v>460711</v>
       </c>
       <c r="R145" t="n">
-        <v>7051857</v>
+        <v>7052457</v>
       </c>
       <c r="S145" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -18251,7 +18265,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -18261,12 +18275,12 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>På rönn i gammal granskog</t>
+          <t>På gammal rönn i gammal granskog</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -18293,57 +18307,48 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>134163868</v>
+        <v>134162493</v>
       </c>
       <c r="B146" t="n">
-        <v>79358</v>
+        <v>80478</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J146" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>460752</v>
+        <v>460804</v>
       </c>
       <c r="R146" t="n">
-        <v>7052276</v>
+        <v>7052009</v>
       </c>
       <c r="S146" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -18372,7 +18377,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -18382,12 +18387,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>11:44</t>
-        </is>
-      </c>
-      <c r="AC146" t="inlineStr">
-        <is>
-          <t>Rikligt på gammal levande grov gran (45 cm dbh) i gammal granskog</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -18402,12 +18402,12 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
@@ -18417,7 +18417,7 @@
         <v>134158853</v>
       </c>
       <c r="B147" t="n">
-        <v>99200</v>
+        <v>99202</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
@@ -18524,7 +18524,7 @@
         <v>134166104</v>
       </c>
       <c r="B148" t="n">
-        <v>99200</v>
+        <v>99202</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -18631,7 +18631,7 @@
         <v>134171976</v>
       </c>
       <c r="B149" t="n">
-        <v>99200</v>
+        <v>99202</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -18743,7 +18743,7 @@
         <v>134171965</v>
       </c>
       <c r="B150" t="n">
-        <v>106292</v>
+        <v>106294</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18852,48 +18852,57 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>134161209</v>
+        <v>134161529</v>
       </c>
       <c r="B151" t="n">
-        <v>91920</v>
+        <v>79359</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P151" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>460668</v>
+        <v>460757</v>
       </c>
       <c r="R151" t="n">
-        <v>7051920</v>
+        <v>7051937</v>
       </c>
       <c r="S151" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -18922,7 +18931,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -18932,7 +18941,12 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>Fördelat på 3 gamla granar</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -18952,17 +18966,17 @@
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>134171956</v>
+        <v>134163277</v>
       </c>
       <c r="B152" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18987,20 +19001,29 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I152" t="inlineStr"/>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>460688</v>
+        <v>460726</v>
       </c>
       <c r="R152" t="n">
-        <v>7052421</v>
+        <v>7052196</v>
       </c>
       <c r="S152" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -19029,7 +19052,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -19039,7 +19062,12 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>Fördelat på 3 gamla granar</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -19054,22 +19082,22 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>134171946</v>
+        <v>134161209</v>
       </c>
       <c r="B153" t="n">
-        <v>80478</v>
+        <v>91922</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -19077,37 +19105,37 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>460716</v>
+        <v>460668</v>
       </c>
       <c r="R153" t="n">
-        <v>7052447</v>
+        <v>7051920</v>
       </c>
       <c r="S153" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -19136,7 +19164,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -19146,12 +19174,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>På rönnlåga i gammal granskog</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -19166,22 +19189,22 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>134162816</v>
+        <v>134171956</v>
       </c>
       <c r="B154" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -19206,29 +19229,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="J154" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>460812</v>
+        <v>460688</v>
       </c>
       <c r="R154" t="n">
-        <v>7052078</v>
+        <v>7052421</v>
       </c>
       <c r="S154" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -19257,7 +19271,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -19267,12 +19281,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>11:10</t>
-        </is>
-      </c>
-      <c r="AC154" t="inlineStr">
-        <is>
-          <t>Gammal död gran (ca 23 cm dbh) draperad med garnlav i gammal gles granskog</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -19299,10 +19308,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>134171970</v>
+        <v>134171946</v>
       </c>
       <c r="B155" t="n">
-        <v>101386</v>
+        <v>80479</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -19310,21 +19319,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>222498</v>
+        <v>6462</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -19334,10 +19343,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>460688</v>
+        <v>460716</v>
       </c>
       <c r="R155" t="n">
-        <v>7051821</v>
+        <v>7052447</v>
       </c>
       <c r="S155" t="n">
         <v>3</v>
@@ -19369,7 +19378,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -19379,12 +19388,12 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AC155" t="inlineStr">
         <is>
-          <t>På marken i gammal fuktig granskog</t>
+          <t>På rönnlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -19411,10 +19420,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>134163277</v>
+        <v>134162816</v>
       </c>
       <c r="B156" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -19441,7 +19450,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>400</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -19451,14 +19460,14 @@
       </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>460726</v>
+        <v>460812</v>
       </c>
       <c r="R156" t="n">
-        <v>7052196</v>
+        <v>7052078</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -19490,7 +19499,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -19500,12 +19509,12 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AC156" t="inlineStr">
         <is>
-          <t>Fördelat på 3 gamla granar</t>
+          <t>Gammal död gran (ca 23 cm dbh) draperad med garnlav i gammal gles granskog</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -19520,69 +19529,60 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>134161529</v>
+        <v>134171970</v>
       </c>
       <c r="B157" t="n">
-        <v>79358</v>
+        <v>101388</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="J157" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>460757</v>
+        <v>460688</v>
       </c>
       <c r="R157" t="n">
-        <v>7051937</v>
+        <v>7051821</v>
       </c>
       <c r="S157" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -19611,7 +19611,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -19621,12 +19621,12 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AC157" t="inlineStr">
         <is>
-          <t>Fördelat på 3 gamla granar</t>
+          <t>På marken i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -19641,12 +19641,12 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
@@ -19656,7 +19656,7 @@
         <v>134166640</v>
       </c>
       <c r="B158" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -19889,7 +19889,7 @@
         <v>134171949</v>
       </c>
       <c r="B160" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -19996,7 +19996,7 @@
         <v>134160980</v>
       </c>
       <c r="B161" t="n">
-        <v>83343</v>
+        <v>83344</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -20108,7 +20108,7 @@
         <v>134165091</v>
       </c>
       <c r="B162" t="n">
-        <v>91920</v>
+        <v>91922</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -20215,7 +20215,7 @@
         <v>134171952</v>
       </c>
       <c r="B163" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -20322,7 +20322,7 @@
         <v>134171954</v>
       </c>
       <c r="B164" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -20429,7 +20429,7 @@
         <v>134158548</v>
       </c>
       <c r="B165" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -20542,32 +20542,32 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>134171967</v>
+        <v>134171957</v>
       </c>
       <c r="B166" t="n">
-        <v>80478</v>
+        <v>79359</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -20577,13 +20577,13 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>460677</v>
+        <v>460698</v>
       </c>
       <c r="R166" t="n">
-        <v>7051857</v>
+        <v>7052420</v>
       </c>
       <c r="S166" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -20612,7 +20612,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -20622,12 +20622,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>09:16</t>
-        </is>
-      </c>
-      <c r="AC166" t="inlineStr">
-        <is>
-          <t>På gammal levande rönn i gammal granskog</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -20654,32 +20649,32 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>134171957</v>
+        <v>134171967</v>
       </c>
       <c r="B167" t="n">
-        <v>79358</v>
+        <v>80479</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -20689,13 +20684,13 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>460698</v>
+        <v>460677</v>
       </c>
       <c r="R167" t="n">
-        <v>7052420</v>
+        <v>7051857</v>
       </c>
       <c r="S167" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -20724,7 +20719,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -20734,7 +20729,12 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>09:16</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>På gammal levande rönn i gammal granskog</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -20764,7 +20764,7 @@
         <v>134158911</v>
       </c>
       <c r="B168" t="n">
-        <v>99200</v>
+        <v>99202</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -20861,52 +20861,52 @@
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>134171955</v>
+        <v>134159322</v>
       </c>
       <c r="B169" t="n">
-        <v>79358</v>
+        <v>99202</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>460685</v>
+        <v>460672</v>
       </c>
       <c r="R169" t="n">
-        <v>7052421</v>
+        <v>7051847</v>
       </c>
       <c r="S169" t="n">
         <v>3</v>
@@ -20938,7 +20938,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -20948,7 +20948,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -20963,60 +20963,65 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>134159322</v>
+        <v>134163852</v>
       </c>
       <c r="B170" t="n">
-        <v>99200</v>
+        <v>57975</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>460672</v>
+        <v>460763</v>
       </c>
       <c r="R170" t="n">
-        <v>7051847</v>
+        <v>7052266</v>
       </c>
       <c r="S170" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -21045,7 +21050,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -21055,7 +21060,12 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -21082,10 +21092,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>134163852</v>
+        <v>134171955</v>
       </c>
       <c r="B171" t="n">
-        <v>57975</v>
+        <v>79359</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -21093,42 +21103,37 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>460763</v>
+        <v>460685</v>
       </c>
       <c r="R171" t="n">
-        <v>7052266</v>
+        <v>7052421</v>
       </c>
       <c r="S171" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -21157,7 +21162,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -21167,12 +21172,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>11:49</t>
-        </is>
-      </c>
-      <c r="AC171" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -21187,60 +21187,60 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>134171974</v>
+        <v>134164951</v>
       </c>
       <c r="B172" t="n">
-        <v>79977</v>
+        <v>96408</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6453</v>
+        <v>2810</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>460722</v>
+        <v>460763</v>
       </c>
       <c r="R172" t="n">
-        <v>7051751</v>
+        <v>7052266</v>
       </c>
       <c r="S172" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -21269,7 +21269,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -21279,12 +21279,12 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AC172" t="inlineStr">
         <is>
-          <t>På dimensionsavverkningsstubbe av tall i gammal garnlavsrik granskog</t>
+          <t>På block i kanten av lok</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -21299,60 +21299,60 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>134164951</v>
+        <v>134171974</v>
       </c>
       <c r="B173" t="n">
-        <v>96406</v>
+        <v>79978</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>2810</v>
+        <v>6453</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>460763</v>
+        <v>460722</v>
       </c>
       <c r="R173" t="n">
-        <v>7052266</v>
+        <v>7051751</v>
       </c>
       <c r="S173" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -21381,7 +21381,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -21391,12 +21391,12 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AC173" t="inlineStr">
         <is>
-          <t>På block i kanten av lok</t>
+          <t>På dimensionsavverkningsstubbe av tall i gammal garnlavsrik granskog</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -21411,12 +21411,12 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
@@ -21534,53 +21534,45 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>134171973</v>
+        <v>134163087</v>
       </c>
       <c r="B175" t="n">
-        <v>57162</v>
+        <v>89339</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>100138</v>
+        <v>510</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K175" t="inlineStr"/>
-      <c r="L175" t="inlineStr"/>
-      <c r="M175" t="inlineStr"/>
-      <c r="N175" t="inlineStr"/>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>460716</v>
+        <v>460736</v>
       </c>
       <c r="R175" t="n">
-        <v>7051811</v>
+        <v>7052124</v>
       </c>
       <c r="S175" t="n">
         <v>3</v>
@@ -21612,7 +21604,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -21622,12 +21614,12 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AC175" t="inlineStr">
         <is>
-          <t>1 ex uppflog</t>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -21642,22 +21634,22 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>134161522</v>
+        <v>134160600</v>
       </c>
       <c r="B176" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -21684,7 +21676,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>400</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -21698,13 +21690,13 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>460702</v>
+        <v>460703</v>
       </c>
       <c r="R176" t="n">
-        <v>7051854</v>
+        <v>7051878</v>
       </c>
       <c r="S176" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -21733,7 +21725,7 @@
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -21743,12 +21735,12 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AC176" t="inlineStr">
         <is>
-          <t>Rikligt, draperat, på de flesta granar i gammal flerskiktad granskog</t>
+          <t>På grov gammal gran</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -21763,57 +21755,65 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>134171960</v>
+        <v>134171973</v>
       </c>
       <c r="B177" t="n">
-        <v>79358</v>
+        <v>57162</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr"/>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" t="inlineStr"/>
+      <c r="N177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>460692</v>
+        <v>460716</v>
       </c>
       <c r="R177" t="n">
-        <v>7052417</v>
+        <v>7051811</v>
       </c>
       <c r="S177" t="n">
         <v>3</v>
@@ -21845,7 +21845,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -21855,7 +21855,12 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>08:59</t>
+        </is>
+      </c>
+      <c r="AC177" t="inlineStr">
+        <is>
+          <t>1 ex uppflog</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -21882,10 +21887,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>134163087</v>
+        <v>134161522</v>
       </c>
       <c r="B178" t="n">
-        <v>89338</v>
+        <v>79359</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -21893,37 +21898,46 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P178" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>460736</v>
+        <v>460702</v>
       </c>
       <c r="R178" t="n">
-        <v>7052124</v>
+        <v>7051854</v>
       </c>
       <c r="S178" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
@@ -21952,7 +21966,7 @@
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -21962,12 +21976,12 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AC178" t="inlineStr">
         <is>
-          <t>På gammal granlåga</t>
+          <t>Rikligt, draperat, på de flesta granar i gammal flerskiktad granskog</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -21982,22 +21996,22 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>134160600</v>
+        <v>134171960</v>
       </c>
       <c r="B179" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -22022,29 +22036,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I179" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="J179" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>460703</v>
+        <v>460692</v>
       </c>
       <c r="R179" t="n">
-        <v>7051878</v>
+        <v>7052417</v>
       </c>
       <c r="S179" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -22073,7 +22078,7 @@
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
@@ -22083,12 +22088,7 @@
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>09:49</t>
-        </is>
-      </c>
-      <c r="AC179" t="inlineStr">
-        <is>
-          <t>På grov gammal gran</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -22103,22 +22103,22 @@
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>134161245</v>
+        <v>134165861</v>
       </c>
       <c r="B180" t="n">
-        <v>83207</v>
+        <v>79359</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -22126,37 +22126,37 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>460664</v>
+        <v>460714</v>
       </c>
       <c r="R180" t="n">
-        <v>7051927</v>
+        <v>7052420</v>
       </c>
       <c r="S180" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T180" t="inlineStr">
         <is>
@@ -22185,7 +22185,7 @@
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
@@ -22195,12 +22195,12 @@
       </c>
       <c r="AB180" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AC180" t="inlineStr">
         <is>
-          <t>På död gammal gran</t>
+          <t>På gammal grov gran, 70 cm i diameter, i gammal bördig granskog</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -22215,12 +22215,12 @@
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
@@ -22230,7 +22230,7 @@
         <v>134162652</v>
       </c>
       <c r="B181" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -22348,32 +22348,32 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>134165861</v>
+        <v>134165723</v>
       </c>
       <c r="B182" t="n">
-        <v>79358</v>
+        <v>80430</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6425</v>
+        <v>229748</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -22383,10 +22383,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>460714</v>
+        <v>460711</v>
       </c>
       <c r="R182" t="n">
-        <v>7052420</v>
+        <v>7052457</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -22418,7 +22418,7 @@
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
@@ -22428,12 +22428,12 @@
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AC182" t="inlineStr">
         <is>
-          <t>På gammal grov gran, 70 cm i diameter, i gammal bördig granskog</t>
+          <t>På gammal rönn i gammal granskog</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -22460,48 +22460,48 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>134165723</v>
+        <v>134161245</v>
       </c>
       <c r="B183" t="n">
-        <v>80429</v>
+        <v>83208</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>229748</v>
+        <v>1312</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>460711</v>
+        <v>460664</v>
       </c>
       <c r="R183" t="n">
-        <v>7052457</v>
+        <v>7051927</v>
       </c>
       <c r="S183" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -22530,7 +22530,7 @@
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
@@ -22540,12 +22540,12 @@
       </c>
       <c r="AB183" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AC183" t="inlineStr">
         <is>
-          <t>På gammal rönn i gammal granskog</t>
+          <t>På död gammal gran</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -22560,66 +22560,57 @@
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>134161669</v>
+        <v>134165966</v>
       </c>
       <c r="B184" t="n">
-        <v>79358</v>
+        <v>79791</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6425</v>
+        <v>1778</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällig knopplav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Biatora fallax</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J184" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Hepp</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>460693</v>
+        <v>460694</v>
       </c>
       <c r="R184" t="n">
-        <v>7051901</v>
+        <v>7052451</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -22651,7 +22642,7 @@
       </c>
       <c r="Z184" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
@@ -22661,12 +22652,12 @@
       </c>
       <c r="AB184" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AC184" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På bark på rotben på gammal levande grov gran (55 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -22693,45 +22684,54 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>134165966</v>
+        <v>134161669</v>
       </c>
       <c r="B185" t="n">
-        <v>79790</v>
+        <v>79359</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>1778</v>
+        <v>6425</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Fjällig knopplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Biatora fallax</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Hepp</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>460694</v>
+        <v>460693</v>
       </c>
       <c r="R185" t="n">
-        <v>7052451</v>
+        <v>7051901</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -22763,7 +22763,7 @@
       </c>
       <c r="Z185" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
@@ -22773,12 +22773,12 @@
       </c>
       <c r="AB185" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AC185" t="inlineStr">
         <is>
-          <t>På bark på rotben på gammal levande grov gran (55 cm dbh) i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -22805,10 +22805,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>134171972</v>
+        <v>134161962</v>
       </c>
       <c r="B186" t="n">
-        <v>79358</v>
+        <v>83208</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -22816,37 +22816,37 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>460714</v>
+        <v>460653</v>
       </c>
       <c r="R186" t="n">
-        <v>7051804</v>
+        <v>7051927</v>
       </c>
       <c r="S186" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -22875,7 +22875,7 @@
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
@@ -22885,12 +22885,12 @@
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AC186" t="inlineStr">
         <is>
-          <t>1000 ex fördelat på 10 granar i gammal garnlavsrik granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -22905,60 +22905,60 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>134161962</v>
+        <v>134164962</v>
       </c>
       <c r="B187" t="n">
-        <v>83207</v>
+        <v>96398</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>1312</v>
+        <v>2809</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>460653</v>
+        <v>460763</v>
       </c>
       <c r="R187" t="n">
-        <v>7051927</v>
+        <v>7052266</v>
       </c>
       <c r="S187" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -22987,7 +22987,7 @@
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
@@ -22997,12 +22997,12 @@
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AC187" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På block i kanten av lok</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -23029,48 +23029,53 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>134164962</v>
+        <v>134163114</v>
       </c>
       <c r="B188" t="n">
-        <v>96396</v>
+        <v>57975</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>2809</v>
+        <v>100109</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>460763</v>
+        <v>460736</v>
       </c>
       <c r="R188" t="n">
-        <v>7052266</v>
+        <v>7052124</v>
       </c>
       <c r="S188" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -23099,7 +23104,7 @@
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
@@ -23109,12 +23114,12 @@
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AC188" t="inlineStr">
         <is>
-          <t>På block i kanten av lok</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -23141,10 +23146,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>134163114</v>
+        <v>134171972</v>
       </c>
       <c r="B189" t="n">
-        <v>57975</v>
+        <v>79359</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -23152,42 +23157,37 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
-      <c r="M189" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>460736</v>
+        <v>460714</v>
       </c>
       <c r="R189" t="n">
-        <v>7052124</v>
+        <v>7051804</v>
       </c>
       <c r="S189" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -23216,7 +23216,7 @@
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
@@ -23226,12 +23226,12 @@
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AC189" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>1000 ex fördelat på 10 granar i gammal garnlavsrik granskog</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -23246,22 +23246,22 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>134171958</v>
+        <v>134162490</v>
       </c>
       <c r="B190" t="n">
-        <v>79358</v>
+        <v>91959</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -23269,37 +23269,37 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>460696</v>
+        <v>460806</v>
       </c>
       <c r="R190" t="n">
-        <v>7052420</v>
+        <v>7052008</v>
       </c>
       <c r="S190" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -23328,7 +23328,7 @@
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
@@ -23338,7 +23338,12 @@
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AC190" t="inlineStr">
+        <is>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -23353,22 +23358,22 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>134162490</v>
+        <v>134161368</v>
       </c>
       <c r="B191" t="n">
-        <v>91957</v>
+        <v>79359</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -23376,37 +23381,46 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P191" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>460806</v>
+        <v>460664</v>
       </c>
       <c r="R191" t="n">
-        <v>7052008</v>
+        <v>7051927</v>
       </c>
       <c r="S191" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -23435,7 +23449,7 @@
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
@@ -23445,12 +23459,12 @@
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AC191" t="inlineStr">
         <is>
-          <t>På gammal granlåga</t>
+          <t>På grov gammal gran</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -23470,17 +23484,17 @@
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>134161368</v>
+        <v>134162546</v>
       </c>
       <c r="B192" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -23507,7 +23521,7 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -23521,13 +23535,13 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>460664</v>
+        <v>460804</v>
       </c>
       <c r="R192" t="n">
-        <v>7051927</v>
+        <v>7052009</v>
       </c>
       <c r="S192" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -23556,7 +23570,7 @@
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -23566,12 +23580,12 @@
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AC192" t="inlineStr">
         <is>
-          <t>På grov gammal gran</t>
+          <t>Fördelat på 5 gamla granar</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -23591,17 +23605,17 @@
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>134162546</v>
+        <v>134171958</v>
       </c>
       <c r="B193" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -23626,29 +23640,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I193" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J193" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>460804</v>
+        <v>460696</v>
       </c>
       <c r="R193" t="n">
-        <v>7052009</v>
+        <v>7052420</v>
       </c>
       <c r="S193" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -23677,7 +23682,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -23687,12 +23692,7 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>11:06</t>
-        </is>
-      </c>
-      <c r="AC193" t="inlineStr">
-        <is>
-          <t>Fördelat på 5 gamla granar</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -23707,12 +23707,12 @@
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
@@ -23722,7 +23722,7 @@
         <v>134160932</v>
       </c>
       <c r="B194" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -23835,27 +23835,27 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>134162379</v>
+        <v>134171968</v>
       </c>
       <c r="B195" t="n">
-        <v>79358</v>
+        <v>80485</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -23863,29 +23863,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I195" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J195" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>460792</v>
+        <v>460675</v>
       </c>
       <c r="R195" t="n">
-        <v>7052051</v>
+        <v>7051857</v>
       </c>
       <c r="S195" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T195" t="inlineStr">
         <is>
@@ -23914,7 +23905,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -23924,12 +23915,12 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AC195" t="inlineStr">
         <is>
-          <t>På gammal död gran (25 cm dbh) i gammal granskog</t>
+          <t>På gammal levande rönn i gammal granskog</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -23959,7 +23950,7 @@
         <v>134162445</v>
       </c>
       <c r="B196" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -24077,10 +24068,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>134166396</v>
+        <v>134162379</v>
       </c>
       <c r="B197" t="n">
-        <v>57975</v>
+        <v>79359</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -24088,39 +24079,43 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr"/>
-      <c r="M197" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>460693</v>
+        <v>460792</v>
       </c>
       <c r="R197" t="n">
-        <v>7052473</v>
+        <v>7052051</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -24152,7 +24147,7 @@
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -24162,12 +24157,12 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AC197" t="inlineStr">
         <is>
-          <t>Ringhack på gammal levande gran i gammal granskog</t>
+          <t>På gammal död gran (25 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -24194,48 +24189,53 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>134171968</v>
+        <v>134166396</v>
       </c>
       <c r="B198" t="n">
-        <v>80484</v>
+        <v>57975</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>460675</v>
+        <v>460693</v>
       </c>
       <c r="R198" t="n">
-        <v>7051857</v>
+        <v>7052473</v>
       </c>
       <c r="S198" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
@@ -24264,7 +24264,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -24274,12 +24274,12 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AC198" t="inlineStr">
         <is>
-          <t>På gammal levande rönn i gammal granskog</t>
+          <t>Ringhack på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -24306,10 +24306,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>134188076</v>
+        <v>134187980</v>
       </c>
       <c r="B199" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -24341,10 +24341,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>460747</v>
+        <v>460749</v>
       </c>
       <c r="R199" t="n">
-        <v>7052190</v>
+        <v>7052313</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -24376,7 +24376,7 @@
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -24386,7 +24386,7 @@
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -24413,10 +24413,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>134187980</v>
+        <v>134190545</v>
       </c>
       <c r="B200" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -24441,17 +24441,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I200" t="inlineStr"/>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P200" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>460749</v>
+        <v>460801</v>
       </c>
       <c r="R200" t="n">
-        <v>7052313</v>
+        <v>7052035</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -24483,7 +24492,7 @@
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
@@ -24493,7 +24502,12 @@
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AC200" t="inlineStr">
+        <is>
+          <t>På gammal gran i garnlavsrik granskog</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -24520,10 +24534,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>134190545</v>
+        <v>134188076</v>
       </c>
       <c r="B201" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -24548,26 +24562,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I201" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J201" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>460801</v>
+        <v>460747</v>
       </c>
       <c r="R201" t="n">
-        <v>7052035</v>
+        <v>7052190</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -24599,7 +24604,7 @@
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
@@ -24609,12 +24614,7 @@
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>11:01</t>
-        </is>
-      </c>
-      <c r="AC201" t="inlineStr">
-        <is>
-          <t>På gammal gran i garnlavsrik granskog</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -24644,7 +24644,7 @@
         <v>134188832</v>
       </c>
       <c r="B202" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -24760,7 +24760,7 @@
         <v>134187405</v>
       </c>
       <c r="B203" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -24881,7 +24881,7 @@
         <v>134187568</v>
       </c>
       <c r="B204" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -25002,7 +25002,7 @@
         <v>134187643</v>
       </c>
       <c r="B205" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -25114,7 +25114,7 @@
         <v>134190856</v>
       </c>
       <c r="B206" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -25218,10 +25218,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>134187781</v>
+        <v>134187721</v>
       </c>
       <c r="B207" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -25253,10 +25253,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>460723</v>
+        <v>460681</v>
       </c>
       <c r="R207" t="n">
-        <v>7052438</v>
+        <v>7052407</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -25288,7 +25288,7 @@
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
@@ -25298,7 +25298,7 @@
       </c>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AC207" t="inlineStr">
@@ -25330,10 +25330,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>134187721</v>
+        <v>134187781</v>
       </c>
       <c r="B208" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -25365,10 +25365,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>460681</v>
+        <v>460723</v>
       </c>
       <c r="R208" t="n">
-        <v>7052407</v>
+        <v>7052438</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -25400,7 +25400,7 @@
       </c>
       <c r="Z208" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
@@ -25410,7 +25410,7 @@
       </c>
       <c r="AB208" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC208" t="inlineStr">
@@ -25442,10 +25442,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>134187536</v>
+        <v>134190717</v>
       </c>
       <c r="B209" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -25477,10 +25477,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>460775</v>
+        <v>460688</v>
       </c>
       <c r="R209" t="n">
-        <v>7052159</v>
+        <v>7051819</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -25512,7 +25512,7 @@
       </c>
       <c r="Z209" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
@@ -25522,12 +25522,7 @@
       </c>
       <c r="AB209" t="inlineStr">
         <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC209" t="inlineStr">
-        <is>
-          <t>På gammal gran, 170-200 år, i gammal granskog</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -25557,7 +25552,7 @@
         <v>134187880</v>
       </c>
       <c r="B210" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -25661,10 +25656,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>134190717</v>
+        <v>134187536</v>
       </c>
       <c r="B211" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -25696,10 +25691,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>460688</v>
+        <v>460775</v>
       </c>
       <c r="R211" t="n">
-        <v>7051819</v>
+        <v>7052159</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -25731,7 +25726,7 @@
       </c>
       <c r="Z211" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
@@ -25741,7 +25736,12 @@
       </c>
       <c r="AB211" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC211" t="inlineStr">
+        <is>
+          <t>På gammal gran, 170-200 år, i gammal granskog</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -25771,7 +25771,7 @@
         <v>134190455</v>
       </c>
       <c r="B212" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -25889,10 +25889,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>134188004</v>
+        <v>134190579</v>
       </c>
       <c r="B213" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -25924,10 +25924,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>460734</v>
+        <v>460635</v>
       </c>
       <c r="R213" t="n">
-        <v>7052252</v>
+        <v>7052005</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -25959,7 +25959,7 @@
       </c>
       <c r="Z213" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="AB213" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -25996,10 +25996,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>134190741</v>
+        <v>134188004</v>
       </c>
       <c r="B214" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -26024,26 +26024,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I214" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J214" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>460702</v>
+        <v>460734</v>
       </c>
       <c r="R214" t="n">
-        <v>7051819</v>
+        <v>7052252</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -26075,7 +26066,7 @@
       </c>
       <c r="Z214" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
@@ -26085,7 +26076,7 @@
       </c>
       <c r="AB214" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -26112,10 +26103,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>134188053</v>
+        <v>134190569</v>
       </c>
       <c r="B215" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -26140,17 +26131,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I215" t="inlineStr"/>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P215" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>460762</v>
+        <v>460773</v>
       </c>
       <c r="R215" t="n">
-        <v>7052283</v>
+        <v>7052035</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -26182,7 +26182,7 @@
       </c>
       <c r="Z215" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
@@ -26192,7 +26192,7 @@
       </c>
       <c r="AB215" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -26219,10 +26219,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>134190569</v>
+        <v>134190741</v>
       </c>
       <c r="B216" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -26263,10 +26263,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>460773</v>
+        <v>460702</v>
       </c>
       <c r="R216" t="n">
-        <v>7052035</v>
+        <v>7051819</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -26298,7 +26298,7 @@
       </c>
       <c r="Z216" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
@@ -26308,7 +26308,7 @@
       </c>
       <c r="AB216" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -26335,10 +26335,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>134190579</v>
+        <v>134188053</v>
       </c>
       <c r="B217" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -26370,10 +26370,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>460635</v>
+        <v>460762</v>
       </c>
       <c r="R217" t="n">
-        <v>7052005</v>
+        <v>7052283</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -26405,7 +26405,7 @@
       </c>
       <c r="Z217" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
@@ -26415,7 +26415,7 @@
       </c>
       <c r="AB217" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -26445,7 +26445,7 @@
         <v>134187660</v>
       </c>
       <c r="B218" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -26557,7 +26557,7 @@
         <v>134188655</v>
       </c>
       <c r="B219" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -26678,7 +26678,7 @@
         <v>134189045</v>
       </c>
       <c r="B220" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -26785,7 +26785,7 @@
         <v>134187869</v>
       </c>
       <c r="B221" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>

--- a/artfynd/A 51504-2025 artfynd.xlsx
+++ b/artfynd/A 51504-2025 artfynd.xlsx
@@ -16374,53 +16374,48 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>134165432</v>
+        <v>134161325</v>
       </c>
       <c r="B129" t="n">
-        <v>79791</v>
+        <v>99202</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1778</v>
+        <v>221952</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Fjällig knopplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Biatora fallax</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Hepp</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>460673</v>
+        <v>460664</v>
       </c>
       <c r="R129" t="n">
-        <v>7052450</v>
+        <v>7051927</v>
       </c>
       <c r="S129" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -16449,7 +16444,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -16459,12 +16454,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>12:42</t>
-        </is>
-      </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>På bark vid basen av gammal levande grov gran i gammal granskog</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -16479,69 +16469,60 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>134166248</v>
+        <v>134159098</v>
       </c>
       <c r="B130" t="n">
-        <v>79359</v>
+        <v>80430</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>229748</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>460708</v>
+        <v>460718</v>
       </c>
       <c r="R130" t="n">
-        <v>7052503</v>
+        <v>7051777</v>
       </c>
       <c r="S130" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -16570,7 +16551,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -16580,12 +16561,12 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På död, klen rönn</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -16600,19 +16581,19 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>134161325</v>
+        <v>134165125</v>
       </c>
       <c r="B131" t="n">
         <v>99202</v>
@@ -16643,14 +16624,14 @@
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>460664</v>
+        <v>460690</v>
       </c>
       <c r="R131" t="n">
-        <v>7051927</v>
+        <v>7052375</v>
       </c>
       <c r="S131" t="n">
         <v>5</v>
@@ -16682,7 +16663,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -16692,7 +16673,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -16712,55 +16693,69 @@
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>134165125</v>
+        <v>134165576</v>
       </c>
       <c r="B132" t="n">
-        <v>99202</v>
+        <v>57975</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>460690</v>
+        <v>460650</v>
       </c>
       <c r="R132" t="n">
-        <v>7052375</v>
+        <v>7052431</v>
       </c>
       <c r="S132" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -16789,7 +16784,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -16799,7 +16794,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -16826,10 +16821,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>134165576</v>
+        <v>134162895</v>
       </c>
       <c r="B133" t="n">
-        <v>57975</v>
+        <v>79359</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16837,51 +16832,46 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L133" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>460650</v>
+        <v>460789</v>
       </c>
       <c r="R133" t="n">
-        <v>7052431</v>
+        <v>7051975</v>
       </c>
       <c r="S133" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -16910,7 +16900,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -16920,7 +16910,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -16947,48 +16937,53 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>134159098</v>
+        <v>134165432</v>
       </c>
       <c r="B134" t="n">
-        <v>80430</v>
+        <v>79791</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>229748</v>
+        <v>1778</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Fjällig knopplav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Biatora fallax</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>Hepp</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>460718</v>
+        <v>460673</v>
       </c>
       <c r="R134" t="n">
-        <v>7051777</v>
+        <v>7052450</v>
       </c>
       <c r="S134" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -17017,7 +17012,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -17027,12 +17022,12 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>På död, klen rönn</t>
+          <t>På bark vid basen av gammal levande grov gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -17047,19 +17042,19 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>134162895</v>
+        <v>134166248</v>
       </c>
       <c r="B135" t="n">
         <v>79359</v>
@@ -17089,7 +17084,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -17099,17 +17094,17 @@
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>460789</v>
+        <v>460708</v>
       </c>
       <c r="R135" t="n">
-        <v>7051975</v>
+        <v>7052503</v>
       </c>
       <c r="S135" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -17138,7 +17133,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -17148,7 +17143,12 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -17163,22 +17163,22 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>134158960</v>
+        <v>134159178</v>
       </c>
       <c r="B136" t="n">
-        <v>80478</v>
+        <v>80479</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -17186,21 +17186,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6461</v>
+        <v>6462</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -17210,13 +17210,13 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>460718</v>
+        <v>460683</v>
       </c>
       <c r="R136" t="n">
-        <v>7051777</v>
+        <v>7051835</v>
       </c>
       <c r="S136" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -17245,7 +17245,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -17255,7 +17255,12 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>På död, klen rönn</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -17282,10 +17287,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>134159178</v>
+        <v>134158960</v>
       </c>
       <c r="B137" t="n">
-        <v>80479</v>
+        <v>80478</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -17293,21 +17298,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6462</v>
+        <v>6461</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -17317,13 +17322,13 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>460683</v>
+        <v>460718</v>
       </c>
       <c r="R137" t="n">
-        <v>7051835</v>
+        <v>7051777</v>
       </c>
       <c r="S137" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -17352,7 +17357,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -17362,12 +17367,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>09:09</t>
-        </is>
-      </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>På död, klen rönn</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -17962,10 +17962,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>134171966</v>
+        <v>134162493</v>
       </c>
       <c r="B143" t="n">
-        <v>80430</v>
+        <v>80478</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17973,37 +17973,37 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>229748</v>
+        <v>6461</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>460676</v>
+        <v>460804</v>
       </c>
       <c r="R143" t="n">
-        <v>7051857</v>
+        <v>7052009</v>
       </c>
       <c r="S143" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -18032,7 +18032,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -18042,12 +18042,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>09:17</t>
-        </is>
-      </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>På rönn i gammal granskog</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -18062,69 +18057,60 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>134163868</v>
+        <v>134171966</v>
       </c>
       <c r="B144" t="n">
-        <v>79359</v>
+        <v>80430</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>229748</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>460752</v>
+        <v>460676</v>
       </c>
       <c r="R144" t="n">
-        <v>7052276</v>
+        <v>7051857</v>
       </c>
       <c r="S144" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -18153,7 +18139,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -18163,12 +18149,12 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>Rikligt på gammal levande grov gran (45 cm dbh) i gammal granskog</t>
+          <t>På rönn i gammal granskog</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -18195,48 +18181,57 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>134165713</v>
+        <v>134163868</v>
       </c>
       <c r="B145" t="n">
-        <v>80479</v>
+        <v>79359</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P145" t="inlineStr">
         <is>
           <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>460711</v>
+        <v>460752</v>
       </c>
       <c r="R145" t="n">
-        <v>7052457</v>
+        <v>7052276</v>
       </c>
       <c r="S145" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -18265,7 +18260,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -18275,12 +18270,12 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>På gammal rönn i gammal granskog</t>
+          <t>Rikligt på gammal levande grov gran (45 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -18307,10 +18302,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>134162493</v>
+        <v>134165713</v>
       </c>
       <c r="B146" t="n">
-        <v>80478</v>
+        <v>80479</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -18318,37 +18313,37 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6461</v>
+        <v>6462</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>460804</v>
+        <v>460711</v>
       </c>
       <c r="R146" t="n">
-        <v>7052009</v>
+        <v>7052457</v>
       </c>
       <c r="S146" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -18377,7 +18372,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -18387,7 +18382,12 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>På gammal rönn i gammal granskog</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -18402,12 +18402,12 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
@@ -18852,7 +18852,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>134161529</v>
+        <v>134163277</v>
       </c>
       <c r="B151" t="n">
         <v>79359</v>
@@ -18882,7 +18882,7 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>800</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -18892,17 +18892,17 @@
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>460757</v>
+        <v>460726</v>
       </c>
       <c r="R151" t="n">
-        <v>7051937</v>
+        <v>7052196</v>
       </c>
       <c r="S151" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -18931,7 +18931,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -18941,7 +18941,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AC151" t="inlineStr">
@@ -18966,14 +18966,14 @@
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>134163277</v>
+        <v>134161529</v>
       </c>
       <c r="B152" t="n">
         <v>79359</v>
@@ -19003,7 +19003,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>400</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -19013,17 +19013,17 @@
       </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>460726</v>
+        <v>460757</v>
       </c>
       <c r="R152" t="n">
-        <v>7052196</v>
+        <v>7051937</v>
       </c>
       <c r="S152" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -19052,7 +19052,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -19062,7 +19062,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AC152" t="inlineStr">
@@ -19087,7 +19087,7 @@
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
@@ -19201,32 +19201,32 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>134171956</v>
+        <v>134171946</v>
       </c>
       <c r="B154" t="n">
-        <v>79359</v>
+        <v>80479</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -19236,10 +19236,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>460688</v>
+        <v>460716</v>
       </c>
       <c r="R154" t="n">
-        <v>7052421</v>
+        <v>7052447</v>
       </c>
       <c r="S154" t="n">
         <v>3</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -19281,7 +19281,12 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>På rönnlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -19308,32 +19313,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>134171946</v>
+        <v>134171956</v>
       </c>
       <c r="B155" t="n">
-        <v>80479</v>
+        <v>79359</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -19343,10 +19348,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>460716</v>
+        <v>460688</v>
       </c>
       <c r="R155" t="n">
-        <v>7052447</v>
+        <v>7052421</v>
       </c>
       <c r="S155" t="n">
         <v>3</v>
@@ -19378,7 +19383,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -19388,12 +19393,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC155" t="inlineStr">
-        <is>
-          <t>På rönnlåga i gammal granskog</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -19653,7 +19653,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>134166640</v>
+        <v>134171949</v>
       </c>
       <c r="B158" t="n">
         <v>79359</v>
@@ -19681,29 +19681,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>460776</v>
+        <v>460691</v>
       </c>
       <c r="R158" t="n">
-        <v>7052247</v>
+        <v>7052421</v>
       </c>
       <c r="S158" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -19732,7 +19723,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -19742,7 +19733,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -19757,22 +19748,22 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>134163338</v>
+        <v>134166640</v>
       </c>
       <c r="B159" t="n">
-        <v>57975</v>
+        <v>79359</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19780,27 +19771,31 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr"/>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P159" t="inlineStr">
@@ -19809,13 +19804,13 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>460744</v>
+        <v>460776</v>
       </c>
       <c r="R159" t="n">
-        <v>7052204</v>
+        <v>7052247</v>
       </c>
       <c r="S159" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -19844,7 +19839,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -19854,12 +19849,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AC159" t="inlineStr">
-        <is>
-          <t>Ca 5 äldre rader med ringhack på gammal grov levande gran i gammal garnlavsrik granskog</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -19874,22 +19864,22 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>134171949</v>
+        <v>134163338</v>
       </c>
       <c r="B160" t="n">
-        <v>79359</v>
+        <v>57975</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -19897,37 +19887,42 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>460691</v>
+        <v>460744</v>
       </c>
       <c r="R160" t="n">
-        <v>7052421</v>
+        <v>7052204</v>
       </c>
       <c r="S160" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -19956,7 +19951,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -19966,7 +19961,12 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>Ca 5 äldre rader med ringhack på gammal grov levande gran i gammal garnlavsrik granskog</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -20861,52 +20861,52 @@
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>134159322</v>
+        <v>134171955</v>
       </c>
       <c r="B169" t="n">
-        <v>99202</v>
+        <v>79359</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>460672</v>
+        <v>460685</v>
       </c>
       <c r="R169" t="n">
-        <v>7051847</v>
+        <v>7052421</v>
       </c>
       <c r="S169" t="n">
         <v>3</v>
@@ -20938,7 +20938,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -20948,7 +20948,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -20963,65 +20963,60 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>134163852</v>
+        <v>134159322</v>
       </c>
       <c r="B170" t="n">
-        <v>57975</v>
+        <v>99202</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
-      <c r="M170" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>460763</v>
+        <v>460672</v>
       </c>
       <c r="R170" t="n">
-        <v>7052266</v>
+        <v>7051847</v>
       </c>
       <c r="S170" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -21050,7 +21045,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -21060,12 +21055,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>11:49</t>
-        </is>
-      </c>
-      <c r="AC170" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -21092,10 +21082,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>134171955</v>
+        <v>134163852</v>
       </c>
       <c r="B171" t="n">
-        <v>79359</v>
+        <v>57975</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -21103,37 +21093,42 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>460685</v>
+        <v>460763</v>
       </c>
       <c r="R171" t="n">
-        <v>7052421</v>
+        <v>7052266</v>
       </c>
       <c r="S171" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -21162,7 +21157,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -21172,7 +21167,12 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AC171" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -21187,12 +21187,12 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
@@ -21767,53 +21767,45 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>134171973</v>
+        <v>134171960</v>
       </c>
       <c r="B177" t="n">
-        <v>57162</v>
+        <v>79359</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K177" t="inlineStr"/>
-      <c r="L177" t="inlineStr"/>
-      <c r="M177" t="inlineStr"/>
-      <c r="N177" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>460716</v>
+        <v>460692</v>
       </c>
       <c r="R177" t="n">
-        <v>7051811</v>
+        <v>7052417</v>
       </c>
       <c r="S177" t="n">
         <v>3</v>
@@ -21845,7 +21837,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -21855,12 +21847,7 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>08:59</t>
-        </is>
-      </c>
-      <c r="AC177" t="inlineStr">
-        <is>
-          <t>1 ex uppflog</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -21887,57 +21874,56 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>134161522</v>
+        <v>134171973</v>
       </c>
       <c r="B178" t="n">
-        <v>79359</v>
+        <v>57162</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J178" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr"/>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" t="inlineStr"/>
+      <c r="N178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>460702</v>
+        <v>460716</v>
       </c>
       <c r="R178" t="n">
-        <v>7051854</v>
+        <v>7051811</v>
       </c>
       <c r="S178" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
@@ -21966,7 +21952,7 @@
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -21976,12 +21962,12 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AC178" t="inlineStr">
         <is>
-          <t>Rikligt, draperat, på de flesta granar i gammal flerskiktad granskog</t>
+          <t>1 ex uppflog</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -22008,7 +21994,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>134171960</v>
+        <v>134161522</v>
       </c>
       <c r="B179" t="n">
         <v>79359</v>
@@ -22036,20 +22022,29 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I179" t="inlineStr"/>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>460692</v>
+        <v>460702</v>
       </c>
       <c r="R179" t="n">
-        <v>7052417</v>
+        <v>7051854</v>
       </c>
       <c r="S179" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -22078,7 +22073,7 @@
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
@@ -22088,7 +22083,12 @@
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AC179" t="inlineStr">
+        <is>
+          <t>Rikligt, draperat, på de flesta granar i gammal flerskiktad granskog</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -22115,10 +22115,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>134165861</v>
+        <v>134161245</v>
       </c>
       <c r="B180" t="n">
-        <v>79359</v>
+        <v>83208</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -22126,37 +22126,37 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>460714</v>
+        <v>460664</v>
       </c>
       <c r="R180" t="n">
-        <v>7052420</v>
+        <v>7051927</v>
       </c>
       <c r="S180" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T180" t="inlineStr">
         <is>
@@ -22185,7 +22185,7 @@
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
@@ -22195,12 +22195,12 @@
       </c>
       <c r="AB180" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AC180" t="inlineStr">
         <is>
-          <t>På gammal grov gran, 70 cm i diameter, i gammal bördig granskog</t>
+          <t>På död gammal gran</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -22215,19 +22215,19 @@
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>134162652</v>
+        <v>134165861</v>
       </c>
       <c r="B181" t="n">
         <v>79359</v>
@@ -22255,26 +22255,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I181" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="J181" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>460812</v>
+        <v>460714</v>
       </c>
       <c r="R181" t="n">
-        <v>7052075</v>
+        <v>7052420</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -22306,7 +22297,7 @@
       </c>
       <c r="Z181" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
@@ -22316,12 +22307,12 @@
       </c>
       <c r="AB181" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AC181" t="inlineStr">
         <is>
-          <t>Gammal gran draperad med garnlav, i gammal gles granskog</t>
+          <t>På gammal grov gran, 70 cm i diameter, i gammal bördig granskog</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -22460,10 +22451,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>134161245</v>
+        <v>134162652</v>
       </c>
       <c r="B183" t="n">
-        <v>83208</v>
+        <v>79359</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -22471,37 +22462,46 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I183" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>460664</v>
+        <v>460812</v>
       </c>
       <c r="R183" t="n">
-        <v>7051927</v>
+        <v>7052075</v>
       </c>
       <c r="S183" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -22530,7 +22530,7 @@
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
@@ -22540,12 +22540,12 @@
       </c>
       <c r="AB183" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AC183" t="inlineStr">
         <is>
-          <t>På död gammal gran</t>
+          <t>Gammal gran draperad med garnlav, i gammal gles granskog</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -22560,12 +22560,12 @@
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
@@ -23947,10 +23947,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>134162445</v>
+        <v>134166396</v>
       </c>
       <c r="B196" t="n">
-        <v>79359</v>
+        <v>57975</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -23958,43 +23958,39 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I196" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J196" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr"/>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>460801</v>
+        <v>460693</v>
       </c>
       <c r="R196" t="n">
-        <v>7052041</v>
+        <v>7052473</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -24026,7 +24022,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -24036,12 +24032,12 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AC196" t="inlineStr">
         <is>
-          <t>På gammal, döende gran i gammal granskog</t>
+          <t>Ringhack på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -24068,7 +24064,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>134162379</v>
+        <v>134162445</v>
       </c>
       <c r="B197" t="n">
         <v>79359</v>
@@ -24112,10 +24108,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>460792</v>
+        <v>460801</v>
       </c>
       <c r="R197" t="n">
-        <v>7052051</v>
+        <v>7052041</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -24147,7 +24143,7 @@
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -24157,12 +24153,12 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AC197" t="inlineStr">
         <is>
-          <t>På gammal död gran (25 cm dbh) i gammal granskog</t>
+          <t>På gammal, döende gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -24189,10 +24185,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>134166396</v>
+        <v>134162379</v>
       </c>
       <c r="B198" t="n">
-        <v>57975</v>
+        <v>79359</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -24200,39 +24196,43 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I198" t="inlineStr"/>
-      <c r="M198" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>460693</v>
+        <v>460792</v>
       </c>
       <c r="R198" t="n">
-        <v>7052473</v>
+        <v>7052051</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -24264,7 +24264,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -24274,12 +24274,12 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AC198" t="inlineStr">
         <is>
-          <t>Ringhack på gammal levande gran i gammal granskog</t>
+          <t>På gammal död gran (25 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -24413,7 +24413,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>134190545</v>
+        <v>134188076</v>
       </c>
       <c r="B200" t="n">
         <v>79359</v>
@@ -24441,26 +24441,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I200" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J200" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>460801</v>
+        <v>460747</v>
       </c>
       <c r="R200" t="n">
-        <v>7052035</v>
+        <v>7052190</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -24492,7 +24483,7 @@
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
@@ -24502,12 +24493,7 @@
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>11:01</t>
-        </is>
-      </c>
-      <c r="AC200" t="inlineStr">
-        <is>
-          <t>På gammal gran i garnlavsrik granskog</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -24534,7 +24520,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>134188076</v>
+        <v>134190545</v>
       </c>
       <c r="B201" t="n">
         <v>79359</v>
@@ -24562,17 +24548,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I201" t="inlineStr"/>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P201" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>460747</v>
+        <v>460801</v>
       </c>
       <c r="R201" t="n">
-        <v>7052190</v>
+        <v>7052035</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -24604,7 +24599,7 @@
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
@@ -24614,7 +24609,12 @@
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AC201" t="inlineStr">
+        <is>
+          <t>På gammal gran i garnlavsrik granskog</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -25218,7 +25218,7 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>134187721</v>
+        <v>134187781</v>
       </c>
       <c r="B207" t="n">
         <v>79359</v>
@@ -25253,10 +25253,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>460681</v>
+        <v>460723</v>
       </c>
       <c r="R207" t="n">
-        <v>7052407</v>
+        <v>7052438</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -25288,7 +25288,7 @@
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
@@ -25298,7 +25298,7 @@
       </c>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC207" t="inlineStr">
@@ -25330,7 +25330,7 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>134187781</v>
+        <v>134187721</v>
       </c>
       <c r="B208" t="n">
         <v>79359</v>
@@ -25365,10 +25365,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>460723</v>
+        <v>460681</v>
       </c>
       <c r="R208" t="n">
-        <v>7052438</v>
+        <v>7052407</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -25400,7 +25400,7 @@
       </c>
       <c r="Z208" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
@@ -25410,7 +25410,7 @@
       </c>
       <c r="AB208" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AC208" t="inlineStr">
@@ -25442,7 +25442,7 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>134190717</v>
+        <v>134187880</v>
       </c>
       <c r="B209" t="n">
         <v>79359</v>
@@ -25477,10 +25477,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>460688</v>
+        <v>460681</v>
       </c>
       <c r="R209" t="n">
-        <v>7051819</v>
+        <v>7052376</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -25512,7 +25512,7 @@
       </c>
       <c r="Z209" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
@@ -25522,7 +25522,7 @@
       </c>
       <c r="AB209" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -25549,7 +25549,7 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>134187880</v>
+        <v>134187536</v>
       </c>
       <c r="B210" t="n">
         <v>79359</v>
@@ -25584,10 +25584,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>460681</v>
+        <v>460775</v>
       </c>
       <c r="R210" t="n">
-        <v>7052376</v>
+        <v>7052159</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -25619,7 +25619,7 @@
       </c>
       <c r="Z210" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
@@ -25629,7 +25629,12 @@
       </c>
       <c r="AB210" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC210" t="inlineStr">
+        <is>
+          <t>På gammal gran, 170-200 år, i gammal granskog</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -25656,7 +25661,7 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>134187536</v>
+        <v>134190717</v>
       </c>
       <c r="B211" t="n">
         <v>79359</v>
@@ -25691,10 +25696,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>460775</v>
+        <v>460688</v>
       </c>
       <c r="R211" t="n">
-        <v>7052159</v>
+        <v>7051819</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -25726,7 +25731,7 @@
       </c>
       <c r="Z211" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
@@ -25736,12 +25741,7 @@
       </c>
       <c r="AB211" t="inlineStr">
         <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC211" t="inlineStr">
-        <is>
-          <t>På gammal gran, 170-200 år, i gammal granskog</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -26103,7 +26103,7 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>134190569</v>
+        <v>134188053</v>
       </c>
       <c r="B215" t="n">
         <v>79359</v>
@@ -26131,26 +26131,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I215" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J215" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I215" t="inlineStr"/>
       <c r="P215" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>460773</v>
+        <v>460762</v>
       </c>
       <c r="R215" t="n">
-        <v>7052035</v>
+        <v>7052283</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -26182,7 +26173,7 @@
       </c>
       <c r="Z215" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
@@ -26192,7 +26183,7 @@
       </c>
       <c r="AB215" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -26219,7 +26210,7 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>134190741</v>
+        <v>134190569</v>
       </c>
       <c r="B216" t="n">
         <v>79359</v>
@@ -26263,10 +26254,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>460702</v>
+        <v>460773</v>
       </c>
       <c r="R216" t="n">
-        <v>7051819</v>
+        <v>7052035</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -26298,7 +26289,7 @@
       </c>
       <c r="Z216" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
@@ -26308,7 +26299,7 @@
       </c>
       <c r="AB216" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -26335,7 +26326,7 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>134188053</v>
+        <v>134190741</v>
       </c>
       <c r="B217" t="n">
         <v>79359</v>
@@ -26363,17 +26354,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I217" t="inlineStr"/>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P217" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>460762</v>
+        <v>460702</v>
       </c>
       <c r="R217" t="n">
-        <v>7052283</v>
+        <v>7051819</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -26405,7 +26405,7 @@
       </c>
       <c r="Z217" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
@@ -26415,7 +26415,7 @@
       </c>
       <c r="AB217" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD217" t="b">

--- a/artfynd/A 51504-2025 artfynd.xlsx
+++ b/artfynd/A 51504-2025 artfynd.xlsx
@@ -16374,48 +16374,62 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>134161325</v>
+        <v>134165576</v>
       </c>
       <c r="B129" t="n">
-        <v>99203</v>
+        <v>57975</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>460664</v>
+        <v>460650</v>
       </c>
       <c r="R129" t="n">
-        <v>7051927</v>
+        <v>7052431</v>
       </c>
       <c r="S129" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -16444,7 +16458,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -16454,7 +16468,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -16474,64 +16488,55 @@
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>134162895</v>
+        <v>134161325</v>
       </c>
       <c r="B130" t="n">
-        <v>79359</v>
+        <v>99203</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>460789</v>
+        <v>460664</v>
       </c>
       <c r="R130" t="n">
-        <v>7051975</v>
+        <v>7051927</v>
       </c>
       <c r="S130" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -16560,7 +16565,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -16570,7 +16575,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -16590,17 +16595,17 @@
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>134159098</v>
+        <v>134165125</v>
       </c>
       <c r="B131" t="n">
-        <v>80430</v>
+        <v>99203</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16608,34 +16613,34 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>229748</v>
+        <v>221952</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>460718</v>
+        <v>460690</v>
       </c>
       <c r="R131" t="n">
-        <v>7051777</v>
+        <v>7052375</v>
       </c>
       <c r="S131" t="n">
         <v>5</v>
@@ -16667,7 +16672,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -16677,12 +16682,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>09:08</t>
-        </is>
-      </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>På död, klen rönn</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -16709,10 +16709,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>134165576</v>
+        <v>134162895</v>
       </c>
       <c r="B132" t="n">
-        <v>57975</v>
+        <v>79359</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16720,51 +16720,46 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L132" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>460650</v>
+        <v>460789</v>
       </c>
       <c r="R132" t="n">
-        <v>7052431</v>
+        <v>7051975</v>
       </c>
       <c r="S132" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -16793,7 +16788,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -16803,7 +16798,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -16830,48 +16825,53 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>134165125</v>
+        <v>134165432</v>
       </c>
       <c r="B133" t="n">
-        <v>99203</v>
+        <v>79791</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>221952</v>
+        <v>1778</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fjällig knopplav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Biatora fallax</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Hepp</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>460690</v>
+        <v>460673</v>
       </c>
       <c r="R133" t="n">
-        <v>7052375</v>
+        <v>7052450</v>
       </c>
       <c r="S133" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -16900,7 +16900,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -16910,7 +16910,12 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>På bark vid basen av gammal levande grov gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -16925,7 +16930,7 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
@@ -16937,38 +16942,42 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>134165432</v>
+        <v>134166248</v>
       </c>
       <c r="B134" t="n">
-        <v>79791</v>
+        <v>79359</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1778</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Fjällig knopplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Biatora fallax</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Hepp</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr"/>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
@@ -16977,10 +16986,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>460673</v>
+        <v>460708</v>
       </c>
       <c r="R134" t="n">
-        <v>7052450</v>
+        <v>7052503</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -17012,7 +17021,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -17022,12 +17031,12 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>På bark vid basen av gammal levande grov gran i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -17054,57 +17063,48 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>134166248</v>
+        <v>134159098</v>
       </c>
       <c r="B135" t="n">
-        <v>79359</v>
+        <v>80430</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>229748</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>460708</v>
+        <v>460718</v>
       </c>
       <c r="R135" t="n">
-        <v>7052503</v>
+        <v>7051777</v>
       </c>
       <c r="S135" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -17133,7 +17133,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -17143,12 +17143,12 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AC135" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På död, klen rönn</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -17163,12 +17163,12 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
@@ -17287,10 +17287,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>134158960</v>
+        <v>134159178</v>
       </c>
       <c r="B137" t="n">
-        <v>80478</v>
+        <v>80479</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -17298,21 +17298,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6461</v>
+        <v>6462</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -17322,13 +17322,13 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>460718</v>
+        <v>460683</v>
       </c>
       <c r="R137" t="n">
-        <v>7051777</v>
+        <v>7051835</v>
       </c>
       <c r="S137" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -17357,7 +17357,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -17367,7 +17367,12 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>På död, klen rönn</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -17394,10 +17399,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>134159178</v>
+        <v>134158960</v>
       </c>
       <c r="B138" t="n">
-        <v>80479</v>
+        <v>80478</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -17405,21 +17410,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6462</v>
+        <v>6461</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -17429,13 +17434,13 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>460683</v>
+        <v>460718</v>
       </c>
       <c r="R138" t="n">
-        <v>7051835</v>
+        <v>7051777</v>
       </c>
       <c r="S138" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -17464,7 +17469,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -17474,12 +17479,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>09:09</t>
-        </is>
-      </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>På död, klen rönn</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -17725,7 +17725,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>134166744</v>
+        <v>134165139</v>
       </c>
       <c r="B141" t="n">
         <v>79359</v>
@@ -17755,7 +17755,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>700</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -17769,10 +17769,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>460779</v>
+        <v>460690</v>
       </c>
       <c r="R141" t="n">
-        <v>7052179</v>
+        <v>7052375</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -17804,7 +17804,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -17814,12 +17814,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>13:39</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>Rikligt på gammal levande gran i gammal granskog</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -17834,19 +17829,19 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>134165139</v>
+        <v>134166744</v>
       </c>
       <c r="B142" t="n">
         <v>79359</v>
@@ -17876,7 +17871,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -17890,10 +17885,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>460690</v>
+        <v>460779</v>
       </c>
       <c r="R142" t="n">
-        <v>7052375</v>
+        <v>7052179</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -17925,7 +17920,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -17935,7 +17930,12 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>Rikligt på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -17950,7 +17950,7 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
@@ -17962,57 +17962,48 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>134163868</v>
+        <v>134162493</v>
       </c>
       <c r="B143" t="n">
-        <v>79359</v>
+        <v>80478</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>460752</v>
+        <v>460804</v>
       </c>
       <c r="R143" t="n">
-        <v>7052276</v>
+        <v>7052009</v>
       </c>
       <c r="S143" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -18041,7 +18032,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -18051,12 +18042,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>11:44</t>
-        </is>
-      </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>Rikligt på gammal levande grov gran (45 cm dbh) i gammal granskog</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -18071,60 +18057,69 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>134165713</v>
+        <v>134163868</v>
       </c>
       <c r="B144" t="n">
-        <v>80479</v>
+        <v>79359</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P144" t="inlineStr">
         <is>
           <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>460711</v>
+        <v>460752</v>
       </c>
       <c r="R144" t="n">
-        <v>7052457</v>
+        <v>7052276</v>
       </c>
       <c r="S144" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -18153,7 +18148,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -18163,12 +18158,12 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>På gammal rönn i gammal granskog</t>
+          <t>Rikligt på gammal levande grov gran (45 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -18195,10 +18190,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>134171966</v>
+        <v>134165713</v>
       </c>
       <c r="B145" t="n">
-        <v>80430</v>
+        <v>80479</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -18206,37 +18201,37 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>229748</v>
+        <v>6462</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>460676</v>
+        <v>460711</v>
       </c>
       <c r="R145" t="n">
-        <v>7051857</v>
+        <v>7052457</v>
       </c>
       <c r="S145" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -18265,7 +18260,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -18275,12 +18270,12 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>På rönn i gammal granskog</t>
+          <t>På gammal rönn i gammal granskog</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -18307,10 +18302,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>134162493</v>
+        <v>134171966</v>
       </c>
       <c r="B146" t="n">
-        <v>80478</v>
+        <v>80430</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -18318,37 +18313,37 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6461</v>
+        <v>229748</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>460804</v>
+        <v>460676</v>
       </c>
       <c r="R146" t="n">
-        <v>7052009</v>
+        <v>7051857</v>
       </c>
       <c r="S146" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -18377,7 +18372,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -18387,7 +18382,12 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>På rönn i gammal granskog</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -18402,19 +18402,19 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>134171976</v>
+        <v>134166104</v>
       </c>
       <c r="B147" t="n">
         <v>99203</v>
@@ -18445,17 +18445,17 @@
       <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>460751</v>
+        <v>460692</v>
       </c>
       <c r="R147" t="n">
-        <v>7051437</v>
+        <v>7052457</v>
       </c>
       <c r="S147" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -18484,7 +18484,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -18494,12 +18494,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="AC147" t="inlineStr">
-        <is>
-          <t>På marken i äldre granskog</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -18514,22 +18509,22 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>134171965</v>
+        <v>134158853</v>
       </c>
       <c r="B148" t="n">
-        <v>106295</v>
+        <v>99203</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -18537,37 +18532,37 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>221725</v>
+        <v>221952</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>460691</v>
+        <v>460723</v>
       </c>
       <c r="R148" t="n">
-        <v>7051813</v>
+        <v>7051736</v>
       </c>
       <c r="S148" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -18596,7 +18591,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -18606,12 +18601,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>10:21</t>
-        </is>
-      </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>På marken i gammal granskog</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -18626,19 +18616,19 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>134158853</v>
+        <v>134171976</v>
       </c>
       <c r="B149" t="n">
         <v>99203</v>
@@ -18669,14 +18659,14 @@
       <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>460723</v>
+        <v>460751</v>
       </c>
       <c r="R149" t="n">
-        <v>7051736</v>
+        <v>7051437</v>
       </c>
       <c r="S149" t="n">
         <v>3</v>
@@ -18708,7 +18698,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -18718,7 +18708,12 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>På marken i äldre granskog</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -18733,22 +18728,22 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>134166104</v>
+        <v>134171965</v>
       </c>
       <c r="B150" t="n">
-        <v>99203</v>
+        <v>106295</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18756,37 +18751,37 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>221952</v>
+        <v>221725</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>460692</v>
+        <v>460691</v>
       </c>
       <c r="R150" t="n">
-        <v>7052457</v>
+        <v>7051813</v>
       </c>
       <c r="S150" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -18815,7 +18810,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -18825,7 +18820,12 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -18840,60 +18840,60 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>134171956</v>
+        <v>134161209</v>
       </c>
       <c r="B151" t="n">
-        <v>79359</v>
+        <v>91923</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>460688</v>
+        <v>460668</v>
       </c>
       <c r="R151" t="n">
-        <v>7052421</v>
+        <v>7051920</v>
       </c>
       <c r="S151" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -18922,7 +18922,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -18932,7 +18932,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -18947,19 +18947,19 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>134162816</v>
+        <v>134163277</v>
       </c>
       <c r="B152" t="n">
         <v>79359</v>
@@ -18989,7 +18989,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>800</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -18999,14 +18999,14 @@
       </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>460812</v>
+        <v>460726</v>
       </c>
       <c r="R152" t="n">
-        <v>7052078</v>
+        <v>7052196</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -19038,7 +19038,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -19048,12 +19048,12 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>Gammal död gran (ca 23 cm dbh) draperad med garnlav i gammal gles granskog</t>
+          <t>Fördelat på 3 gamla granar</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -19068,12 +19068,12 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
@@ -19201,48 +19201,57 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>134171946</v>
+        <v>134162816</v>
       </c>
       <c r="B154" t="n">
-        <v>80479</v>
+        <v>79359</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>460716</v>
+        <v>460812</v>
       </c>
       <c r="R154" t="n">
-        <v>7052447</v>
+        <v>7052078</v>
       </c>
       <c r="S154" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -19271,7 +19280,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -19281,12 +19290,12 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AC154" t="inlineStr">
         <is>
-          <t>På rönnlåga i gammal granskog</t>
+          <t>Gammal död gran (ca 23 cm dbh) draperad med garnlav i gammal gles granskog</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -19313,10 +19322,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>134171970</v>
+        <v>134171946</v>
       </c>
       <c r="B155" t="n">
-        <v>101389</v>
+        <v>80479</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -19324,21 +19333,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>222498</v>
+        <v>6462</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -19348,10 +19357,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>460688</v>
+        <v>460716</v>
       </c>
       <c r="R155" t="n">
-        <v>7051821</v>
+        <v>7052447</v>
       </c>
       <c r="S155" t="n">
         <v>3</v>
@@ -19383,7 +19392,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -19393,12 +19402,12 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AC155" t="inlineStr">
         <is>
-          <t>På marken i gammal fuktig granskog</t>
+          <t>På rönnlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -19425,57 +19434,48 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>134163277</v>
+        <v>134171970</v>
       </c>
       <c r="B156" t="n">
-        <v>79359</v>
+        <v>101389</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>460726</v>
+        <v>460688</v>
       </c>
       <c r="R156" t="n">
-        <v>7052196</v>
+        <v>7051821</v>
       </c>
       <c r="S156" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -19504,7 +19504,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -19514,12 +19514,12 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AC156" t="inlineStr">
         <is>
-          <t>Fördelat på 3 gamla granar</t>
+          <t>På marken i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -19534,60 +19534,60 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>134161209</v>
+        <v>134171956</v>
       </c>
       <c r="B157" t="n">
-        <v>91923</v>
+        <v>79359</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>460668</v>
+        <v>460688</v>
       </c>
       <c r="R157" t="n">
-        <v>7051920</v>
+        <v>7052421</v>
       </c>
       <c r="S157" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -19616,7 +19616,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -19626,7 +19626,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -19641,22 +19641,22 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>134166640</v>
+        <v>134163338</v>
       </c>
       <c r="B158" t="n">
-        <v>79359</v>
+        <v>57975</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -19664,31 +19664,27 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P158" t="inlineStr">
@@ -19697,13 +19693,13 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>460776</v>
+        <v>460744</v>
       </c>
       <c r="R158" t="n">
-        <v>7052247</v>
+        <v>7052204</v>
       </c>
       <c r="S158" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -19732,7 +19728,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -19742,7 +19738,12 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>Ca 5 äldre rader med ringhack på gammal grov levande gran i gammal garnlavsrik granskog</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -19757,22 +19758,22 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>134163338</v>
+        <v>134166640</v>
       </c>
       <c r="B159" t="n">
-        <v>57975</v>
+        <v>79359</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19780,27 +19781,31 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr"/>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P159" t="inlineStr">
@@ -19809,13 +19814,13 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>460744</v>
+        <v>460776</v>
       </c>
       <c r="R159" t="n">
-        <v>7052204</v>
+        <v>7052247</v>
       </c>
       <c r="S159" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -19844,7 +19849,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -19854,12 +19859,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AC159" t="inlineStr">
-        <is>
-          <t>Ca 5 äldre rader med ringhack på gammal grov levande gran i gammal garnlavsrik granskog</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -19874,12 +19874,12 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
@@ -19993,7 +19993,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>134171954</v>
+        <v>134171952</v>
       </c>
       <c r="B161" t="n">
         <v>79359</v>
@@ -20028,10 +20028,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>460686</v>
+        <v>460688</v>
       </c>
       <c r="R161" t="n">
-        <v>7052421</v>
+        <v>7052420</v>
       </c>
       <c r="S161" t="n">
         <v>3</v>
@@ -20100,10 +20100,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>134171952</v>
+        <v>134160980</v>
       </c>
       <c r="B162" t="n">
-        <v>79359</v>
+        <v>83344</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -20111,37 +20111,37 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>460688</v>
+        <v>460672</v>
       </c>
       <c r="R162" t="n">
-        <v>7052420</v>
+        <v>7051901</v>
       </c>
       <c r="S162" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -20170,7 +20170,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -20180,7 +20180,12 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC162" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -20195,60 +20200,60 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>134160980</v>
+        <v>134165091</v>
       </c>
       <c r="B163" t="n">
-        <v>83344</v>
+        <v>91923</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>460672</v>
+        <v>460690</v>
       </c>
       <c r="R163" t="n">
-        <v>7051901</v>
+        <v>7052375</v>
       </c>
       <c r="S163" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -20277,7 +20282,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -20287,12 +20292,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC163" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -20319,48 +20319,48 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>134165091</v>
+        <v>134171954</v>
       </c>
       <c r="B164" t="n">
-        <v>91923</v>
+        <v>79359</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>460690</v>
+        <v>460686</v>
       </c>
       <c r="R164" t="n">
-        <v>7052375</v>
+        <v>7052421</v>
       </c>
       <c r="S164" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -20389,7 +20389,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -20399,7 +20399,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -20414,60 +20414,69 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>134171967</v>
+        <v>134158548</v>
       </c>
       <c r="B165" t="n">
-        <v>80479</v>
+        <v>99181</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>460677</v>
+        <v>460863</v>
       </c>
       <c r="R165" t="n">
-        <v>7051857</v>
+        <v>7051485</v>
       </c>
       <c r="S165" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -20496,7 +20505,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -20506,12 +20515,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>09:16</t>
-        </is>
-      </c>
-      <c r="AC165" t="inlineStr">
-        <is>
-          <t>På gammal levande rönn i gammal granskog</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -20526,44 +20530,44 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>134171957</v>
+        <v>134171967</v>
       </c>
       <c r="B166" t="n">
-        <v>79359</v>
+        <v>80479</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -20573,13 +20577,13 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>460698</v>
+        <v>460677</v>
       </c>
       <c r="R166" t="n">
-        <v>7052420</v>
+        <v>7051857</v>
       </c>
       <c r="S166" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -20608,7 +20612,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -20618,7 +20622,12 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>09:16</t>
+        </is>
+      </c>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t>På gammal levande rönn i gammal granskog</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -20645,57 +20654,48 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>134158548</v>
+        <v>134171957</v>
       </c>
       <c r="B167" t="n">
-        <v>99181</v>
+        <v>79359</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="J167" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>460863</v>
+        <v>460698</v>
       </c>
       <c r="R167" t="n">
-        <v>7051485</v>
+        <v>7052420</v>
       </c>
       <c r="S167" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -20724,7 +20724,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -20749,12 +20749,12 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
@@ -21199,48 +21199,48 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>134171974</v>
+        <v>134164951</v>
       </c>
       <c r="B172" t="n">
-        <v>79978</v>
+        <v>96409</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6453</v>
+        <v>2810</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>460722</v>
+        <v>460763</v>
       </c>
       <c r="R172" t="n">
-        <v>7051751</v>
+        <v>7052266</v>
       </c>
       <c r="S172" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -21269,7 +21269,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -21279,12 +21279,12 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AC172" t="inlineStr">
         <is>
-          <t>På dimensionsavverkningsstubbe av tall i gammal garnlavsrik granskog</t>
+          <t>På block i kanten av lok</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -21299,60 +21299,60 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>134164951</v>
+        <v>134171974</v>
       </c>
       <c r="B173" t="n">
-        <v>96409</v>
+        <v>79978</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>2810</v>
+        <v>6453</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>460763</v>
+        <v>460722</v>
       </c>
       <c r="R173" t="n">
-        <v>7052266</v>
+        <v>7051751</v>
       </c>
       <c r="S173" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -21381,7 +21381,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -21391,12 +21391,12 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AC173" t="inlineStr">
         <is>
-          <t>På block i kanten av lok</t>
+          <t>På dimensionsavverkningsstubbe av tall i gammal garnlavsrik granskog</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -21411,19 +21411,19 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>134160600</v>
+        <v>134171960</v>
       </c>
       <c r="B174" t="n">
         <v>79359</v>
@@ -21451,29 +21451,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="J174" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>460703</v>
+        <v>460692</v>
       </c>
       <c r="R174" t="n">
-        <v>7051878</v>
+        <v>7052417</v>
       </c>
       <c r="S174" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>
@@ -21502,7 +21493,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -21512,12 +21503,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>09:49</t>
-        </is>
-      </c>
-      <c r="AC174" t="inlineStr">
-        <is>
-          <t>På grov gammal gran</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -21532,12 +21518,12 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
@@ -21655,53 +21641,45 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>134171973</v>
+        <v>134163087</v>
       </c>
       <c r="B176" t="n">
-        <v>57162</v>
+        <v>89340</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>100138</v>
+        <v>510</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K176" t="inlineStr"/>
-      <c r="L176" t="inlineStr"/>
-      <c r="M176" t="inlineStr"/>
-      <c r="N176" t="inlineStr"/>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>460716</v>
+        <v>460736</v>
       </c>
       <c r="R176" t="n">
-        <v>7051811</v>
+        <v>7052124</v>
       </c>
       <c r="S176" t="n">
         <v>3</v>
@@ -21733,7 +21711,7 @@
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -21743,12 +21721,12 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AC176" t="inlineStr">
         <is>
-          <t>1 ex uppflog</t>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -21763,12 +21741,12 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
@@ -21896,7 +21874,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>134171960</v>
+        <v>134160600</v>
       </c>
       <c r="B178" t="n">
         <v>79359</v>
@@ -21924,20 +21902,29 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I178" t="inlineStr"/>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>460692</v>
+        <v>460703</v>
       </c>
       <c r="R178" t="n">
-        <v>7052417</v>
+        <v>7051878</v>
       </c>
       <c r="S178" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
@@ -21966,7 +21953,7 @@
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -21976,7 +21963,12 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AC178" t="inlineStr">
+        <is>
+          <t>På grov gammal gran</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -21991,57 +21983,65 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>134163087</v>
+        <v>134171973</v>
       </c>
       <c r="B179" t="n">
-        <v>89340</v>
+        <v>57162</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>510</v>
+        <v>100138</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I179" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" t="inlineStr"/>
+      <c r="N179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>460736</v>
+        <v>460716</v>
       </c>
       <c r="R179" t="n">
-        <v>7052124</v>
+        <v>7051811</v>
       </c>
       <c r="S179" t="n">
         <v>3</v>
@@ -22073,7 +22073,7 @@
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
@@ -22083,12 +22083,12 @@
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AC179" t="inlineStr">
         <is>
-          <t>På gammal granlåga</t>
+          <t>1 ex uppflog</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -22103,22 +22103,22 @@
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>134162652</v>
+        <v>134161245</v>
       </c>
       <c r="B180" t="n">
-        <v>79359</v>
+        <v>83208</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -22126,46 +22126,37 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="J180" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>460812</v>
+        <v>460664</v>
       </c>
       <c r="R180" t="n">
-        <v>7052075</v>
+        <v>7051927</v>
       </c>
       <c r="S180" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T180" t="inlineStr">
         <is>
@@ -22194,7 +22185,7 @@
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
@@ -22204,12 +22195,12 @@
       </c>
       <c r="AB180" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AC180" t="inlineStr">
         <is>
-          <t>Gammal gran draperad med garnlav, i gammal gles granskog</t>
+          <t>På död gammal gran</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -22224,19 +22215,19 @@
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>134165861</v>
+        <v>134162652</v>
       </c>
       <c r="B181" t="n">
         <v>79359</v>
@@ -22264,17 +22255,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I181" t="inlineStr"/>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>460714</v>
+        <v>460812</v>
       </c>
       <c r="R181" t="n">
-        <v>7052420</v>
+        <v>7052075</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -22306,7 +22306,7 @@
       </c>
       <c r="Z181" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
@@ -22316,12 +22316,12 @@
       </c>
       <c r="AB181" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AC181" t="inlineStr">
         <is>
-          <t>På gammal grov gran, 70 cm i diameter, i gammal bördig granskog</t>
+          <t>Gammal gran draperad med garnlav, i gammal gles granskog</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -22348,32 +22348,32 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>134165723</v>
+        <v>134165861</v>
       </c>
       <c r="B182" t="n">
-        <v>80430</v>
+        <v>79359</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>229748</v>
+        <v>6425</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -22383,10 +22383,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>460711</v>
+        <v>460714</v>
       </c>
       <c r="R182" t="n">
-        <v>7052457</v>
+        <v>7052420</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -22418,7 +22418,7 @@
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
@@ -22428,12 +22428,12 @@
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AC182" t="inlineStr">
         <is>
-          <t>På gammal rönn i gammal granskog</t>
+          <t>På gammal grov gran, 70 cm i diameter, i gammal bördig granskog</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -22460,48 +22460,48 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>134161245</v>
+        <v>134165723</v>
       </c>
       <c r="B183" t="n">
-        <v>83208</v>
+        <v>80430</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>1312</v>
+        <v>229748</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>460664</v>
+        <v>460711</v>
       </c>
       <c r="R183" t="n">
-        <v>7051927</v>
+        <v>7052457</v>
       </c>
       <c r="S183" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -22530,7 +22530,7 @@
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
@@ -22540,12 +22540,12 @@
       </c>
       <c r="AB183" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AC183" t="inlineStr">
         <is>
-          <t>På död gammal gran</t>
+          <t>På gammal rönn i gammal granskog</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -22560,12 +22560,12 @@
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
@@ -22805,10 +22805,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>134171972</v>
+        <v>134161962</v>
       </c>
       <c r="B186" t="n">
-        <v>79359</v>
+        <v>83208</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -22816,37 +22816,37 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>460714</v>
+        <v>460653</v>
       </c>
       <c r="R186" t="n">
-        <v>7051804</v>
+        <v>7051927</v>
       </c>
       <c r="S186" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -22875,7 +22875,7 @@
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
@@ -22885,12 +22885,12 @@
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AC186" t="inlineStr">
         <is>
-          <t>1000 ex fördelat på 10 granar i gammal garnlavsrik granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -22905,12 +22905,12 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
@@ -23146,10 +23146,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>134161962</v>
+        <v>134171972</v>
       </c>
       <c r="B189" t="n">
-        <v>83208</v>
+        <v>79359</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -23157,37 +23157,37 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>460653</v>
+        <v>460714</v>
       </c>
       <c r="R189" t="n">
-        <v>7051927</v>
+        <v>7051804</v>
       </c>
       <c r="S189" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -23216,7 +23216,7 @@
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
@@ -23226,12 +23226,12 @@
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AC189" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>1000 ex fördelat på 10 granar i gammal garnlavsrik granskog</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -23246,12 +23246,12 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
@@ -23365,10 +23365,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>134162546</v>
+        <v>134162490</v>
       </c>
       <c r="B191" t="n">
-        <v>79359</v>
+        <v>91960</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -23376,46 +23376,37 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J191" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>460804</v>
+        <v>460806</v>
       </c>
       <c r="R191" t="n">
-        <v>7052009</v>
+        <v>7052008</v>
       </c>
       <c r="S191" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -23444,7 +23435,7 @@
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
@@ -23454,12 +23445,12 @@
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AC191" t="inlineStr">
         <is>
-          <t>Fördelat på 5 gamla granar</t>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -23486,10 +23477,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>134162490</v>
+        <v>134161368</v>
       </c>
       <c r="B192" t="n">
-        <v>91960</v>
+        <v>79359</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -23497,37 +23488,46 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I192" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P192" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>460806</v>
+        <v>460664</v>
       </c>
       <c r="R192" t="n">
-        <v>7052008</v>
+        <v>7051927</v>
       </c>
       <c r="S192" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -23556,7 +23556,7 @@
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -23566,12 +23566,12 @@
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AC192" t="inlineStr">
         <is>
-          <t>På gammal granlåga</t>
+          <t>På grov gammal gran</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -23591,14 +23591,14 @@
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>134161368</v>
+        <v>134162546</v>
       </c>
       <c r="B193" t="n">
         <v>79359</v>
@@ -23628,7 +23628,7 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
@@ -23642,13 +23642,13 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>460664</v>
+        <v>460804</v>
       </c>
       <c r="R193" t="n">
-        <v>7051927</v>
+        <v>7052009</v>
       </c>
       <c r="S193" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -23677,7 +23677,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -23687,12 +23687,12 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AC193" t="inlineStr">
         <is>
-          <t>På grov gammal gran</t>
+          <t>Fördelat på 5 gamla granar</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -23712,14 +23712,14 @@
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>134162379</v>
+        <v>134160932</v>
       </c>
       <c r="B194" t="n">
         <v>79359</v>
@@ -23749,7 +23749,7 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>400</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -23759,17 +23759,17 @@
       </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>460792</v>
+        <v>460672</v>
       </c>
       <c r="R194" t="n">
-        <v>7052051</v>
+        <v>7051901</v>
       </c>
       <c r="S194" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -23798,7 +23798,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -23808,12 +23808,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>10:58</t>
-        </is>
-      </c>
-      <c r="AC194" t="inlineStr">
-        <is>
-          <t>På gammal död gran (25 cm dbh) i gammal granskog</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -23828,12 +23823,12 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
@@ -23961,27 +23956,27 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>134171968</v>
+        <v>134162379</v>
       </c>
       <c r="B196" t="n">
-        <v>80485</v>
+        <v>79359</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -23989,20 +23984,29 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I196" t="inlineStr"/>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>460675</v>
+        <v>460792</v>
       </c>
       <c r="R196" t="n">
-        <v>7051857</v>
+        <v>7052051</v>
       </c>
       <c r="S196" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T196" t="inlineStr">
         <is>
@@ -24031,7 +24035,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -24041,12 +24045,12 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AC196" t="inlineStr">
         <is>
-          <t>På gammal levande rönn i gammal granskog</t>
+          <t>På gammal död gran (25 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -24073,10 +24077,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>134160932</v>
+        <v>134166396</v>
       </c>
       <c r="B197" t="n">
-        <v>79359</v>
+        <v>57975</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -24084,46 +24088,42 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="J197" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr"/>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>460672</v>
+        <v>460693</v>
       </c>
       <c r="R197" t="n">
-        <v>7051901</v>
+        <v>7052473</v>
       </c>
       <c r="S197" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T197" t="inlineStr">
         <is>
@@ -24152,7 +24152,7 @@
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -24162,7 +24162,12 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AC197" t="inlineStr">
+        <is>
+          <t>Ringhack på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -24177,65 +24182,60 @@
       <c r="AT197" t="inlineStr"/>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>134166396</v>
+        <v>134171968</v>
       </c>
       <c r="B198" t="n">
-        <v>57975</v>
+        <v>80485</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
-      <c r="M198" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>460693</v>
+        <v>460675</v>
       </c>
       <c r="R198" t="n">
-        <v>7052473</v>
+        <v>7051857</v>
       </c>
       <c r="S198" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
@@ -24264,7 +24264,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -24274,12 +24274,12 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AC198" t="inlineStr">
         <is>
-          <t>Ringhack på gammal levande gran i gammal granskog</t>
+          <t>På gammal levande rönn i gammal granskog</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -24413,7 +24413,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>134190545</v>
+        <v>134188076</v>
       </c>
       <c r="B200" t="n">
         <v>79359</v>
@@ -24441,26 +24441,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I200" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J200" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>460801</v>
+        <v>460747</v>
       </c>
       <c r="R200" t="n">
-        <v>7052035</v>
+        <v>7052190</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -24492,7 +24483,7 @@
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
@@ -24502,12 +24493,7 @@
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>11:01</t>
-        </is>
-      </c>
-      <c r="AC200" t="inlineStr">
-        <is>
-          <t>På gammal gran i garnlavsrik granskog</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -24534,7 +24520,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>134188076</v>
+        <v>134190545</v>
       </c>
       <c r="B201" t="n">
         <v>79359</v>
@@ -24562,17 +24548,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I201" t="inlineStr"/>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P201" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>460747</v>
+        <v>460801</v>
       </c>
       <c r="R201" t="n">
-        <v>7052190</v>
+        <v>7052035</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -24604,7 +24599,7 @@
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
@@ -24614,7 +24609,12 @@
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AC201" t="inlineStr">
+        <is>
+          <t>På gammal gran i garnlavsrik granskog</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -25889,7 +25889,7 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>134190741</v>
+        <v>134188053</v>
       </c>
       <c r="B213" t="n">
         <v>79359</v>
@@ -25917,26 +25917,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I213" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J213" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I213" t="inlineStr"/>
       <c r="P213" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>460702</v>
+        <v>460762</v>
       </c>
       <c r="R213" t="n">
-        <v>7051819</v>
+        <v>7052283</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -25968,7 +25959,7 @@
       </c>
       <c r="Z213" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
@@ -25978,7 +25969,7 @@
       </c>
       <c r="AB213" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -26005,7 +25996,7 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>134190569</v>
+        <v>134190579</v>
       </c>
       <c r="B214" t="n">
         <v>79359</v>
@@ -26033,26 +26024,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I214" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J214" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>460773</v>
+        <v>460635</v>
       </c>
       <c r="R214" t="n">
-        <v>7052035</v>
+        <v>7052005</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -26084,7 +26066,7 @@
       </c>
       <c r="Z214" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
@@ -26094,7 +26076,7 @@
       </c>
       <c r="AB214" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -26121,7 +26103,7 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>134190579</v>
+        <v>134188004</v>
       </c>
       <c r="B215" t="n">
         <v>79359</v>
@@ -26156,10 +26138,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>460635</v>
+        <v>460734</v>
       </c>
       <c r="R215" t="n">
-        <v>7052005</v>
+        <v>7052252</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -26191,7 +26173,7 @@
       </c>
       <c r="Z215" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
@@ -26201,7 +26183,7 @@
       </c>
       <c r="AB215" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -26228,7 +26210,7 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>134188053</v>
+        <v>134190741</v>
       </c>
       <c r="B216" t="n">
         <v>79359</v>
@@ -26256,17 +26238,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I216" t="inlineStr"/>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P216" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>460762</v>
+        <v>460702</v>
       </c>
       <c r="R216" t="n">
-        <v>7052283</v>
+        <v>7051819</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -26298,7 +26289,7 @@
       </c>
       <c r="Z216" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
@@ -26308,7 +26299,7 @@
       </c>
       <c r="AB216" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -26335,7 +26326,7 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>134188004</v>
+        <v>134190569</v>
       </c>
       <c r="B217" t="n">
         <v>79359</v>
@@ -26363,17 +26354,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I217" t="inlineStr"/>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P217" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>460734</v>
+        <v>460773</v>
       </c>
       <c r="R217" t="n">
-        <v>7052252</v>
+        <v>7052035</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -26405,7 +26405,7 @@
       </c>
       <c r="Z217" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
@@ -26415,7 +26415,7 @@
       </c>
       <c r="AB217" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD217" t="b">

--- a/artfynd/A 51504-2025 artfynd.xlsx
+++ b/artfynd/A 51504-2025 artfynd.xlsx
@@ -16023,7 +16023,7 @@
         <v>134159342</v>
       </c>
       <c r="B126" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -16136,62 +16136,48 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>134161617</v>
+        <v>134171971</v>
       </c>
       <c r="B127" t="n">
-        <v>79359</v>
+        <v>96406</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>460738</v>
+        <v>460688</v>
       </c>
       <c r="R127" t="n">
-        <v>7051903</v>
+        <v>7051821</v>
       </c>
       <c r="S127" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -16220,7 +16206,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -16230,12 +16216,12 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>Fördelat på 2 gamla granar</t>
+          <t>På marken i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -16250,60 +16236,74 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>134171971</v>
+        <v>134161617</v>
       </c>
       <c r="B128" t="n">
-        <v>96399</v>
+        <v>79366</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>460688</v>
+        <v>460738</v>
       </c>
       <c r="R128" t="n">
-        <v>7051821</v>
+        <v>7051903</v>
       </c>
       <c r="S128" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -16332,7 +16332,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -16342,12 +16342,12 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>På marken i gammal fuktig granskog</t>
+          <t>Fördelat på 2 gamla granar</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -16362,74 +16362,60 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>134165576</v>
+        <v>134161325</v>
       </c>
       <c r="B129" t="n">
-        <v>57975</v>
+        <v>99210</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L129" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>460650</v>
+        <v>460664</v>
       </c>
       <c r="R129" t="n">
-        <v>7052431</v>
+        <v>7051927</v>
       </c>
       <c r="S129" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -16458,7 +16444,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -16468,7 +16454,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -16488,55 +16474,60 @@
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>134161325</v>
+        <v>134165432</v>
       </c>
       <c r="B130" t="n">
-        <v>99203</v>
+        <v>79798</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>221952</v>
+        <v>1778</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fjällig knopplav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Biatora fallax</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Hepp</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>460664</v>
+        <v>460673</v>
       </c>
       <c r="R130" t="n">
-        <v>7051927</v>
+        <v>7052450</v>
       </c>
       <c r="S130" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -16565,7 +16556,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -16575,7 +16566,12 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>På bark vid basen av gammal levande grov gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -16590,60 +16586,69 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>134165125</v>
+        <v>134166248</v>
       </c>
       <c r="B131" t="n">
-        <v>99203</v>
+        <v>79366</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>460690</v>
+        <v>460708</v>
       </c>
       <c r="R131" t="n">
-        <v>7052375</v>
+        <v>7052503</v>
       </c>
       <c r="S131" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -16672,7 +16677,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -16682,7 +16687,12 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -16697,69 +16707,60 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>134162895</v>
+        <v>134159098</v>
       </c>
       <c r="B132" t="n">
-        <v>79359</v>
+        <v>80437</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>229748</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>460789</v>
+        <v>460718</v>
       </c>
       <c r="R132" t="n">
-        <v>7051975</v>
+        <v>7051777</v>
       </c>
       <c r="S132" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -16788,7 +16789,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -16798,7 +16799,12 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:08</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>På död, klen rönn</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -16825,53 +16831,48 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>134165432</v>
+        <v>134165125</v>
       </c>
       <c r="B133" t="n">
-        <v>79791</v>
+        <v>99210</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1778</v>
+        <v>221952</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Fjällig knopplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Biatora fallax</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Hepp</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>460673</v>
+        <v>460690</v>
       </c>
       <c r="R133" t="n">
-        <v>7052450</v>
+        <v>7052375</v>
       </c>
       <c r="S133" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -16900,7 +16901,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -16910,12 +16911,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>12:42</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>På bark vid basen av gammal levande grov gran i gammal granskog</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -16930,22 +16926,22 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>134166248</v>
+        <v>134165576</v>
       </c>
       <c r="B134" t="n">
-        <v>79359</v>
+        <v>57975</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16953,31 +16949,36 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
@@ -16986,10 +16987,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>460708</v>
+        <v>460650</v>
       </c>
       <c r="R134" t="n">
-        <v>7052503</v>
+        <v>7052431</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -17021,7 +17022,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -17031,12 +17032,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>13:18</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -17051,60 +17047,69 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>134159098</v>
+        <v>134162895</v>
       </c>
       <c r="B135" t="n">
-        <v>80430</v>
+        <v>79366</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>229748</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>460718</v>
+        <v>460789</v>
       </c>
       <c r="R135" t="n">
-        <v>7051777</v>
+        <v>7051975</v>
       </c>
       <c r="S135" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -17133,7 +17138,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -17143,12 +17148,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>09:08</t>
-        </is>
-      </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>På död, klen rönn</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -17175,10 +17175,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>134165214</v>
+        <v>134159178</v>
       </c>
       <c r="B136" t="n">
-        <v>80479</v>
+        <v>80486</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -17206,17 +17206,17 @@
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>460690</v>
+        <v>460683</v>
       </c>
       <c r="R136" t="n">
-        <v>7052375</v>
+        <v>7051835</v>
       </c>
       <c r="S136" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -17245,7 +17245,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -17255,12 +17255,12 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AC136" t="inlineStr">
         <is>
-          <t>På rönn</t>
+          <t>På död, klen rönn</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -17287,10 +17287,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>134159178</v>
+        <v>134158960</v>
       </c>
       <c r="B137" t="n">
-        <v>80479</v>
+        <v>80485</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -17298,21 +17298,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6462</v>
+        <v>6461</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -17322,13 +17322,13 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>460683</v>
+        <v>460718</v>
       </c>
       <c r="R137" t="n">
-        <v>7051835</v>
+        <v>7051777</v>
       </c>
       <c r="S137" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -17357,7 +17357,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -17367,12 +17367,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>09:09</t>
-        </is>
-      </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>På död, klen rönn</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -17399,10 +17394,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>134158960</v>
+        <v>134165214</v>
       </c>
       <c r="B138" t="n">
-        <v>80478</v>
+        <v>80486</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -17410,37 +17405,37 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6461</v>
+        <v>6462</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>460718</v>
+        <v>460690</v>
       </c>
       <c r="R138" t="n">
-        <v>7051777</v>
+        <v>7052375</v>
       </c>
       <c r="S138" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -17469,7 +17464,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -17479,7 +17474,12 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>På rönn</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -17509,7 +17509,7 @@
         <v>134171947</v>
       </c>
       <c r="B139" t="n">
-        <v>80486</v>
+        <v>80493</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17621,7 +17621,7 @@
         <v>134171951</v>
       </c>
       <c r="B140" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17728,7 +17728,7 @@
         <v>134165139</v>
       </c>
       <c r="B141" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17844,7 +17844,7 @@
         <v>134166744</v>
       </c>
       <c r="B142" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17965,7 +17965,7 @@
         <v>134162493</v>
       </c>
       <c r="B143" t="n">
-        <v>80478</v>
+        <v>80485</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -18069,57 +18069,48 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>134163868</v>
+        <v>134165713</v>
       </c>
       <c r="B144" t="n">
-        <v>79359</v>
+        <v>80486</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>460752</v>
+        <v>460711</v>
       </c>
       <c r="R144" t="n">
-        <v>7052276</v>
+        <v>7052457</v>
       </c>
       <c r="S144" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -18148,7 +18139,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -18158,12 +18149,12 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>Rikligt på gammal levande grov gran (45 cm dbh) i gammal granskog</t>
+          <t>På gammal rönn i gammal granskog</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -18190,10 +18181,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>134165713</v>
+        <v>134171966</v>
       </c>
       <c r="B145" t="n">
-        <v>80479</v>
+        <v>80437</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -18201,37 +18192,37 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6462</v>
+        <v>229748</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>460711</v>
+        <v>460676</v>
       </c>
       <c r="R145" t="n">
-        <v>7052457</v>
+        <v>7051857</v>
       </c>
       <c r="S145" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -18260,7 +18251,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -18270,12 +18261,12 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>På gammal rönn i gammal granskog</t>
+          <t>På rönn i gammal granskog</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -18302,48 +18293,57 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>134171966</v>
+        <v>134163868</v>
       </c>
       <c r="B146" t="n">
-        <v>80430</v>
+        <v>79366</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>229748</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>460676</v>
+        <v>460752</v>
       </c>
       <c r="R146" t="n">
-        <v>7051857</v>
+        <v>7052276</v>
       </c>
       <c r="S146" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -18372,7 +18372,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -18382,12 +18382,12 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>På rönn i gammal granskog</t>
+          <t>Rikligt på gammal levande grov gran (45 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -18414,10 +18414,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>134166104</v>
+        <v>134171976</v>
       </c>
       <c r="B147" t="n">
-        <v>99203</v>
+        <v>99210</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -18445,17 +18445,17 @@
       <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>460692</v>
+        <v>460751</v>
       </c>
       <c r="R147" t="n">
-        <v>7052457</v>
+        <v>7051437</v>
       </c>
       <c r="S147" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -18484,7 +18484,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -18494,7 +18494,12 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>På marken i äldre granskog</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -18509,22 +18514,22 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>134158853</v>
+        <v>134171965</v>
       </c>
       <c r="B148" t="n">
-        <v>99203</v>
+        <v>106302</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -18532,37 +18537,37 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>221952</v>
+        <v>221725</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>460723</v>
+        <v>460691</v>
       </c>
       <c r="R148" t="n">
-        <v>7051736</v>
+        <v>7051813</v>
       </c>
       <c r="S148" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -18591,7 +18596,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -18601,7 +18606,12 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -18616,22 +18626,22 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>134171976</v>
+        <v>134158853</v>
       </c>
       <c r="B149" t="n">
-        <v>99203</v>
+        <v>99210</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -18659,14 +18669,14 @@
       <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>460751</v>
+        <v>460723</v>
       </c>
       <c r="R149" t="n">
-        <v>7051437</v>
+        <v>7051736</v>
       </c>
       <c r="S149" t="n">
         <v>3</v>
@@ -18698,7 +18708,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -18708,12 +18718,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="AC149" t="inlineStr">
-        <is>
-          <t>På marken i äldre granskog</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -18728,22 +18733,22 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>134171965</v>
+        <v>134166104</v>
       </c>
       <c r="B150" t="n">
-        <v>106295</v>
+        <v>99210</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18751,37 +18756,37 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>221725</v>
+        <v>221952</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>460691</v>
+        <v>460692</v>
       </c>
       <c r="R150" t="n">
-        <v>7051813</v>
+        <v>7052457</v>
       </c>
       <c r="S150" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -18810,7 +18815,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -18820,12 +18825,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>10:21</t>
-        </is>
-      </c>
-      <c r="AC150" t="inlineStr">
-        <is>
-          <t>På marken i gammal granskog</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -18840,60 +18840,69 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>134161209</v>
+        <v>134163277</v>
       </c>
       <c r="B151" t="n">
-        <v>91923</v>
+        <v>79366</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>460668</v>
+        <v>460726</v>
       </c>
       <c r="R151" t="n">
-        <v>7051920</v>
+        <v>7052196</v>
       </c>
       <c r="S151" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -18922,7 +18931,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -18932,7 +18941,12 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>Fördelat på 3 gamla granar</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -18959,10 +18973,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>134163277</v>
+        <v>134161529</v>
       </c>
       <c r="B152" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18989,7 +19003,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>400</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -18999,17 +19013,17 @@
       </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>460726</v>
+        <v>460757</v>
       </c>
       <c r="R152" t="n">
-        <v>7052196</v>
+        <v>7051937</v>
       </c>
       <c r="S152" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -19038,7 +19052,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -19048,7 +19062,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AC152" t="inlineStr">
@@ -19073,17 +19087,17 @@
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>134161529</v>
+        <v>134171956</v>
       </c>
       <c r="B153" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -19108,29 +19122,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="J153" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>460757</v>
+        <v>460688</v>
       </c>
       <c r="R153" t="n">
-        <v>7051937</v>
+        <v>7052421</v>
       </c>
       <c r="S153" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -19159,7 +19164,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -19169,12 +19174,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>10:31</t>
-        </is>
-      </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>Fördelat på 3 gamla granar</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -19189,69 +19189,60 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>134162816</v>
+        <v>134171946</v>
       </c>
       <c r="B154" t="n">
-        <v>79359</v>
+        <v>80486</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="J154" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>460812</v>
+        <v>460716</v>
       </c>
       <c r="R154" t="n">
-        <v>7052078</v>
+        <v>7052447</v>
       </c>
       <c r="S154" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -19280,7 +19271,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -19290,12 +19281,12 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AC154" t="inlineStr">
         <is>
-          <t>Gammal död gran (ca 23 cm dbh) draperad med garnlav i gammal gles granskog</t>
+          <t>På rönnlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -19322,48 +19313,57 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>134171946</v>
+        <v>134162816</v>
       </c>
       <c r="B155" t="n">
-        <v>80479</v>
+        <v>79366</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>460716</v>
+        <v>460812</v>
       </c>
       <c r="R155" t="n">
-        <v>7052447</v>
+        <v>7052078</v>
       </c>
       <c r="S155" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -19392,7 +19392,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -19402,12 +19402,12 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AC155" t="inlineStr">
         <is>
-          <t>På rönnlåga i gammal granskog</t>
+          <t>Gammal död gran (ca 23 cm dbh) draperad med garnlav i gammal gles granskog</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -19437,7 +19437,7 @@
         <v>134171970</v>
       </c>
       <c r="B156" t="n">
-        <v>101389</v>
+        <v>101396</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -19546,48 +19546,48 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>134171956</v>
+        <v>134161209</v>
       </c>
       <c r="B157" t="n">
-        <v>79359</v>
+        <v>91930</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>460688</v>
+        <v>460668</v>
       </c>
       <c r="R157" t="n">
-        <v>7052421</v>
+        <v>7051920</v>
       </c>
       <c r="S157" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -19616,7 +19616,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -19626,7 +19626,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -19641,12 +19641,12 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
@@ -19770,10 +19770,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>134166640</v>
+        <v>134171949</v>
       </c>
       <c r="B159" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19798,29 +19798,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="J159" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>460776</v>
+        <v>460691</v>
       </c>
       <c r="R159" t="n">
-        <v>7052247</v>
+        <v>7052421</v>
       </c>
       <c r="S159" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -19849,7 +19840,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -19859,7 +19850,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -19874,22 +19865,22 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>134171949</v>
+        <v>134166640</v>
       </c>
       <c r="B160" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -19914,20 +19905,29 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I160" t="inlineStr"/>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>460691</v>
+        <v>460776</v>
       </c>
       <c r="R160" t="n">
-        <v>7052421</v>
+        <v>7052247</v>
       </c>
       <c r="S160" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -19956,7 +19956,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -19966,7 +19966,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -19981,12 +19981,12 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
@@ -19996,7 +19996,7 @@
         <v>134171952</v>
       </c>
       <c r="B161" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -20100,10 +20100,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>134160980</v>
+        <v>134171954</v>
       </c>
       <c r="B162" t="n">
-        <v>83344</v>
+        <v>79366</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -20111,37 +20111,37 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>460672</v>
+        <v>460686</v>
       </c>
       <c r="R162" t="n">
-        <v>7051901</v>
+        <v>7052421</v>
       </c>
       <c r="S162" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -20170,7 +20170,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -20180,12 +20180,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC162" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -20200,60 +20195,60 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>134165091</v>
+        <v>134160980</v>
       </c>
       <c r="B163" t="n">
-        <v>91923</v>
+        <v>83351</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>460690</v>
+        <v>460672</v>
       </c>
       <c r="R163" t="n">
-        <v>7052375</v>
+        <v>7051901</v>
       </c>
       <c r="S163" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -20282,7 +20277,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -20292,7 +20287,12 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC163" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -20319,48 +20319,48 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>134171954</v>
+        <v>134165091</v>
       </c>
       <c r="B164" t="n">
-        <v>79359</v>
+        <v>91930</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>460686</v>
+        <v>460690</v>
       </c>
       <c r="R164" t="n">
-        <v>7052421</v>
+        <v>7052375</v>
       </c>
       <c r="S164" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -20389,7 +20389,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -20399,7 +20399,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -20414,69 +20414,60 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>134158548</v>
+        <v>134171967</v>
       </c>
       <c r="B165" t="n">
-        <v>99181</v>
+        <v>80486</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="J165" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>460863</v>
+        <v>460677</v>
       </c>
       <c r="R165" t="n">
-        <v>7051485</v>
+        <v>7051857</v>
       </c>
       <c r="S165" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -20505,7 +20496,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -20515,7 +20506,12 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>09:16</t>
+        </is>
+      </c>
+      <c r="AC165" t="inlineStr">
+        <is>
+          <t>På gammal levande rönn i gammal granskog</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -20530,44 +20526,44 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>134171967</v>
+        <v>134171957</v>
       </c>
       <c r="B166" t="n">
-        <v>80479</v>
+        <v>79366</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -20577,13 +20573,13 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>460677</v>
+        <v>460698</v>
       </c>
       <c r="R166" t="n">
-        <v>7051857</v>
+        <v>7052420</v>
       </c>
       <c r="S166" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -20612,7 +20608,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -20622,12 +20618,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>09:16</t>
-        </is>
-      </c>
-      <c r="AC166" t="inlineStr">
-        <is>
-          <t>På gammal levande rönn i gammal granskog</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -20654,48 +20645,57 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>134171957</v>
+        <v>134158548</v>
       </c>
       <c r="B167" t="n">
-        <v>79359</v>
+        <v>99188</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>460698</v>
+        <v>460863</v>
       </c>
       <c r="R167" t="n">
-        <v>7052420</v>
+        <v>7051485</v>
       </c>
       <c r="S167" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -20724,7 +20724,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -20749,12 +20749,12 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
@@ -20764,7 +20764,7 @@
         <v>134158911</v>
       </c>
       <c r="B168" t="n">
-        <v>99203</v>
+        <v>99210</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -20868,45 +20868,45 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>134171955</v>
+        <v>134159322</v>
       </c>
       <c r="B169" t="n">
-        <v>79359</v>
+        <v>99210</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>460685</v>
+        <v>460672</v>
       </c>
       <c r="R169" t="n">
-        <v>7052421</v>
+        <v>7051847</v>
       </c>
       <c r="S169" t="n">
         <v>3</v>
@@ -20938,7 +20938,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -20948,7 +20948,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -20963,60 +20963,65 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>134159322</v>
+        <v>134163852</v>
       </c>
       <c r="B170" t="n">
-        <v>99203</v>
+        <v>57975</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>460672</v>
+        <v>460763</v>
       </c>
       <c r="R170" t="n">
-        <v>7051847</v>
+        <v>7052266</v>
       </c>
       <c r="S170" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -21045,7 +21050,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -21055,7 +21060,12 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -21082,10 +21092,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>134163852</v>
+        <v>134171955</v>
       </c>
       <c r="B171" t="n">
-        <v>57975</v>
+        <v>79366</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -21093,42 +21103,37 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>460763</v>
+        <v>460685</v>
       </c>
       <c r="R171" t="n">
-        <v>7052266</v>
+        <v>7052421</v>
       </c>
       <c r="S171" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -21157,7 +21162,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -21167,12 +21172,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>11:49</t>
-        </is>
-      </c>
-      <c r="AC171" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -21187,60 +21187,60 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>134164951</v>
+        <v>134171974</v>
       </c>
       <c r="B172" t="n">
-        <v>96409</v>
+        <v>79985</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>2810</v>
+        <v>6453</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>460763</v>
+        <v>460722</v>
       </c>
       <c r="R172" t="n">
-        <v>7052266</v>
+        <v>7051751</v>
       </c>
       <c r="S172" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -21269,7 +21269,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -21279,12 +21279,12 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AC172" t="inlineStr">
         <is>
-          <t>På block i kanten av lok</t>
+          <t>På dimensionsavverkningsstubbe av tall i gammal garnlavsrik granskog</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -21299,60 +21299,60 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>134171974</v>
+        <v>134164951</v>
       </c>
       <c r="B173" t="n">
-        <v>79978</v>
+        <v>96416</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6453</v>
+        <v>2810</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>460722</v>
+        <v>460763</v>
       </c>
       <c r="R173" t="n">
-        <v>7051751</v>
+        <v>7052266</v>
       </c>
       <c r="S173" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -21381,7 +21381,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -21391,12 +21391,12 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AC173" t="inlineStr">
         <is>
-          <t>På dimensionsavverkningsstubbe av tall i gammal garnlavsrik granskog</t>
+          <t>På block i kanten av lok</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -21411,57 +21411,65 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>134171960</v>
+        <v>134171973</v>
       </c>
       <c r="B174" t="n">
-        <v>79359</v>
+        <v>57162</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" t="inlineStr"/>
+      <c r="N174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>460692</v>
+        <v>460716</v>
       </c>
       <c r="R174" t="n">
-        <v>7052417</v>
+        <v>7051811</v>
       </c>
       <c r="S174" t="n">
         <v>3</v>
@@ -21493,7 +21501,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -21503,7 +21511,12 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>08:59</t>
+        </is>
+      </c>
+      <c r="AC174" t="inlineStr">
+        <is>
+          <t>1 ex uppflog</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -21530,52 +21543,57 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>134165583</v>
+        <v>134161522</v>
       </c>
       <c r="B175" t="n">
-        <v>58079</v>
+        <v>79366</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>460650</v>
+        <v>460702</v>
       </c>
       <c r="R175" t="n">
-        <v>7052431</v>
+        <v>7051854</v>
       </c>
       <c r="S175" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T175" t="inlineStr">
         <is>
@@ -21604,7 +21622,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -21614,7 +21632,12 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AC175" t="inlineStr">
+        <is>
+          <t>Rikligt, draperat, på de flesta granar i gammal flerskiktad granskog</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -21629,22 +21652,22 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>134163087</v>
+        <v>134171960</v>
       </c>
       <c r="B176" t="n">
-        <v>89340</v>
+        <v>79366</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -21652,34 +21675,34 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>460736</v>
+        <v>460692</v>
       </c>
       <c r="R176" t="n">
-        <v>7052124</v>
+        <v>7052417</v>
       </c>
       <c r="S176" t="n">
         <v>3</v>
@@ -21711,7 +21734,7 @@
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -21721,12 +21744,7 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>11:21</t>
-        </is>
-      </c>
-      <c r="AC176" t="inlineStr">
-        <is>
-          <t>På gammal granlåga</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -21741,69 +21759,64 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>134161522</v>
+        <v>134165583</v>
       </c>
       <c r="B177" t="n">
-        <v>79359</v>
+        <v>58079</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J177" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>460702</v>
+        <v>460650</v>
       </c>
       <c r="R177" t="n">
-        <v>7051854</v>
+        <v>7052431</v>
       </c>
       <c r="S177" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -21832,7 +21845,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -21842,12 +21855,7 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="AC177" t="inlineStr">
-        <is>
-          <t>Rikligt, draperat, på de flesta granar i gammal flerskiktad granskog</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -21862,22 +21870,22 @@
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>134160600</v>
+        <v>134163087</v>
       </c>
       <c r="B178" t="n">
-        <v>79359</v>
+        <v>89347</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -21885,46 +21893,37 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="J178" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>460703</v>
+        <v>460736</v>
       </c>
       <c r="R178" t="n">
-        <v>7051878</v>
+        <v>7052124</v>
       </c>
       <c r="S178" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
@@ -21953,7 +21952,7 @@
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -21963,12 +21962,12 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AC178" t="inlineStr">
         <is>
-          <t>På grov gammal gran</t>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -21995,56 +21994,57 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>134171973</v>
+        <v>134160600</v>
       </c>
       <c r="B179" t="n">
-        <v>57162</v>
+        <v>79366</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K179" t="inlineStr"/>
-      <c r="L179" t="inlineStr"/>
-      <c r="M179" t="inlineStr"/>
-      <c r="N179" t="inlineStr"/>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>460716</v>
+        <v>460703</v>
       </c>
       <c r="R179" t="n">
-        <v>7051811</v>
+        <v>7051878</v>
       </c>
       <c r="S179" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -22073,7 +22073,7 @@
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
@@ -22083,12 +22083,12 @@
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AC179" t="inlineStr">
         <is>
-          <t>1 ex uppflog</t>
+          <t>På grov gammal gran</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -22103,22 +22103,22 @@
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>134161245</v>
+        <v>134162652</v>
       </c>
       <c r="B180" t="n">
-        <v>83208</v>
+        <v>79366</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -22126,37 +22126,46 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>460664</v>
+        <v>460812</v>
       </c>
       <c r="R180" t="n">
-        <v>7051927</v>
+        <v>7052075</v>
       </c>
       <c r="S180" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T180" t="inlineStr">
         <is>
@@ -22185,7 +22194,7 @@
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
@@ -22195,12 +22204,12 @@
       </c>
       <c r="AB180" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AC180" t="inlineStr">
         <is>
-          <t>På död gammal gran</t>
+          <t>Gammal gran draperad med garnlav, i gammal gles granskog</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -22215,22 +22224,22 @@
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>134162652</v>
+        <v>134165861</v>
       </c>
       <c r="B181" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -22255,26 +22264,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I181" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="J181" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>460812</v>
+        <v>460714</v>
       </c>
       <c r="R181" t="n">
-        <v>7052075</v>
+        <v>7052420</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -22306,7 +22306,7 @@
       </c>
       <c r="Z181" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
@@ -22316,12 +22316,12 @@
       </c>
       <c r="AB181" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AC181" t="inlineStr">
         <is>
-          <t>Gammal gran draperad med garnlav, i gammal gles granskog</t>
+          <t>På gammal grov gran, 70 cm i diameter, i gammal bördig granskog</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -22348,32 +22348,32 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>134165861</v>
+        <v>134165723</v>
       </c>
       <c r="B182" t="n">
-        <v>79359</v>
+        <v>80437</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6425</v>
+        <v>229748</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -22383,10 +22383,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>460714</v>
+        <v>460711</v>
       </c>
       <c r="R182" t="n">
-        <v>7052420</v>
+        <v>7052457</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -22418,7 +22418,7 @@
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
@@ -22428,12 +22428,12 @@
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AC182" t="inlineStr">
         <is>
-          <t>På gammal grov gran, 70 cm i diameter, i gammal bördig granskog</t>
+          <t>På gammal rönn i gammal granskog</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -22460,48 +22460,48 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>134165723</v>
+        <v>134161245</v>
       </c>
       <c r="B183" t="n">
-        <v>80430</v>
+        <v>83215</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>229748</v>
+        <v>1312</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>460711</v>
+        <v>460664</v>
       </c>
       <c r="R183" t="n">
-        <v>7052457</v>
+        <v>7051927</v>
       </c>
       <c r="S183" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -22530,7 +22530,7 @@
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
@@ -22540,12 +22540,12 @@
       </c>
       <c r="AB183" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AC183" t="inlineStr">
         <is>
-          <t>På gammal rönn i gammal granskog</t>
+          <t>På död gammal gran</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -22560,57 +22560,66 @@
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>134165966</v>
+        <v>134161669</v>
       </c>
       <c r="B184" t="n">
-        <v>79791</v>
+        <v>79366</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>1778</v>
+        <v>6425</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Fjällig knopplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Biatora fallax</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Hepp</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>460694</v>
+        <v>460693</v>
       </c>
       <c r="R184" t="n">
-        <v>7052451</v>
+        <v>7051901</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -22642,7 +22651,7 @@
       </c>
       <c r="Z184" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
@@ -22652,12 +22661,12 @@
       </c>
       <c r="AB184" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AC184" t="inlineStr">
         <is>
-          <t>På bark på rotben på gammal levande grov gran (55 cm dbh) i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -22684,54 +22693,45 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>134161669</v>
+        <v>134165966</v>
       </c>
       <c r="B185" t="n">
-        <v>79359</v>
+        <v>79798</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6425</v>
+        <v>1778</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällig knopplav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Biatora fallax</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J185" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Hepp</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>460693</v>
+        <v>460694</v>
       </c>
       <c r="R185" t="n">
-        <v>7051901</v>
+        <v>7052451</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -22763,7 +22763,7 @@
       </c>
       <c r="Z185" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
@@ -22773,12 +22773,12 @@
       </c>
       <c r="AB185" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AC185" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På bark på rotben på gammal levande grov gran (55 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -22805,48 +22805,48 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>134161962</v>
+        <v>134164962</v>
       </c>
       <c r="B186" t="n">
-        <v>83208</v>
+        <v>96406</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>1312</v>
+        <v>2809</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>460653</v>
+        <v>460763</v>
       </c>
       <c r="R186" t="n">
-        <v>7051927</v>
+        <v>7052266</v>
       </c>
       <c r="S186" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -22875,7 +22875,7 @@
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
@@ -22885,12 +22885,12 @@
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AC186" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På block i kanten av lok</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -22917,48 +22917,48 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>134164962</v>
+        <v>134171972</v>
       </c>
       <c r="B187" t="n">
-        <v>96399</v>
+        <v>79366</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>460763</v>
+        <v>460714</v>
       </c>
       <c r="R187" t="n">
-        <v>7052266</v>
+        <v>7051804</v>
       </c>
       <c r="S187" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -22987,7 +22987,7 @@
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
@@ -22997,12 +22997,12 @@
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AC187" t="inlineStr">
         <is>
-          <t>På block i kanten av lok</t>
+          <t>1000 ex fördelat på 10 granar i gammal garnlavsrik granskog</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -23017,22 +23017,22 @@
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>134163114</v>
+        <v>134161962</v>
       </c>
       <c r="B188" t="n">
-        <v>57975</v>
+        <v>83215</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -23040,39 +23040,34 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
-      <c r="M188" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P188" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>460736</v>
+        <v>460653</v>
       </c>
       <c r="R188" t="n">
-        <v>7052124</v>
+        <v>7051927</v>
       </c>
       <c r="S188" t="n">
         <v>4</v>
@@ -23104,7 +23099,7 @@
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
@@ -23114,12 +23109,12 @@
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AC188" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -23146,10 +23141,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>134171972</v>
+        <v>134163114</v>
       </c>
       <c r="B189" t="n">
-        <v>79359</v>
+        <v>57975</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -23157,37 +23152,42 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>460714</v>
+        <v>460736</v>
       </c>
       <c r="R189" t="n">
-        <v>7051804</v>
+        <v>7052124</v>
       </c>
       <c r="S189" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -23216,7 +23216,7 @@
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
@@ -23226,12 +23226,12 @@
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AC189" t="inlineStr">
         <is>
-          <t>1000 ex fördelat på 10 granar i gammal garnlavsrik granskog</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -23246,12 +23246,12 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
@@ -23261,7 +23261,7 @@
         <v>134171958</v>
       </c>
       <c r="B190" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -23368,7 +23368,7 @@
         <v>134162490</v>
       </c>
       <c r="B191" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -23480,7 +23480,7 @@
         <v>134161368</v>
       </c>
       <c r="B192" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -23601,7 +23601,7 @@
         <v>134162546</v>
       </c>
       <c r="B193" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -23719,10 +23719,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>134160932</v>
+        <v>134162379</v>
       </c>
       <c r="B194" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -23749,7 +23749,7 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -23759,17 +23759,17 @@
       </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Kampen, Kampen, Jmt</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>460672</v>
+        <v>460792</v>
       </c>
       <c r="R194" t="n">
-        <v>7051901</v>
+        <v>7052051</v>
       </c>
       <c r="S194" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -23798,7 +23798,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -23808,7 +23808,12 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AC194" t="inlineStr">
+        <is>
+          <t>På gammal död gran (25 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -23823,12 +23828,12 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
@@ -23838,7 +23843,7 @@
         <v>134162445</v>
       </c>
       <c r="B195" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -23956,10 +23961,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>134162379</v>
+        <v>134166396</v>
       </c>
       <c r="B196" t="n">
-        <v>79359</v>
+        <v>57975</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -23967,43 +23972,39 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I196" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J196" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr"/>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Kampen, Kampen, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>460792</v>
+        <v>460693</v>
       </c>
       <c r="R196" t="n">
-        <v>7052051</v>
+        <v>7052473</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -24035,7 +24036,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -24045,12 +24046,12 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AC196" t="inlineStr">
         <is>
-          <t>På gammal död gran (25 cm dbh) i gammal granskog</t>
+          <t>Ringhack på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -24077,53 +24078,48 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>134166396</v>
+        <v>134171968</v>
       </c>
       <c r="B197" t="n">
-        <v>57975</v>
+        <v>80492</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
-      <c r="M197" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>460693</v>
+        <v>460675</v>
       </c>
       <c r="R197" t="n">
-        <v>7052473</v>
+        <v>7051857</v>
       </c>
       <c r="S197" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T197" t="inlineStr">
         <is>
@@ -24152,7 +24148,7 @@
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -24162,12 +24158,12 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AC197" t="inlineStr">
         <is>
-          <t>Ringhack på gammal levande gran i gammal granskog</t>
+          <t>På gammal levande rönn i gammal granskog</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -24194,27 +24190,27 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>134171968</v>
+        <v>134160932</v>
       </c>
       <c r="B198" t="n">
-        <v>80485</v>
+        <v>79366</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -24222,20 +24218,29 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I198" t="inlineStr"/>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>460675</v>
+        <v>460672</v>
       </c>
       <c r="R198" t="n">
-        <v>7051857</v>
+        <v>7051901</v>
       </c>
       <c r="S198" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
@@ -24264,7 +24269,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -24274,12 +24279,7 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>09:16</t>
-        </is>
-      </c>
-      <c r="AC198" t="inlineStr">
-        <is>
-          <t>På gammal levande rönn i gammal granskog</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -24294,22 +24294,22 @@
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>134187980</v>
+        <v>134188076</v>
       </c>
       <c r="B199" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -24341,10 +24341,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>460749</v>
+        <v>460747</v>
       </c>
       <c r="R199" t="n">
-        <v>7052313</v>
+        <v>7052190</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -24376,7 +24376,7 @@
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -24386,7 +24386,7 @@
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -24413,10 +24413,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>134188076</v>
+        <v>134187980</v>
       </c>
       <c r="B200" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -24448,10 +24448,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>460747</v>
+        <v>460749</v>
       </c>
       <c r="R200" t="n">
-        <v>7052190</v>
+        <v>7052313</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -24483,7 +24483,7 @@
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
@@ -24493,7 +24493,7 @@
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -24523,7 +24523,7 @@
         <v>134190545</v>
       </c>
       <c r="B201" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -24644,7 +24644,7 @@
         <v>134188832</v>
       </c>
       <c r="B202" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -24760,7 +24760,7 @@
         <v>134187405</v>
       </c>
       <c r="B203" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -24881,7 +24881,7 @@
         <v>134187568</v>
       </c>
       <c r="B204" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -25002,7 +25002,7 @@
         <v>134187643</v>
       </c>
       <c r="B205" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -25114,7 +25114,7 @@
         <v>134190856</v>
       </c>
       <c r="B206" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -25211,7 +25211,7 @@
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
@@ -25221,7 +25221,7 @@
         <v>134187781</v>
       </c>
       <c r="B207" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -25333,7 +25333,7 @@
         <v>134187721</v>
       </c>
       <c r="B208" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -25442,10 +25442,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>134190717</v>
+        <v>134187536</v>
       </c>
       <c r="B209" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -25477,10 +25477,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>460688</v>
+        <v>460775</v>
       </c>
       <c r="R209" t="n">
-        <v>7051819</v>
+        <v>7052159</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -25512,7 +25512,7 @@
       </c>
       <c r="Z209" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
@@ -25522,7 +25522,12 @@
       </c>
       <c r="AB209" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC209" t="inlineStr">
+        <is>
+          <t>På gammal gran, 170-200 år, i gammal granskog</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -25552,7 +25557,7 @@
         <v>134187880</v>
       </c>
       <c r="B210" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -25656,10 +25661,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>134187536</v>
+        <v>134190717</v>
       </c>
       <c r="B211" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -25691,10 +25696,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>460775</v>
+        <v>460688</v>
       </c>
       <c r="R211" t="n">
-        <v>7052159</v>
+        <v>7051819</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -25726,7 +25731,7 @@
       </c>
       <c r="Z211" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
@@ -25736,12 +25741,7 @@
       </c>
       <c r="AB211" t="inlineStr">
         <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC211" t="inlineStr">
-        <is>
-          <t>På gammal gran, 170-200 år, i gammal granskog</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -25771,7 +25771,7 @@
         <v>134190455</v>
       </c>
       <c r="B212" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -25889,10 +25889,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>134188053</v>
+        <v>134188004</v>
       </c>
       <c r="B213" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -25924,10 +25924,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>460762</v>
+        <v>460734</v>
       </c>
       <c r="R213" t="n">
-        <v>7052283</v>
+        <v>7052252</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -25996,10 +25996,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>134190579</v>
+        <v>134190741</v>
       </c>
       <c r="B214" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -26024,17 +26024,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I214" t="inlineStr"/>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P214" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>460635</v>
+        <v>460702</v>
       </c>
       <c r="R214" t="n">
-        <v>7052005</v>
+        <v>7051819</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -26066,7 +26075,7 @@
       </c>
       <c r="Z214" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
@@ -26076,7 +26085,7 @@
       </c>
       <c r="AB214" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -26103,10 +26112,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>134188004</v>
+        <v>134188053</v>
       </c>
       <c r="B215" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -26138,10 +26147,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>460734</v>
+        <v>460762</v>
       </c>
       <c r="R215" t="n">
-        <v>7052252</v>
+        <v>7052283</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -26210,10 +26219,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>134190741</v>
+        <v>134190569</v>
       </c>
       <c r="B216" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -26254,10 +26263,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>460702</v>
+        <v>460773</v>
       </c>
       <c r="R216" t="n">
-        <v>7051819</v>
+        <v>7052035</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -26289,7 +26298,7 @@
       </c>
       <c r="Z216" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
@@ -26299,7 +26308,7 @@
       </c>
       <c r="AB216" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -26326,10 +26335,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>134190569</v>
+        <v>134190579</v>
       </c>
       <c r="B217" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -26354,26 +26363,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I217" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J217" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I217" t="inlineStr"/>
       <c r="P217" t="inlineStr">
         <is>
           <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>460773</v>
+        <v>460635</v>
       </c>
       <c r="R217" t="n">
-        <v>7052035</v>
+        <v>7052005</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -26405,7 +26405,7 @@
       </c>
       <c r="Z217" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
@@ -26415,7 +26415,7 @@
       </c>
       <c r="AB217" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -26445,7 +26445,7 @@
         <v>134187660</v>
       </c>
       <c r="B218" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -26557,7 +26557,7 @@
         <v>134188655</v>
       </c>
       <c r="B219" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -26678,7 +26678,7 @@
         <v>134189045</v>
       </c>
       <c r="B220" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -26785,7 +26785,7 @@
         <v>134187869</v>
       </c>
       <c r="B221" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>

--- a/artfynd/A 51504-2025 artfynd.xlsx
+++ b/artfynd/A 51504-2025 artfynd.xlsx
@@ -9669,7 +9669,7 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -23952,7 +23952,7 @@
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>

--- a/artfynd/A 51504-2025 artfynd.xlsx
+++ b/artfynd/A 51504-2025 artfynd.xlsx
@@ -9669,7 +9669,7 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -22166,7 +22166,7 @@
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
@@ -23952,7 +23952,7 @@
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>

--- a/artfynd/A 51504-2025 artfynd.xlsx
+++ b/artfynd/A 51504-2025 artfynd.xlsx
@@ -13235,7 +13235,7 @@
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>

--- a/artfynd/A 51504-2025 artfynd.xlsx
+++ b/artfynd/A 51504-2025 artfynd.xlsx
@@ -9669,7 +9669,7 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -13235,7 +13235,7 @@
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
@@ -17488,7 +17488,7 @@
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
@@ -22166,7 +22166,7 @@
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
@@ -23952,7 +23952,7 @@
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>

--- a/artfynd/A 51504-2025 artfynd.xlsx
+++ b/artfynd/A 51504-2025 artfynd.xlsx
@@ -12137,7 +12137,7 @@
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
@@ -17488,7 +17488,7 @@
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>

--- a/artfynd/A 51504-2025 artfynd.xlsx
+++ b/artfynd/A 51504-2025 artfynd.xlsx
@@ -12137,7 +12137,7 @@
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>

--- a/artfynd/A 51504-2025 artfynd.xlsx
+++ b/artfynd/A 51504-2025 artfynd.xlsx
@@ -12137,7 +12137,7 @@
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>

--- a/artfynd/A 51504-2025 artfynd.xlsx
+++ b/artfynd/A 51504-2025 artfynd.xlsx
@@ -9669,7 +9669,7 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -23952,7 +23952,7 @@
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>

--- a/artfynd/A 51504-2025 artfynd.xlsx
+++ b/artfynd/A 51504-2025 artfynd.xlsx
@@ -26333,7 +26333,7 @@
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>

--- a/artfynd/A 51504-2025 artfynd.xlsx
+++ b/artfynd/A 51504-2025 artfynd.xlsx
@@ -26333,7 +26333,7 @@
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>

--- a/artfynd/A 51504-2025 artfynd.xlsx
+++ b/artfynd/A 51504-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY227"/>
+  <dimension ref="A1:AY222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25751,10 +25751,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>134163114</v>
+        <v>134165583</v>
       </c>
       <c r="B217" t="n">
-        <v>57975</v>
+        <v>58079</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -25762,16 +25762,16 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -25779,25 +25779,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I217" t="inlineStr"/>
-      <c r="M217" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="P217" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>460736</v>
+        <v>460650</v>
       </c>
       <c r="R217" t="n">
-        <v>7052124</v>
+        <v>7052431</v>
       </c>
       <c r="S217" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T217" t="inlineStr">
         <is>
@@ -25826,7 +25825,7 @@
       </c>
       <c r="Z217" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
@@ -25836,12 +25835,7 @@
       </c>
       <c r="AB217" t="inlineStr">
         <is>
-          <t>11:24</t>
-        </is>
-      </c>
-      <c r="AC217" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -25868,53 +25862,48 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>134163338</v>
+        <v>134165125</v>
       </c>
       <c r="B218" t="n">
-        <v>57975</v>
+        <v>99217</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
-      <c r="M218" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P218" t="inlineStr">
         <is>
           <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>460744</v>
+        <v>460690</v>
       </c>
       <c r="R218" t="n">
-        <v>7052204</v>
+        <v>7052375</v>
       </c>
       <c r="S218" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T218" t="inlineStr">
         <is>
@@ -25943,7 +25932,7 @@
       </c>
       <c r="Z218" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
@@ -25953,12 +25942,7 @@
       </c>
       <c r="AB218" t="inlineStr">
         <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AC218" t="inlineStr">
-        <is>
-          <t>Ca 5 äldre rader med ringhack på gammal grov levande gran i gammal garnlavsrik granskog</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -25973,65 +25957,60 @@
       <c r="AT218" t="inlineStr"/>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>134163852</v>
+        <v>134166104</v>
       </c>
       <c r="B219" t="n">
-        <v>57975</v>
+        <v>99217</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
-      <c r="M219" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P219" t="inlineStr">
         <is>
           <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>460763</v>
+        <v>460692</v>
       </c>
       <c r="R219" t="n">
-        <v>7052266</v>
+        <v>7052457</v>
       </c>
       <c r="S219" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T219" t="inlineStr">
         <is>
@@ -26060,7 +26039,7 @@
       </c>
       <c r="Z219" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
@@ -26070,12 +26049,7 @@
       </c>
       <c r="AB219" t="inlineStr">
         <is>
-          <t>11:49</t>
-        </is>
-      </c>
-      <c r="AC219" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -26102,10 +26076,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>134165576</v>
+        <v>124272867</v>
       </c>
       <c r="B220" t="n">
-        <v>57975</v>
+        <v>79085</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -26113,48 +26087,34 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I220" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L220" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M220" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr"/>
       <c r="P220" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>460650</v>
+        <v>460773</v>
       </c>
       <c r="R220" t="n">
-        <v>7052431</v>
+        <v>7052228</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -26181,22 +26141,27 @@
       </c>
       <c r="Y220" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="Z220" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="AB220" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="AC220" t="inlineStr">
+        <is>
+          <t>På kolad ved på gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -26211,62 +26176,57 @@
       <c r="AT220" t="inlineStr"/>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>134166396</v>
+        <v>134165723</v>
       </c>
       <c r="B221" t="n">
-        <v>57975</v>
+        <v>80444</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>100109</v>
+        <v>229748</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
-      <c r="M221" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P221" t="inlineStr">
         <is>
           <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>460693</v>
+        <v>460711</v>
       </c>
       <c r="R221" t="n">
-        <v>7052473</v>
+        <v>7052457</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -26298,7 +26258,7 @@
       </c>
       <c r="Z221" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
@@ -26308,12 +26268,12 @@
       </c>
       <c r="AB221" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AC221" t="inlineStr">
         <is>
-          <t>Ringhack på gammal levande gran i gammal granskog</t>
+          <t>På gammal rönn i gammal granskog</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -26340,10 +26300,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>134165583</v>
+        <v>134171948</v>
       </c>
       <c r="B222" t="n">
-        <v>58079</v>
+        <v>86699</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -26351,41 +26311,32 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>103031</v>
-      </c>
-      <c r="F222" t="inlineStr">
-        <is>
-          <t>Lavskrika</t>
-        </is>
+        <v>229848</v>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Refractohilum galligenum</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I222" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>460650</v>
+        <v>460714</v>
       </c>
       <c r="R222" t="n">
-        <v>7052431</v>
+        <v>7052447</v>
       </c>
       <c r="S222" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T222" t="inlineStr">
         <is>
@@ -26414,7 +26365,7 @@
       </c>
       <c r="Z222" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
@@ -26424,7 +26375,12 @@
       </c>
       <c r="AB222" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AC222" t="inlineStr">
+        <is>
+          <t>På stuplav på gammal rönnlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -26439,560 +26395,15 @@
       <c r="AT222" t="inlineStr"/>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
-    </row>
-    <row r="223">
-      <c r="A223" t="n">
-        <v>134165125</v>
-      </c>
-      <c r="B223" t="n">
-        <v>99217</v>
-      </c>
-      <c r="D223" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E223" t="n">
-        <v>221952</v>
-      </c>
-      <c r="F223" t="inlineStr">
-        <is>
-          <t>Spindelblomster</t>
-        </is>
-      </c>
-      <c r="G223" t="inlineStr">
-        <is>
-          <t>Neottia cordata</t>
-        </is>
-      </c>
-      <c r="H223" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I223" t="inlineStr"/>
-      <c r="P223" t="inlineStr">
-        <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q223" t="n">
-        <v>460690</v>
-      </c>
-      <c r="R223" t="n">
-        <v>7052375</v>
-      </c>
-      <c r="S223" t="n">
-        <v>5</v>
-      </c>
-      <c r="T223" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U223" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V223" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W223" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y223" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="Z223" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AA223" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="AB223" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AD223" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE223" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG223" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT223" t="inlineStr"/>
-      <c r="AW223" t="inlineStr">
-        <is>
-          <t>Ludvig Nordin</t>
-        </is>
-      </c>
-      <c r="AX223" t="inlineStr">
-        <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
-        </is>
-      </c>
-      <c r="AY223" t="inlineStr"/>
-    </row>
-    <row r="224">
-      <c r="A224" t="n">
-        <v>134166104</v>
-      </c>
-      <c r="B224" t="n">
-        <v>99217</v>
-      </c>
-      <c r="D224" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E224" t="n">
-        <v>221952</v>
-      </c>
-      <c r="F224" t="inlineStr">
-        <is>
-          <t>Spindelblomster</t>
-        </is>
-      </c>
-      <c r="G224" t="inlineStr">
-        <is>
-          <t>Neottia cordata</t>
-        </is>
-      </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I224" t="inlineStr"/>
-      <c r="P224" t="inlineStr">
-        <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q224" t="n">
-        <v>460692</v>
-      </c>
-      <c r="R224" t="n">
-        <v>7052457</v>
-      </c>
-      <c r="S224" t="n">
-        <v>4</v>
-      </c>
-      <c r="T224" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U224" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V224" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W224" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y224" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="Z224" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="AA224" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="AB224" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="AD224" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE224" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG224" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT224" t="inlineStr"/>
-      <c r="AW224" t="inlineStr">
-        <is>
-          <t>Ludvig Nordin</t>
-        </is>
-      </c>
-      <c r="AX224" t="inlineStr">
-        <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
-        </is>
-      </c>
-      <c r="AY224" t="inlineStr"/>
-    </row>
-    <row r="225">
-      <c r="A225" t="n">
-        <v>124272867</v>
-      </c>
-      <c r="B225" t="n">
-        <v>79085</v>
-      </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E225" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F225" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G225" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H225" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I225" t="inlineStr"/>
-      <c r="P225" t="inlineStr">
-        <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
-        </is>
-      </c>
-      <c r="Q225" t="n">
-        <v>460773</v>
-      </c>
-      <c r="R225" t="n">
-        <v>7052228</v>
-      </c>
-      <c r="S225" t="n">
-        <v>10</v>
-      </c>
-      <c r="T225" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U225" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V225" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W225" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y225" t="inlineStr">
-        <is>
-          <t>2025-04-20</t>
-        </is>
-      </c>
-      <c r="Z225" t="inlineStr">
-        <is>
-          <t>18:50</t>
-        </is>
-      </c>
-      <c r="AA225" t="inlineStr">
-        <is>
-          <t>2025-04-20</t>
-        </is>
-      </c>
-      <c r="AB225" t="inlineStr">
-        <is>
-          <t>18:50</t>
-        </is>
-      </c>
-      <c r="AC225" t="inlineStr">
-        <is>
-          <t>På kolad ved på gammal tallhögstubbe</t>
-        </is>
-      </c>
-      <c r="AD225" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE225" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG225" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT225" t="inlineStr"/>
-      <c r="AW225" t="inlineStr">
-        <is>
-          <t>Fredrik Jonsson</t>
-        </is>
-      </c>
-      <c r="AX225" t="inlineStr">
-        <is>
-          <t>Fredrik Jonsson</t>
-        </is>
-      </c>
-      <c r="AY225" t="inlineStr"/>
-    </row>
-    <row r="226">
-      <c r="A226" t="n">
-        <v>134165723</v>
-      </c>
-      <c r="B226" t="n">
-        <v>80444</v>
-      </c>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E226" t="n">
-        <v>229748</v>
-      </c>
-      <c r="F226" t="inlineStr">
-        <is>
-          <t>Gytterlav</t>
-        </is>
-      </c>
-      <c r="G226" t="inlineStr">
-        <is>
-          <t>Protopannaria pezizoides</t>
-        </is>
-      </c>
-      <c r="H226" t="inlineStr">
-        <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
-        </is>
-      </c>
-      <c r="I226" t="inlineStr"/>
-      <c r="P226" t="inlineStr">
-        <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q226" t="n">
-        <v>460711</v>
-      </c>
-      <c r="R226" t="n">
-        <v>7052457</v>
-      </c>
-      <c r="S226" t="n">
-        <v>10</v>
-      </c>
-      <c r="T226" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U226" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V226" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W226" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y226" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="Z226" t="inlineStr">
-        <is>
-          <t>12:58</t>
-        </is>
-      </c>
-      <c r="AA226" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="AB226" t="inlineStr">
-        <is>
-          <t>12:58</t>
-        </is>
-      </c>
-      <c r="AC226" t="inlineStr">
-        <is>
-          <t>På gammal rönn i gammal granskog</t>
-        </is>
-      </c>
-      <c r="AD226" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE226" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG226" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT226" t="inlineStr"/>
-      <c r="AW226" t="inlineStr">
-        <is>
-          <t>Fredrik Jonsson</t>
-        </is>
-      </c>
-      <c r="AX226" t="inlineStr">
-        <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
-        </is>
-      </c>
-      <c r="AY226" t="inlineStr"/>
-    </row>
-    <row r="227">
-      <c r="A227" t="n">
-        <v>134171948</v>
-      </c>
-      <c r="B227" t="n">
-        <v>86699</v>
-      </c>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E227" t="n">
-        <v>229848</v>
-      </c>
-      <c r="G227" t="inlineStr">
-        <is>
-          <t>Refractohilum galligenum</t>
-        </is>
-      </c>
-      <c r="H227" t="inlineStr">
-        <is>
-          <t>D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I227" t="inlineStr"/>
-      <c r="P227" t="inlineStr">
-        <is>
-          <t>Bergmyrbäcken, Jmt</t>
-        </is>
-      </c>
-      <c r="Q227" t="n">
-        <v>460714</v>
-      </c>
-      <c r="R227" t="n">
-        <v>7052447</v>
-      </c>
-      <c r="S227" t="n">
-        <v>11</v>
-      </c>
-      <c r="T227" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U227" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V227" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W227" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y227" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="Z227" t="inlineStr">
-        <is>
-          <t>13:23</t>
-        </is>
-      </c>
-      <c r="AA227" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="AB227" t="inlineStr">
-        <is>
-          <t>13:23</t>
-        </is>
-      </c>
-      <c r="AC227" t="inlineStr">
-        <is>
-          <t>På stuplav på gammal rönnlåga i gammal granskog</t>
-        </is>
-      </c>
-      <c r="AD227" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE227" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG227" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT227" t="inlineStr"/>
-      <c r="AW227" t="inlineStr">
-        <is>
-          <t>Fredrik Jonsson</t>
-        </is>
-      </c>
-      <c r="AX227" t="inlineStr">
-        <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
-        </is>
-      </c>
-      <c r="AY227" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51504-2025 artfynd.xlsx
+++ b/artfynd/A 51504-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY222"/>
+  <dimension ref="A1:AY227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25751,10 +25751,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>134165583</v>
+        <v>134163114</v>
       </c>
       <c r="B217" t="n">
-        <v>58079</v>
+        <v>57975</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -25762,16 +25762,16 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -25779,24 +25779,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I217" t="inlineStr">
-        <is>
-          <t>3</t>
+      <c r="I217" t="inlineStr"/>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P217" t="inlineStr">
         <is>
-          <t>Lortåsen, Lortåsen, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>460650</v>
+        <v>460736</v>
       </c>
       <c r="R217" t="n">
-        <v>7052431</v>
+        <v>7052124</v>
       </c>
       <c r="S217" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T217" t="inlineStr">
         <is>
@@ -25825,7 +25826,7 @@
       </c>
       <c r="Z217" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
@@ -25835,7 +25836,12 @@
       </c>
       <c r="AB217" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AC217" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -25862,48 +25868,53 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>134165125</v>
+        <v>134163338</v>
       </c>
       <c r="B218" t="n">
-        <v>99217</v>
+        <v>57975</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P218" t="inlineStr">
         <is>
           <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>460690</v>
+        <v>460744</v>
       </c>
       <c r="R218" t="n">
-        <v>7052375</v>
+        <v>7052204</v>
       </c>
       <c r="S218" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T218" t="inlineStr">
         <is>
@@ -25932,7 +25943,7 @@
       </c>
       <c r="Z218" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
@@ -25942,7 +25953,12 @@
       </c>
       <c r="AB218" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC218" t="inlineStr">
+        <is>
+          <t>Ca 5 äldre rader med ringhack på gammal grov levande gran i gammal garnlavsrik granskog</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -25957,60 +25973,65 @@
       <c r="AT218" t="inlineStr"/>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>134166104</v>
+        <v>134163852</v>
       </c>
       <c r="B219" t="n">
-        <v>99217</v>
+        <v>57975</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P219" t="inlineStr">
         <is>
           <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>460692</v>
+        <v>460763</v>
       </c>
       <c r="R219" t="n">
-        <v>7052457</v>
+        <v>7052266</v>
       </c>
       <c r="S219" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T219" t="inlineStr">
         <is>
@@ -26039,7 +26060,7 @@
       </c>
       <c r="Z219" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
@@ -26049,7 +26070,12 @@
       </c>
       <c r="AB219" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AC219" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -26076,10 +26102,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>124272867</v>
+        <v>134165576</v>
       </c>
       <c r="B220" t="n">
-        <v>79085</v>
+        <v>57975</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -26087,34 +26113,48 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I220" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P220" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>460773</v>
+        <v>460650</v>
       </c>
       <c r="R220" t="n">
-        <v>7052228</v>
+        <v>7052431</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -26141,27 +26181,22 @@
       </c>
       <c r="Y220" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="Z220" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AB220" t="inlineStr">
         <is>
-          <t>18:50</t>
-        </is>
-      </c>
-      <c r="AC220" t="inlineStr">
-        <is>
-          <t>På kolad ved på gammal tallhögstubbe</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -26176,57 +26211,62 @@
       <c r="AT220" t="inlineStr"/>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>134165723</v>
+        <v>134166396</v>
       </c>
       <c r="B221" t="n">
-        <v>80444</v>
+        <v>57975</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>229748</v>
+        <v>100109</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P221" t="inlineStr">
         <is>
           <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>460711</v>
+        <v>460693</v>
       </c>
       <c r="R221" t="n">
-        <v>7052457</v>
+        <v>7052473</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -26258,7 +26298,7 @@
       </c>
       <c r="Z221" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
@@ -26268,12 +26308,12 @@
       </c>
       <c r="AB221" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AC221" t="inlineStr">
         <is>
-          <t>På gammal rönn i gammal granskog</t>
+          <t>Ringhack på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -26300,10 +26340,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>134171948</v>
+        <v>134165583</v>
       </c>
       <c r="B222" t="n">
-        <v>86699</v>
+        <v>58079</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -26311,32 +26351,41 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>229848</v>
+        <v>103031</v>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Refractohilum galligenum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I222" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P222" t="inlineStr">
         <is>
-          <t>Bergmyrbäcken, Jmt</t>
+          <t>Lortåsen, Lortåsen, Jmt</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>460714</v>
+        <v>460650</v>
       </c>
       <c r="R222" t="n">
-        <v>7052447</v>
+        <v>7052431</v>
       </c>
       <c r="S222" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T222" t="inlineStr">
         <is>
@@ -26365,7 +26414,7 @@
       </c>
       <c r="Z222" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
@@ -26375,12 +26424,7 @@
       </c>
       <c r="AB222" t="inlineStr">
         <is>
-          <t>13:23</t>
-        </is>
-      </c>
-      <c r="AC222" t="inlineStr">
-        <is>
-          <t>På stuplav på gammal rönnlåga i gammal granskog</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -26395,15 +26439,560 @@
       <c r="AT222" t="inlineStr"/>
       <c r="AW222" t="inlineStr">
         <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX222" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>134165125</v>
+      </c>
+      <c r="B223" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E223" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr"/>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>Lortåsen, Lortåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q223" t="n">
+        <v>460690</v>
+      </c>
+      <c r="R223" t="n">
+        <v>7052375</v>
+      </c>
+      <c r="S223" t="n">
+        <v>5</v>
+      </c>
+      <c r="T223" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U223" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V223" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W223" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y223" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z223" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB223" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AD223" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE223" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG223" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT223" t="inlineStr"/>
+      <c r="AW223" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX223" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>134166104</v>
+      </c>
+      <c r="B224" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E224" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr"/>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>Lortåsen, Lortåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q224" t="n">
+        <v>460692</v>
+      </c>
+      <c r="R224" t="n">
+        <v>7052457</v>
+      </c>
+      <c r="S224" t="n">
+        <v>4</v>
+      </c>
+      <c r="T224" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U224" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V224" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W224" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y224" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z224" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AA224" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB224" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AD224" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE224" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG224" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT224" t="inlineStr"/>
+      <c r="AW224" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX224" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>124272867</v>
+      </c>
+      <c r="B225" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E225" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr"/>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q225" t="n">
+        <v>460773</v>
+      </c>
+      <c r="R225" t="n">
+        <v>7052228</v>
+      </c>
+      <c r="S225" t="n">
+        <v>10</v>
+      </c>
+      <c r="T225" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V225" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W225" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y225" t="inlineStr">
+        <is>
+          <t>2025-04-20</t>
+        </is>
+      </c>
+      <c r="Z225" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>2025-04-20</t>
+        </is>
+      </c>
+      <c r="AB225" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="AC225" t="inlineStr">
+        <is>
+          <t>På kolad ved på gammal tallhögstubbe</t>
+        </is>
+      </c>
+      <c r="AD225" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE225" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG225" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT225" t="inlineStr"/>
+      <c r="AW225" t="inlineStr">
+        <is>
           <t>Fredrik Jonsson</t>
         </is>
       </c>
-      <c r="AX222" t="inlineStr">
+      <c r="AX225" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY225" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>134165723</v>
+      </c>
+      <c r="B226" t="n">
+        <v>80444</v>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E226" t="n">
+        <v>229748</v>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>Protopannaria pezizoides</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr"/>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>Lortåsen, Lortåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q226" t="n">
+        <v>460711</v>
+      </c>
+      <c r="R226" t="n">
+        <v>7052457</v>
+      </c>
+      <c r="S226" t="n">
+        <v>10</v>
+      </c>
+      <c r="T226" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V226" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W226" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y226" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z226" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB226" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AC226" t="inlineStr">
+        <is>
+          <t>På gammal rönn i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD226" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE226" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG226" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT226" t="inlineStr"/>
+      <c r="AW226" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX226" t="inlineStr">
         <is>
           <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
-      <c r="AY222" t="inlineStr"/>
+      <c r="AY226" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>134171948</v>
+      </c>
+      <c r="B227" t="n">
+        <v>86699</v>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E227" t="n">
+        <v>229848</v>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>Refractohilum galligenum</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr"/>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>Bergmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q227" t="n">
+        <v>460714</v>
+      </c>
+      <c r="R227" t="n">
+        <v>7052447</v>
+      </c>
+      <c r="S227" t="n">
+        <v>11</v>
+      </c>
+      <c r="T227" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U227" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V227" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W227" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y227" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z227" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AA227" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB227" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AC227" t="inlineStr">
+        <is>
+          <t>På stuplav på gammal rönnlåga i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD227" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE227" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG227" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT227" t="inlineStr"/>
+      <c r="AW227" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX227" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY227" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51504-2025 artfynd.xlsx
+++ b/artfynd/A 51504-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY227"/>
+  <dimension ref="A1:AZ227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124266771</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124267610</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1003,6 +1018,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124267176</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1115,6 +1135,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124266902</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124268780</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1344,6 +1374,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124273037</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1486,6 +1521,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124273727</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1598,6 +1638,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124270220</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1714,6 +1759,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124267622</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1821,6 +1871,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124266776</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1933,6 +1988,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124268772</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2045,6 +2105,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124270147</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2157,6 +2222,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134162490</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2269,6 +2339,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124270241</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2381,6 +2456,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124270612</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2488,6 +2568,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124273453</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2595,6 +2680,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124273671</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2707,6 +2797,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134161245</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2819,6 +2914,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134161962</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2931,6 +3031,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124266217</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3043,6 +3148,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124268429</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3155,6 +3265,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124269652</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3267,6 +3382,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124274109</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3379,6 +3499,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134171971</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3491,6 +3616,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124266795</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3598,6 +3728,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134161209</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3710,6 +3845,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124266696</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3842,6 +3982,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124266718</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3974,6 +4119,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124267327</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4111,6 +4261,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124267409</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4248,6 +4403,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124267659</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4369,6 +4529,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124268210</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4476,6 +4641,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124268409</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4613,6 +4783,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124268502</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4720,6 +4895,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124268956</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4832,6 +5012,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124269204</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4969,6 +5154,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124269395</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5111,6 +5301,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124269628</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5232,6 +5427,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124270076</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5344,6 +5544,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124272071</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5490,6 +5695,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124274112</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5621,6 +5831,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124274542</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5737,6 +5952,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134159342</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5858,6 +6078,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134160600</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5974,6 +6199,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134160932</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6095,6 +6325,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134161368</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6216,6 +6451,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134161522</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6337,6 +6577,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134161529</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6463,6 +6708,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134161617</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6584,6 +6834,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134161669</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6705,6 +6960,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134162379</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6826,6 +7086,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134162445</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6947,6 +7212,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134162546</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7068,6 +7338,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134162652</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7189,6 +7464,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134162816</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7305,6 +7585,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134162895</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7417,6 +7702,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134171972</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7538,6 +7828,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134187405</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7659,6 +7954,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134188655</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7766,6 +8066,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134188822</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7873,6 +8178,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134189045</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7994,6 +8304,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134190455</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -8115,6 +8430,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134190545</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8231,6 +8551,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134190569</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8338,6 +8663,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134190579</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8445,6 +8775,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134190717</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8561,6 +8896,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134190741</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8668,6 +9008,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134190856</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8780,6 +9125,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124266490</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8892,6 +9242,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124267282</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8999,6 +9354,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124267753</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -9106,6 +9466,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124268432</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -9218,6 +9583,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124269152</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9330,6 +9700,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124270433</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9442,6 +9817,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124272396</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9554,6 +9934,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124272644</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9666,6 +10051,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124272951</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9778,6 +10168,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124273054</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9890,6 +10285,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124273176</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -10002,6 +10402,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124273508</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -10114,6 +10519,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134160980</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -10226,6 +10636,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124269445</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -10338,6 +10753,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134171974</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10450,6 +10870,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124266911</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10557,6 +10982,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124269569</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10664,6 +11094,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124267103</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10776,6 +11211,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124267477</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10883,6 +11323,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124267924</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10995,6 +11440,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124268628</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -11102,6 +11552,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134158960</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -11209,6 +11664,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134162493</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -11321,6 +11781,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124266255</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11428,6 +11893,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124266826</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11545,6 +12015,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124269872</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11657,6 +12132,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124273892</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11799,6 +12279,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124273896</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11911,6 +12396,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134159178</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -12023,6 +12513,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134171967</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -12130,6 +12625,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124266881</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -12242,6 +12742,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124269673</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -12384,6 +12889,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124273916</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -12496,6 +13006,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124273924</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12608,6 +13123,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134171968</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12715,6 +13235,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124266871</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12827,6 +13352,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124269686</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12939,6 +13469,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124274095</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -13081,6 +13616,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124266520</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -13228,6 +13768,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124268342</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -13345,6 +13890,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124268557</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -13481,6 +14031,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124269975</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -13628,6 +14183,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124266973</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -13775,6 +14335,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124267188</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -13922,6 +14487,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124268185</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -14039,6 +14609,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124268252</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -14156,6 +14731,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124269436</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -14303,6 +14883,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124269906</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -14420,6 +15005,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124270215</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -14537,6 +15127,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124271818</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -14654,6 +15249,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124272685</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -14771,6 +15371,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124272912</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -14913,6 +15518,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124274274</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -15030,6 +15640,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124274581</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -15150,6 +15765,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134171973</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -15266,6 +15886,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124266592</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -15378,6 +16003,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124268233</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -15494,6 +16124,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124269131</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -15606,6 +16241,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134171963</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -15722,6 +16362,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134158548</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -15829,6 +16474,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134158417</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -15941,6 +16591,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134171969</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -16058,6 +16713,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124274324</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -16170,6 +16830,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134171965</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -16277,6 +16942,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134158853</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -16384,6 +17054,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134158911</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -16491,6 +17166,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134159322</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -16598,6 +17278,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134161325</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -16710,6 +17395,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134171976</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -16827,6 +17517,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124266798</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -16939,6 +17634,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124266857</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -17051,6 +17751,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124267750</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -17163,6 +17868,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134171970</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -17275,6 +17985,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124266590</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -17387,6 +18102,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124266711</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -17499,6 +18219,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124268215</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -17611,6 +18336,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124268273</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -17723,6 +18453,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124268415</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -17835,6 +18570,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124270409</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -17947,6 +18687,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124271872</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -18054,6 +18799,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124274384</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -18166,6 +18916,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124266724</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -18282,6 +19037,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124270194</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -18394,6 +19154,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124266865</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -18506,6 +19271,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124266993</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -18618,6 +19388,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124269984</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -18730,6 +19505,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134159098</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -18842,6 +19622,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134171966</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -18964,6 +19749,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124269968</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -19086,6 +19876,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124274126</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -19197,6 +19992,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134171975</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -19309,6 +20109,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134163087</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -19426,6 +20231,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134165432</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -19538,6 +20348,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134165966</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -19650,6 +20465,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134164962</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -19762,6 +20582,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134164951</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -19869,6 +20694,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134165091</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -19976,6 +20806,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124269155</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -20083,6 +20918,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124269623</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -20225,6 +21065,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124270532</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -20367,6 +21212,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124271205</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -20504,6 +21354,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124271595</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -20636,6 +21491,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124271938</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -20773,6 +21633,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124272148</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -20915,6 +21780,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124272422</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -21061,6 +21931,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124272846</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -21207,6 +22082,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124273053</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -21328,6 +22208,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134163277</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -21449,6 +22334,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134163868</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -21565,6 +22455,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134165139</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -21677,6 +22572,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134165861</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -21798,6 +22698,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134166248</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -21919,6 +22824,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134166331</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -22035,6 +22945,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134166640</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -22156,6 +23071,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134166744</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -22263,6 +23183,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134171949</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -22370,6 +23295,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134171950</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -22477,6 +23407,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134171952</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -22584,6 +23519,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134171953</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -22691,6 +23631,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134171954</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -22798,6 +23743,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134171955</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -22905,6 +23855,11 @@
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134171957</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -23012,6 +23967,11 @@
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134171958</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -23119,6 +24079,11 @@
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134171959</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -23231,6 +24196,11 @@
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134187536</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -23352,6 +24322,11 @@
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134187568</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -23464,6 +24439,11 @@
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134187643</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -23576,6 +24556,11 @@
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134187660</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -23688,6 +24673,11 @@
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134187721</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -23800,6 +24790,11 @@
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134187781</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -23907,6 +24902,11 @@
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134187869</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -24014,6 +25014,11 @@
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134187880</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -24121,6 +25126,11 @@
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134187980</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -24228,6 +25238,11 @@
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134188004</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -24335,6 +25350,11 @@
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134188053</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -24442,6 +25462,11 @@
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134188076</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -24554,6 +25579,11 @@
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124272014</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -24666,6 +25696,11 @@
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134165214</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -24778,6 +25813,11 @@
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134165713</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -24890,6 +25930,11 @@
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134171946</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -25002,6 +26047,11 @@
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134171947</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -25109,6 +26159,11 @@
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124269874</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -25251,6 +26306,11 @@
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124272055</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -25367,6 +26427,11 @@
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124272441</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -25514,6 +26579,11 @@
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124271760</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -25631,6 +26701,11 @@
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124272428</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -25748,6 +26823,11 @@
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124272795</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -25865,6 +26945,11 @@
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134163114</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -25982,6 +27067,11 @@
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134163338</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -26099,6 +27189,11 @@
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134163852</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -26220,6 +27315,11 @@
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134165576</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -26333,10 +27433,15 @@
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134166396</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -26448,6 +27553,11 @@
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134165583</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -26555,6 +27665,11 @@
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134165125</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -26662,6 +27777,11 @@
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134166104</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -26774,6 +27894,11 @@
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124272867</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -26886,6 +28011,11 @@
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134165723</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -26993,8 +28123,241 @@
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134171948</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 51504-2025 artfynd.xlsx
+++ b/artfynd/A 51504-2025 artfynd.xlsx
@@ -26834,7 +26834,7 @@
         <v>134163114</v>
       </c>
       <c r="B217" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -26956,7 +26956,7 @@
         <v>134163338</v>
       </c>
       <c r="B218" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -27078,7 +27078,7 @@
         <v>134163852</v>
       </c>
       <c r="B219" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -27200,7 +27200,7 @@
         <v>134165576</v>
       </c>
       <c r="B220" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -27326,7 +27326,7 @@
         <v>134166396</v>
       </c>
       <c r="B221" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -27433,7 +27433,7 @@
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>

--- a/artfynd/A 51504-2025 artfynd.xlsx
+++ b/artfynd/A 51504-2025 artfynd.xlsx
@@ -27433,7 +27433,7 @@
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
